--- a/RXL_WbInfo.xlsx
+++ b/RXL_WbInfo.xlsx
@@ -1,32 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\_RXL\Development\LAMBDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\_RXL\Development\LAMBDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABE5A68-E007-41F9-89ED-90B1174CA453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28677701-034E-4A86-935F-3C7E6413D6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29E0D24-0EA8-4D41-8E06-9F040E158B6C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C29E0D24-0EA8-4D41-8E06-9F040E158B6C}"/>
   </bookViews>
   <sheets>
     <sheet name="SheetName" sheetId="11" r:id="rId1"/>
     <sheet name="WorkbookName" sheetId="14" r:id="rId2"/>
     <sheet name="FilePath" sheetId="15" r:id="rId3"/>
     <sheet name="Demo" sheetId="13" r:id="rId4"/>
-    <sheet name="Lookups" sheetId="12" r:id="rId5"/>
+    <sheet name="VBA" sheetId="17" r:id="rId5"/>
+    <sheet name="Lookups" sheetId="12" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_OnOff">Lookups!$C$6:$C$7</definedName>
     <definedName name="_YesNo">Lookups!$C$3:$C$4</definedName>
-    <definedName name="RXL_FilePath" comment="Returns the Workbook file path, with or without the full file name, for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_last_char,_xlop.inc_file_name,_xlfn.LET(_xlpm._chrChk,AND(NOT(_xlfn.ISOMITTED(_xlpm.remove_last_char)),NOT(ISLOGICAL(_xlpm.remove_last_char)),NOT(ISNUMBER(_xlpm.remove_last_char))),_xlpm._fnmChk,AND(NOT(_xlfn.ISOMITTED(_xlpm.inc_file_name)),NOT(ISLOGICAL(_xlpm.inc_file_name)),NOT(ISNUMBER(_xlpm.inc_file_name))),_xlpm._refChk,NOT(ISREF(_xlpm.cell_ref)),_xlpm._lastChr,IF(OR(_xlfn.ISOMITTED(_xlpm.remove_last_char),_xlpm._chrChk),FALSE,_xlpm.remove_last_char),_xlpm._incFile,IF(OR(_xlfn.ISOMITTED(_xlpm.inc_file_name),_xlpm._fnmChk),FALSE,_xlpm.inc_file_name),_xlpm._full,CELL("filename",_xlpm.cell_ref),_xlpm._path,_xlfn.TEXTBEFORE(_xlpm._full,"[",-1,,,"#"),_xlpm._filePath,IF(_xlpm._lastChr,LEFT(_xlpm._path,LEN(_xlpm._path)-1),_xlpm._path),_xlpm._wbName,_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm._full,"[",-1,,,"#"),"]",-1,,,"#"),_xlpm._errChk,_xlfn.IFS(_xlpm._refChk,"#[Error: cell reference required]",OR(_xlpm._chrChk,_xlpm._fnmChk),"#[Error: invalid optional input]",OR(ISERROR(_xlpm._filePath),_xlpm._filePath="#"),"#[Error reading File Path]",AND(OR(ISERROR(_xlpm._wbName),_xlpm._wbName="#"),_xlpm._incFile),"#[Error reading Workbook Name]",TRUE,""),_xlpm._rtn,IF(_xlpm._incFile,_xlpm._path&amp;_xlpm._wbName,_xlpm._filePath),IF(_xlpm._errChk&lt;&gt;"",_xlpm._errChk,_xlpm._rtn)))</definedName>
+    <definedName name="RXL_FilePath" comment="Returns the Workbook file path, with or without the full file name, for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_last_char,_xlop.inc_file_name, _xlfn.LET(_xlpm._chrChk, AND(NOT(_xlfn.ISOMITTED(_xlpm.remove_last_char)), NOT(ISLOGICAL(_xlpm.remove_last_char)), NOT(ISNUMBER(_xlpm.remove_last_char))), _xlpm._fnmChk, AND(NOT(_xlfn.ISOMITTED(_xlpm.inc_file_name)), NOT(ISLOGICAL(_xlpm.inc_file_name)), NOT(ISNUMBER(_xlpm.inc_file_name))), _xlpm._refChk, NOT(ISREF(_xlpm.cell_ref)), _xlpm._lastChr, IF(OR(_xlfn.ISOMITTED(_xlpm.remove_last_char), _xlpm._chrChk), FALSE, _xlpm.remove_last_char), _xlpm._incFile, IF(OR(_xlfn.ISOMITTED(_xlpm.inc_file_name), _xlpm._fnmChk), FALSE, _xlpm.inc_file_name), _xlpm._full, CELL("filename", _xlpm.cell_ref), _xlpm._path, _xlfn.TEXTBEFORE(_xlpm._full, "[", -1, , , "#"), _xlpm._filePath, IF(_xlpm._lastChr, LEFT(_xlpm._path, LEN(_xlpm._path) - 1), _xlpm._path), _xlpm._wbName, _xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm._full, "[", -1, , , "#"), "]", -1, , , "#"), _xlpm._errChk, _xlfn.IFS(_xlpm._refChk, "#[Error: cell reference required]", _xlpm._full = "", "#[Error: Workbook must be saved]", OR(_xlpm._chrChk, _xlpm._fnmChk), "#[Error: invalid optional input]", OR(ISERROR(_xlpm._filePath), _xlpm._filePath = "#"), "#[Error reading File Path]", AND(OR(ISERROR(_xlpm._wbName), _xlpm._wbName = "#"), _xlpm._incFile), "#[Error reading Workbook Name]", TRUE, ""), _xlpm._rtn, IF(_xlpm._incFile, _xlpm._path &amp; _xlpm._wbName, _xlpm._filePath), IF(_xlpm._errChk &lt;&gt; "", _xlpm._errChk, _xlpm._rtn)))</definedName>
     <definedName name="RXL_FilePath_Alt" comment="Returns the Workbook file path, with or without the full file name, for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_last_char,_xlop.inc_file_name,_xlfn.LET(_xlpm._chrChk,AND(NOT(_xlfn.ISOMITTED(_xlpm.remove_last_char)),NOT(ISLOGICAL(_xlpm.remove_last_char)),NOT(ISNUMBER(_xlpm.remove_last_char))),_xlpm._fnmChk,AND(NOT(_xlfn.ISOMITTED(_xlpm.inc_file_name)),NOT(ISLOGICAL(_xlpm.inc_file_name)),NOT(ISNUMBER(_xlpm.inc_file_name))),_xlpm._refChk,NOT(ISREF(_xlpm.cell_ref)),_xlpm._lastChr,IF(OR(_xlfn.ISOMITTED(_xlpm.remove_last_char),_xlpm._chrChk),FALSE,_xlpm.remove_last_char),_xlpm._incFile,IF(OR(_xlfn.ISOMITTED(_xlpm.inc_file_name),_xlpm._fnmChk),FALSE,_xlpm.inc_file_name),_xlpm._full,CELL("filename",_xlpm.cell_ref),_xlpm._nOpen,IFERROR(FIND("&lt;",SUBSTITUTE(_xlpm._full,"[","&lt;",LEN(_xlpm._full)-LEN(SUBSTITUTE(_xlpm._full,"[",""))))-1,0),_xlpm._nClose,IFERROR(FIND("&gt;",SUBSTITUTE(_xlpm._full,"]","&gt;",LEN(_xlpm._full)-LEN(SUBSTITUTE(_xlpm._full,"]",""))))-1,0),_xlpm._posL,IFERROR(FIND("[",_xlpm._full,_xlpm._nOpen),0),_xlpm._posR,IFERROR(FIND("]",_xlpm._full,_xlpm._nClose),0),_xlpm._fPath,IF(_xlpm._posL&gt;0,LEFT(_xlpm._full,_xlpm._posL-1),"#"),_xlpm._rPath,IF(_xlpm._lastChr,LEFT(_xlpm._fPath,LEN(_xlpm._fPath)-1),_xlpm._fPath),_xlpm._wbName,IF(AND(_xlpm._posL&gt;0,_xlpm._posR&gt;0),MID(_xlpm._full,_xlpm._posL+1,_xlpm._posR-(_xlpm._posL+1)),"#"),_xlpm._errChk,_xlfn.IFS(_xlpm._refChk,"#[Error: cell reference required]",OR(_xlpm._chrChk,_xlpm._fnmChk),"#[Error: invalid optional input]",OR(ISERROR(_xlpm._rPath),_xlpm._rPath="#"),"#[Error reading File Path]",AND(OR(ISERROR(_xlpm._wbName),_xlpm._wbName="#"),_xlpm._incFile),"#[Error reading Workbook Name]",TRUE,""),_xlpm._rtn,IF(_xlpm._incFile,_xlpm._fPath&amp;_xlpm._wbName,_xlpm._rPath),IF(_xlpm._errChk&lt;&gt;"",_xlpm._errChk,_xlpm._rtn)))</definedName>
-    <definedName name="RXL_SheetName" comment="Returns the worksheet name (as displayed in the worksheet tab) for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlfn.LET(_xlpm._inpChk,IF(NOT(ISREF(_xlpm.cell_ref)),"#[Error: cell reference required]",""),_xlpm._fileName,CELL("filename",_xlpm.cell_ref),_xlpm._wsName,_xlfn.TEXTAFTER(_xlpm._fileName, "]",-1,,,"#"),_xlpm._rtn,IF(OR(ISERROR(_xlpm._wsName),_xlpm._wsName="#"),"#[Error reading Sheet name]",_xlpm._wsName),IF(_xlpm._inpChk&lt;&gt;"",_xlpm._inpChk,_xlpm._rtn)))</definedName>
+    <definedName name="RXL_SheetName" comment="Returns the worksheet name (as displayed in the worksheet tab) for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref, _xlfn.LET(_xlpm._inpChk, IF(NOT(ISREF(_xlpm.cell_ref)), "#[Error: cell reference required]", ""), _xlpm._fileName, CELL("filename", _xlpm.cell_ref), _xlpm._wsName, IF(_xlpm._fileName &lt;&gt; "", _xlfn.TEXTAFTER(_xlpm._fileName, "]", -1, , , "#"), "#[Error: Workbook must be saved]"), _xlpm._rtn, IF(OR(ISERROR(_xlpm._wsName), _xlpm._wsName = "#"), "#[Error reading Sheet name]", _xlpm._wsName), IF(_xlpm._inpChk &lt;&gt; "", _xlpm._inpChk, _xlpm._rtn)))</definedName>
     <definedName name="RXL_SheetName_Alt" comment="Returns the worksheet name (as displayed in the worksheet tab) for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlfn.LET(_xlpm._inpChk,IF(NOT(ISREF(_xlpm.cell_ref)),"#[Error: cell reference required]",""),_xlpm._fileName,CELL("filename",_xlpm.cell_ref),_xlpm._pos,IFERROR(FIND("?",SUBSTITUTE(_xlpm._fileName,"]","?",LEN(_xlpm._fileName)-LEN(SUBSTITUTE(_xlpm._fileName,"]","")))),0),_xlpm._wsName,IF(_xlpm._pos&lt;&gt;0,RIGHT(_xlpm._fileName,LEN(_xlpm._fileName)-_xlpm._pos),"#"),_xlpm._rtn,IF(OR(ISERROR(_xlpm._wsName),_xlpm._wsName="#"),"#[Error reading Sheet Name]",_xlpm._wsName),IF(_xlpm._inpChk&lt;&gt;"",_xlpm._inpChk,_xlpm._rtn)))</definedName>
-    <definedName name="RXL_WorkbookName" comment="Returns the Workbook name, with or without the file extension, for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_extension,_xlfn.LET(_xlpm._extChk,AND(NOT(ISLOGICAL(_xlpm.remove_extension)),NOT(ISNUMBER(_xlpm.remove_extension))),_xlpm._fileExt,IF(OR(_xlfn.ISOMITTED(_xlpm.remove_extension),_xlpm._extChk),FALSE,_xlpm.remove_extension),_xlpm._inpChk,IF(NOT(ISREF(_xlpm.cell_ref)),"#[Error: cell reference required]",""),_xlpm._fileName,CELL("filename",_xlpm.cell_ref),_xlpm._strName,_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm._fileName,"[",-1,,,"#"),"]",-1,,,"#"),_xlpm._wbName,IF(_xlpm._fileExt,_xlfn.TEXTBEFORE(_xlpm._strName,".",-1,,,_xlpm._strName),_xlpm._strName),_xlpm._rtn,IF(OR(ISERROR(_xlpm._wbName),_xlpm._wbName="#"),"#[Error reading Workbook name]",_xlpm._wbName),IF(_xlpm._inpChk&lt;&gt;"",_xlpm._inpChk,_xlpm._rtn)))</definedName>
+    <definedName name="RXL_WbInfo.About" comment="Provides information about the functions in this module">_xlfn.LAMBDA(_xlop.select_function, _xlfn.LET(_xlpm._num, IF(_xlfn.ISOMITTED(_xlpm.select_function), 0, IF(ISNUMBER(_xlpm.select_function), INT(_xlpm.select_function), "#")), _xlpm._arrDef, IF(_xlpm._num = 0, _xlfn.TEXTSPLIT("About:¬RXL Workbook Info functions.|" &amp; "¬Suggested module name = RXL_WbInfo|" &amp; "Version:¬v1.06  (April 2025)|" &amp; "Author:¬R Silk, RXL Development|" &amp; "URL:¬https://gist.github.com/r-silk/8160866c15d6184d4958579928647371|" &amp; "¬|" &amp; "Function¬Description|" &amp; "0 - About¬Provides information about the functions in this module|" &amp; "1 - SheetName¬Returns the referenced Worksheet name|" &amp; "2 - WorkbookName¬Returns the referenced Workbook name|" &amp; "3 - FilePath¬Returns the referenced Workbook file path", "¬", "|"), ""), _xlpm._arrNames, _xlfn.TEXTSPLIT("SheetName¦" &amp; "WorkbookName¦" &amp; "FilePath", "¦"), _xlpm._arrHelp, _xlfn.TEXTSPLIT("NAME:¬SheetName|" &amp; "DESCRIPTION:¬Returns the referenced worksheet name|" &amp; "VERSION:¬v1.04  (23-Mar-2025)|" &amp; "PARAMETERS:¬|" &amp; "cell_ref¬(required) a valid cell reference, e.g. 'Sheet1'!A1" &amp; "¦" &amp; "NAME:¬WorkbookName|" &amp; "DESCRIPTION:¬Returns the referenced Workbook name|" &amp; "VERSION:¬v1.05  (23-Mar-2025)|" &amp; "PARAMETERS:¬|" &amp; "cell_ref¬(required) a valid cell reference, e.g. 'Sheet1'!A1|" &amp; "remove_extension¬(optional) Choose whether to remove the file extension (True/False)" &amp; "¦" &amp; "NAME:¬FilePath|" &amp; "DESCRIPTION:¬Returns the referenced Workbook file path|" &amp; "VERSION:¬v1.04  (23-Mar-2025)|" &amp; "PARAMETERS:¬|" &amp; "cell_ref¬(required) a valid cell reference, e.g. 'Sheet1'!A1|" &amp; "remove_last_char¬(optional) Choose whether to remove the last character of the file path (True/False)|" &amp; "inc_file_name¬(optional) Choose whether to add the file name to the file path (True/False)", "¦"), _xlpm._arrOut, IF(_xlpm._num = "#", _xlfn.LET(_xlpm._idx, SUM(_xlfn.SEQUENCE(1, COUNTA(_xlpm._arrNames)) * (_xlpm._arrNames = _xlpm.select_function)), IF(_xlpm._idx &gt; 0, _xlfn.TEXTSPLIT(INDEX(_xlpm._arrHelp, _xlpm._idx), "¬", "|"), "#[Error: name not recognised]")), IF(_xlpm._num &lt;&gt; 0, IFERROR(_xlfn.TEXTSPLIT(INDEX(_xlpm._arrHelp, _xlpm._num), "¬", "|"), "#[Error: index not recognised]"), "")), IF(_xlpm._arrDef = "", _xlpm._arrOut, _xlpm._arrDef)))</definedName>
+    <definedName name="RXL_WbInfo.FilePath" comment="Returns the Workbook file path, with or without the full file name, for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_last_char,_xlop.inc_file_name, _xlfn.LET(_xlpm._chrChk, AND(NOT(_xlfn.ISOMITTED(_xlpm.remove_last_char)), NOT(ISLOGICAL(_xlpm.remove_last_char)), NOT(ISNUMBER(_xlpm.remove_last_char))), _xlpm._fnmChk, AND(NOT(_xlfn.ISOMITTED(_xlpm.inc_file_name)), NOT(ISLOGICAL(_xlpm.inc_file_name)), NOT(ISNUMBER(_xlpm.inc_file_name))), _xlpm._refChk, NOT(ISREF(_xlpm.cell_ref)), _xlpm._lastChr, IF(OR(_xlfn.ISOMITTED(_xlpm.remove_last_char), _xlpm._chrChk), FALSE, _xlpm.remove_last_char), _xlpm._incFile, IF(OR(_xlfn.ISOMITTED(_xlpm.inc_file_name), _xlpm._fnmChk), FALSE, _xlpm.inc_file_name), _xlpm._full, CELL("filename", _xlpm.cell_ref), _xlpm._path, _xlfn.TEXTBEFORE(_xlpm._full, "[", -1, , , "#"), _xlpm._filePath, IF(_xlpm._lastChr, LEFT(_xlpm._path, LEN(_xlpm._path) - 1), _xlpm._path), _xlpm._wbName, _xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm._full, "[", -1, , , "#"), "]", -1, , , "#"), _xlpm._errChk, _xlfn.IFS(_xlpm._refChk, "#[Error: cell reference required]", _xlpm._full = "", "#[Error: Workbook must be saved]", OR(_xlpm._chrChk, _xlpm._fnmChk), "#[Error: invalid optional input]", OR(ISERROR(_xlpm._filePath), _xlpm._filePath = "#"), "#[Error reading File Path]", AND(OR(ISERROR(_xlpm._wbName), _xlpm._wbName = "#"), _xlpm._incFile), "#[Error reading Workbook Name]", TRUE, ""), _xlpm._rtn, IF(_xlpm._incFile, _xlpm._path &amp; _xlpm._wbName, _xlpm._filePath), IF(_xlpm._errChk &lt;&gt; "", _xlpm._errChk, _xlpm._rtn)))</definedName>
+    <definedName name="RXL_WbInfo.SheetName" comment="Returns the worksheet name (as displayed in the worksheet tab) for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref, _xlfn.LET(_xlpm._inpChk, IF(NOT(ISREF(_xlpm.cell_ref)), "#[Error: cell reference required]", ""), _xlpm._fileName, CELL("filename", _xlpm.cell_ref), _xlpm._wsName, IF(_xlpm._fileName &lt;&gt; "", _xlfn.TEXTAFTER(_xlpm._fileName, "]", -1, , , "#"), "#[Error: Workbook must be saved]"), _xlpm._rtn, IF(OR(ISERROR(_xlpm._wsName), _xlpm._wsName = "#"), "#[Error reading Sheet name]", _xlpm._wsName), IF(_xlpm._inpChk &lt;&gt; "", _xlpm._inpChk, _xlpm._rtn)))</definedName>
+    <definedName name="RXL_WbInfo.WorkbookName" comment="Returns the Workbook name, with or without the file extension, for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_extension, _xlfn.LET(_xlpm._extChk, AND(NOT(ISLOGICAL(_xlpm.remove_extension)), NOT(ISNUMBER(_xlpm.remove_extension))), _xlpm._fileExt, IF(OR(_xlfn.ISOMITTED(_xlpm.remove_extension), _xlpm._extChk), FALSE, _xlpm.remove_extension), _xlpm._inpChk, IF(NOT(ISREF(_xlpm.cell_ref)), "#[Error: cell reference required]", ""), _xlpm._fileName, CELL("filename", _xlpm.cell_ref), _xlpm._strName, _xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm._fileName, "[", -1, , , "#"), "]", -1, , , "#"), _xlpm._wbName, IF(_xlpm._fileExt, _xlfn.TEXTBEFORE(_xlpm._strName, ".", -1, , , _xlpm._strName), _xlpm._strName), _xlpm._rtn, _xlfn.IFS(_xlpm._fileName = "", "#[Error: Workbook must be saved]", OR(ISERROR(_xlpm._wbName), _xlpm._wbName = "#"), "#[Error reading Workbook name]", TRUE, _xlpm._wbName), IF(_xlpm._inpChk &lt;&gt; "", _xlpm._inpChk, _xlpm._rtn)))</definedName>
+    <definedName name="RXL_WorkbookName" comment="Returns the Workbook name, with or without the file extension, for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_extension, _xlfn.LET(_xlpm._extChk, AND(NOT(ISLOGICAL(_xlpm.remove_extension)), NOT(ISNUMBER(_xlpm.remove_extension))), _xlpm._fileExt, IF(OR(_xlfn.ISOMITTED(_xlpm.remove_extension), _xlpm._extChk), FALSE, _xlpm.remove_extension), _xlpm._inpChk, IF(NOT(ISREF(_xlpm.cell_ref)), "#[Error: cell reference required]", ""), _xlpm._fileName, CELL("filename", _xlpm.cell_ref), _xlpm._strName, _xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm._fileName, "[", -1, , , "#"), "]", -1, , , "#"), _xlpm._wbName, IF(_xlpm._fileExt, _xlfn.TEXTBEFORE(_xlpm._strName, ".", -1, , , _xlpm._strName), _xlpm._strName), _xlpm._rtn, _xlfn.IFS(_xlpm._fileName = "", "#[Error: Workbook must be saved]", OR(ISERROR(_xlpm._wbName), _xlpm._wbName = "#"), "#[Error reading Workbook name]", TRUE, _xlpm._wbName), IF(_xlpm._inpChk &lt;&gt; "", _xlpm._inpChk, _xlpm._rtn)))</definedName>
     <definedName name="RXL_WorkbookName_Alt" comment="Returns the Workbook name, with or without the file extension, for the cell reference provided; Workbook must be saved first">_xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_extension,_xlfn.LET(_xlpm._inpChk,IF(NOT(ISREF(_xlpm.cell_ref)),"#[Error: cell reference required]",""),_xlpm._extChk,AND(NOT(ISLOGICAL(_xlpm.remove_extension)),NOT(ISNUMBER(_xlpm.remove_extension))),_xlpm._fileExt,IF(OR(_xlfn.ISOMITTED(_xlpm.remove_extension),_xlpm._extChk),FALSE,_xlpm.remove_extension),_xlpm._fileName,CELL("filename",_xlpm.cell_ref),_xlpm._posR,IFERROR(FIND("?",SUBSTITUTE(_xlpm._fileName,"]","?",LEN(_xlpm._fileName)-LEN(SUBSTITUTE(_xlpm._fileName,"]","")))),0),_xlpm._str,IF(_xlpm._posR&gt;0,LEFT(_xlpm._fileName,_xlpm._posR-1),"#"),_xlpm._posL,IFERROR(FIND("?",SUBSTITUTE(_xlpm._str,"[","?",LEN(_xlpm._str)-LEN(SUBSTITUTE(_xlpm._str,"[","")))),0),_xlpm._strName,IF(_xlpm._posL&gt;0,RIGHT(_xlpm._str,LEN(_xlpm._str)-_xlpm._posL),"#"),_xlpm._posX,IF(_xlpm._fileExt,IFERROR(FIND("?",SUBSTITUTE(_xlpm._strName,".","?",LEN(_xlpm._strName)-LEN(SUBSTITUTE(_xlpm._strName,".",""))))-1,0),0),_xlpm._wbName,IF(_xlpm._posX&gt;0,LEFT(_xlpm._strName,_xlpm._posX),_xlpm._strName),_xlpm._rtn,IF(_xlpm._wbName="#","#[Error reading Workbook name]",_xlpm._wbName),IF(_xlpm._inpChk&lt;&gt;"",_xlpm._inpChk,_xlpm._rtn)))</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="autoNoTable"/>
@@ -72,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="244">
   <si>
     <t>)</t>
   </si>
@@ -630,6 +635,842 @@
   </si>
   <si>
     <t>Workbook Information Module</t>
+  </si>
+  <si>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <t>VBA Code</t>
+  </si>
+  <si>
+    <t>A.</t>
+  </si>
+  <si>
+    <t>Start by ensuring that you have this Workbook and the Workbook you wish to copy the function to open in the same Excel instance</t>
+  </si>
+  <si>
+    <t>B.</t>
+  </si>
+  <si>
+    <t>Open the VB Editor window</t>
+  </si>
+  <si>
+    <t>C.</t>
+  </si>
+  <si>
+    <t>D.</t>
+  </si>
+  <si>
+    <t>In the code window which opens for ThisWorkbook, paste the VBA code from below exactly as written</t>
+  </si>
+  <si>
+    <t>E.</t>
+  </si>
+  <si>
+    <t>F.</t>
+  </si>
+  <si>
+    <t>Run the CopyLambda sub routine in ThisWorkbook module and check the Immediate window for the feedback message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    On Error Resume Next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        'Update "Example.xlsx" with name of the Workbook you wish to copy the function to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Exit Sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    End If</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Else</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        End If</t>
+  </si>
+  <si>
+    <t>End Sub</t>
+  </si>
+  <si>
+    <t>In order to copy across the RXL_WbInfo() module from this Workbook to your own project you can use the instructions and VBA code below .</t>
+  </si>
+  <si>
+    <t>In the VB Editor Project Explorer window, select this Workbook (RXL_WbInfo.xlsx) and double click on the object named "ThisWorkbook"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' Defining the module base name and individual function Names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' Creates the list of custom Lambda function to copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        arrFuncs = Split(STR_FUNC, "|")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        strLambda = STR_MDL &amp; "." &amp; arrFuncs(i)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        On Error Resume Next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Err.Clear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                  RefersTo:=nm.RefersTo, _</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                  Visible:=nm.Visible)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                fn.Comment = nm.Comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Else</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            End If</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Exit Sub</t>
+  </si>
+  <si>
+    <t>ErrHndlr:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Private Sub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CopyLambda()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> wb </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Workbook, nm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Name, fn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> strLambda </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As String</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, arrFuncs() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As String</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> i </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As Long</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> STR_MDL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As String</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = "RXL_WbInfo"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> STR_FUNC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As String</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = "About|FilePath|SheetName|WorkbookName"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>On Error GoTo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ErrHndlr</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> wb = Application.Workbooks("Example.xlsx")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>On Error GoTo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>If</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> wb </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Is Nothing Then</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: Destination Workbook not found - please ensure it is open"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>For</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> i = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>LBound</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(arrFuncs) To </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>UBound</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(arrFuncs)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> nm = ThisWorkbook.Names(strLambda)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>If Not</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> nm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Is Nothing Then</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> fn = wb.Names.Add(Name:=nm.Name, _</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>If</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Err.Number = 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Then</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "Success! -&gt; " &amp; strLambda &amp; " copied to " &amp; wb.Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: Unable to copy " &amp; strLambda &amp; " to " &amp; wb.Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: " &amp; strLambda &amp; " not found"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Next</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> i</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: Unable to correctly handle expected module function names"</t>
+    </r>
+  </si>
+  <si>
+    <t>After copying the VBA code into code window, update line 16 replacing the text "Example.xlsx" with the name of your Excel Workbook/file</t>
   </si>
 </sst>
 </file>
@@ -646,7 +1487,7 @@
     <numFmt numFmtId="170" formatCode="&quot;On (1)&quot;;[Red]&quot;Err&quot;;&quot;Off (0)&quot;"/>
     <numFmt numFmtId="171" formatCode="&quot;Yes (1)&quot;;[Red]&quot;Err&quot;;&quot;No (0)&quot;"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="43" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF002138"/>
@@ -960,8 +1801,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1114,12 +1960,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEE6CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1520,10 +2360,10 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="30" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1538,15 +2378,15 @@
     <xf numFmtId="165" fontId="24" fillId="0" borderId="0" applyFill="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="10" applyAlignment="0"/>
-    <xf numFmtId="166" fontId="27" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="10" applyAlignment="0"/>
+    <xf numFmtId="166" fontId="27" fillId="35" borderId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="20" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="13" fillId="41" borderId="10"/>
-    <xf numFmtId="166" fontId="13" fillId="41" borderId="12" applyNumberFormat="0"/>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="20" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="13" fillId="40" borderId="10"/>
+    <xf numFmtId="166" fontId="13" fillId="40" borderId="12" applyNumberFormat="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1586,22 +2426,22 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="13" applyFill="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" applyAlignment="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="10" applyAlignment="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" applyAlignment="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="10" applyAlignment="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" applyAlignment="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="10" applyAlignment="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" applyAlignment="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="10" applyAlignment="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="38" borderId="0">
+    <xf numFmtId="166" fontId="28" fillId="37" borderId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFill="0" applyAlignment="0"/>
@@ -1611,13 +2451,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyFill="0" applyAlignment="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="19"/>
-    <xf numFmtId="0" fontId="13" fillId="41" borderId="10"/>
+    <xf numFmtId="0" fontId="13" fillId="40" borderId="10"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="25" fillId="34" borderId="10" applyAlignment="0">
+    <xf numFmtId="166" fontId="25" fillId="33" borderId="10" applyAlignment="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="37" borderId="0">
+    <xf numFmtId="166" fontId="27" fillId="36" borderId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
@@ -1631,15 +2471,15 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="10" applyAlignment="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="11" applyNumberFormat="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="10" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="13" fillId="39" borderId="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="38" borderId="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="41" borderId="11" applyNumberFormat="0"/>
+    <xf numFmtId="166" fontId="13" fillId="40" borderId="11" applyNumberFormat="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="14" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="14" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="89" applyAlignment="1"/>
@@ -1652,7 +2492,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="30"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="14" xfId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="14" xfId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="58">
@@ -1672,34 +2512,33 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="71"/>
     <xf numFmtId="169" fontId="34" fillId="0" borderId="19" xfId="71" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="17" xfId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="17" xfId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="17" xfId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="17" xfId="10" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="28" borderId="8" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="16" fillId="35" borderId="10" xfId="23" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="16" fillId="35" borderId="10" xfId="23" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="16" fillId="34" borderId="10" xfId="23" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="16" fillId="34" borderId="10" xfId="23" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="21" xfId="49" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="14" xfId="7" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="14" xfId="7" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="17" xfId="10"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="17" xfId="10"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="22" xfId="49" applyBorder="1"/>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="23" xfId="49" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="17" xfId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="17" xfId="10" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="16" fillId="33" borderId="10" xfId="59" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="16" fillId="32" borderId="10" xfId="59" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1708,6 +2547,9 @@
     </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="21" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="73"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="91">
     <cellStyle name="20% - Accent1" xfId="31" builtinId="30" customBuiltin="1"/>
@@ -1779,7 +2621,7 @@
     <cellStyle name="Output - SubTotal" xfId="68" xr:uid="{3944BA35-D861-48C8-BF5E-3B5A261E1A76}"/>
     <cellStyle name="Output - Text" xfId="69" xr:uid="{D8AED5B9-3D8F-49BF-8E7D-B2C435B0B345}"/>
     <cellStyle name="Output - Total" xfId="70" xr:uid="{4535EB24-0E67-4CEB-99CB-25A662CC9E57}"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Per cent" xfId="5" builtinId="5" customBuiltin="1"/>
     <cellStyle name="Ref.In - #" xfId="78" xr:uid="{7AC7FA44-CE33-4D97-A9FF-6DB2BE2FBF7C}"/>
     <cellStyle name="Ref.In - %" xfId="79" xr:uid="{BE627C07-1DF5-42CE-90A7-95B617354C42}"/>
     <cellStyle name="Ref.In - Date" xfId="80" xr:uid="{70FB18BE-2731-4B77-8479-BF1A1A35C14E}"/>
@@ -1807,6 +2649,7 @@
   <colors>
     <mruColors>
       <color rgb="FF1E4FA8"/>
+      <color rgb="FF3F9C35"/>
       <color rgb="FF0000FF"/>
       <color rgb="FF00153D"/>
       <color rgb="FF009CDE"/>
@@ -2044,6 +2887,237 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>355542</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="A black and white logo&#10;&#10;AI-generated content may be incorrect.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3066911B-2BC0-4069-98DD-45732B3141EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="38100"/>
+          <a:ext cx="609600" cy="317442"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>555206</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47365</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEC536C5-4537-43BD-C39F-EC57DFAA5A26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="1516380"/>
+          <a:ext cx="5432006" cy="1396105"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>526364</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>53802</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2460CF6-63D3-2B3B-0F28-D4852C1BD7DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="3284220"/>
+          <a:ext cx="4183964" cy="3315162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>435678</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>31013</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B079E71-9FDA-02B9-4FBB-A23FCBEFAE8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594361" y="7139940"/>
+          <a:ext cx="9579677" cy="3818153"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>526195</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>45811</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B091A4D-15A7-2FB6-00F8-742D889D1883}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="11323320"/>
+          <a:ext cx="4793395" cy="1051651"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2370,7 +3444,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="976" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="9">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2404,18 +3478,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458C7317-EEEF-4D0C-A570-5CBA36EE881D}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:W86"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27"/>
+    <row r="1" spans="1:13" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26"/>
       <c r="C1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="18" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" s="18" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="19">
         <f xml:space="preserve"> MAX(B$1:B1) + 1</f>
         <v>1</v>
@@ -2424,35 +3498,35 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C11" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="C11" ca="1" xml:space="preserve"> CELL("filename", $C$1)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\[RXL_WbInfo.xlsx]SheetName</v>
+        <v>D:\Work\_RXL\Development\LAMBDA\[RXL_WbInfo.xlsx]SheetName</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
@@ -2465,18 +3539,18 @@
       <c r="L11" s="12"/>
       <c r="M11" s="10"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C12" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C11)</f>
         <v>= CELL("filename", $C$1)</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C15" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="C15" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm._fileName, CELL("filename", $C$1),
@@ -2490,7 +3564,7 @@
       <c r="E15" s="12"/>
       <c r="F15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C16" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C15)</f>
         <v>= LET(
@@ -2501,12 +3575,12 @@
 )</v>
       </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C19" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="C19" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm._fileName, CELL("filename", $C$1),
@@ -2520,7 +3594,7 @@
       <c r="E19" s="12"/>
       <c r="F19" s="10"/>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C20" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C19)</f>
         <v>= LET(
@@ -2531,7 +3605,7 @@
 )</v>
       </c>
     </row>
-    <row r="23" spans="2:23" s="18" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:23" s="18" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="19">
         <f xml:space="preserve"> MAX(B$1:B22) + 1</f>
         <v>2</v>
@@ -2540,7 +3614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B25" s="21" t="s">
         <v>42</v>
       </c>
@@ -2566,8 +3640,8 @@
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C27" s="25" t="str" cm="1">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C27" s="24" t="str" cm="1">
         <f t="array" aca="1" ref="C27" ca="1" xml:space="preserve"> _xlfn.LAMBDA(_xlpm.cell_ref,
   _xlfn.LET(
     _xlpm._inpChk, IF( NOT(ISREF(_xlpm.cell_ref)), "#[Error: cell reference required]", ""),
@@ -2583,7 +3657,7 @@
       <c r="E27" s="12"/>
       <c r="F27" s="10"/>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C28" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C27)</f>
         <v>= LAMBDA(cell_ref,
@@ -2597,110 +3671,110 @@
 )($C$1)</v>
       </c>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C29" s="7"/>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C30" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C31" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C32" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C34" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C35" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C36" s="17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C37" s="16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C38" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C39" s="16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C40" s="16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C41" s="17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C42" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C43" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C44" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C45" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C46" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C47" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C49" s="26" t="s">
+    <row r="49" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C49" s="25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C50" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B53" s="21" t="s">
         <v>34</v>
       </c>
@@ -2726,8 +3800,8 @@
       <c r="V53" s="20"/>
       <c r="W53" s="20"/>
     </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C55" s="22" t="str" cm="1">
+    <row r="55" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C55" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="C55" ca="1" xml:space="preserve"> _xlfn.LAMBDA(_xlpm.cell_ref,
   _xlfn.LET(
     _xlpm._inpChk, IF( NOT(ISREF(_xlpm.cell_ref)), "#[Error: cell reference required]", ""),
@@ -2744,7 +3818,7 @@
       <c r="E55" s="12"/>
       <c r="F55" s="10"/>
     </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C56" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C55)</f>
         <v>= LAMBDA(cell_ref,
@@ -2759,139 +3833,139 @@
 )($C$1)</v>
       </c>
     </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C57" s="7"/>
     </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B58" s="7"/>
       <c r="C58" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B59" s="7"/>
       <c r="C59" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B60" s="7"/>
       <c r="C60" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C61" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C62" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C63" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C64" s="17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C65" s="16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C66" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C67" s="16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C68" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C69" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C70" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C71" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C72" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C73" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C74" s="17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C75" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C76" s="17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C77" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C78" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C79" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C80" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C82" s="26" t="s">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C82" s="25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C83" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="85" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:3" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="86" spans="2:3" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B86" s="9" t="s">
         <v>3</v>
       </c>
@@ -2905,19 +3979,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03EFA570-26D2-439D-9DA6-A95E85759345}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:W126"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27"/>
+    <row r="1" spans="1:13" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26"/>
       <c r="C1" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="18" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" s="18" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="19">
         <f xml:space="preserve"> MAX(B$1:B1) + 1</f>
         <v>1</v>
@@ -2926,40 +4001,40 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C12" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="C12" ca="1" xml:space="preserve"> CELL("filename", $A$1)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\[RXL_WbInfo.xlsx]WorkbookName</v>
+        <v>D:\Work\_RXL\Development\LAMBDA\[RXL_WbInfo.xlsx]WorkbookName</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -2972,18 +4047,18 @@
       <c r="L12" s="12"/>
       <c r="M12" s="10"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C13" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C12)</f>
         <v>= CELL("filename", $A$1)</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C16" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="C16" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm.cell_ref, $A$1,
@@ -2998,7 +4073,7 @@
       <c r="E16" s="12"/>
       <c r="F16" s="10"/>
     </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C17" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C16)</f>
         <v>= LET(
@@ -3010,18 +4085,18 @@
 )</v>
       </c>
     </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="34" t="s">
+      <c r="G19" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C20" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="C20" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm.cell_ref, $A$1,
@@ -3038,7 +4113,7 @@
       <c r="E20" s="12"/>
       <c r="F20" s="10"/>
     </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C21" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C20)</f>
         <v>= LET(
@@ -3052,13 +4127,13 @@
 )</v>
       </c>
     </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C25" s="25" t="str" cm="1">
+    <row r="25" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C25" s="24" t="str" cm="1">
         <f t="array" aca="1" ref="C25" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm.cell_ref, $A$1,
   _xlpm._fileName, CELL("filename", _xlpm.cell_ref),
@@ -3071,11 +4146,11 @@
 )</f>
         <v>RXL_WbInfo.xlsx</v>
       </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
-    </row>
-    <row r="26" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
+    </row>
+    <row r="26" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C26" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C25)</f>
         <v>= LET(
@@ -3090,19 +4165,19 @@
 )</v>
       </c>
     </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="34" t="s">
+      <c r="G28" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="H28" s="35">
+      <c r="H28" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C29" s="25" t="str" cm="1">
+    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C29" s="24" t="str" cm="1">
         <f t="array" aca="1" ref="C29" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm.cell_ref, $A$1,
   _xlpm.remove_extension, $H$28,
@@ -3118,11 +4193,11 @@
 )</f>
         <v>RXL_WbInfo</v>
       </c>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="32"/>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="31"/>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C30" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C29)</f>
         <v>= LET(
@@ -3140,7 +4215,7 @@
 )</v>
       </c>
     </row>
-    <row r="33" spans="2:23" s="18" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:23" s="18" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="19">
         <f xml:space="preserve"> MAX(B$1:B32) + 1</f>
         <v>2</v>
@@ -3149,7 +4224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B35" s="21" t="s">
         <v>42</v>
       </c>
@@ -3175,8 +4250,8 @@
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C37" s="25" t="str" cm="1">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C37" s="24" t="str" cm="1">
         <f t="array" aca="1" ref="C37" ca="1" xml:space="preserve"> _xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_extension,
   _xlfn.LET(
     _xlpm._extChk, AND( NOT(ISLOGICAL(_xlpm.remove_extension)), NOT(ISNUMBER(_xlpm.remove_extension))),
@@ -3210,7 +4285,7 @@
       <c r="E37" s="12"/>
       <c r="F37" s="10"/>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C38" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C37)</f>
         <v>= LAMBDA(cell_ref,[remove_extension],
@@ -3242,215 +4317,215 @@
 )($A$1)</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C39" s="7"/>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C40" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C41" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C42" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C43" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C44" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C45" s="17" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C46" s="16" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C47" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C48" s="17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C49" s="36" t="s">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C49" s="35" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C50" s="36" t="s">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="35" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C51" s="36" t="s">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C52" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C53" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C54" s="17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C55" s="36" t="s">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C55" s="35" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C56" s="36" t="s">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C56" s="35" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C57" s="36" t="s">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C57" s="35" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C58" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C59" s="16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C60" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C61" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C62" s="17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C63" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C64" s="17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C65" s="36" t="s">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C66" s="36" t="s">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C66" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C67" s="36" t="s">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C67" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C68" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C69" s="16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C70" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C71" s="36" t="s">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C71" s="35" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C72" s="36" t="s">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C72" s="35" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C73" s="36" t="s">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C73" s="35" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C74" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C75" s="16" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C76" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C77" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C78" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C80" s="26" t="s">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C80" s="25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C81" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B84" s="21" t="s">
         <v>34</v>
       </c>
@@ -3476,7 +4551,7 @@
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C86" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="C86" ca="1" xml:space="preserve"> _xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_extension,
   _xlfn.LET(
@@ -3503,7 +4578,7 @@
       <c r="E86" s="12"/>
       <c r="F86" s="10"/>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C87" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C86)</f>
         <v>= LAMBDA(cell_ref,[remove_extension],
@@ -3527,193 +4602,193 @@
 )($A$1)</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C88" s="7"/>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B89" s="7"/>
       <c r="C89" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B90" s="7"/>
       <c r="C90" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B91" s="7"/>
       <c r="C91" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B92" s="7"/>
       <c r="C92" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B93" s="7"/>
       <c r="C93" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B94" s="7"/>
       <c r="C94" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B95" s="7"/>
       <c r="C95" s="16" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B96" s="7"/>
       <c r="C96" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B97" s="7"/>
       <c r="C97" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B98" s="7"/>
       <c r="C98" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99" s="7"/>
       <c r="C99" s="17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100" s="7"/>
       <c r="C100" s="16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C101" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C102" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C103" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C104" s="16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C105" s="16" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C106" s="17" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C107" s="17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C108" s="16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C109" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C110" s="17" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C111" s="16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C112" s="17" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C113" s="16" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C114" s="17" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C115" s="16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C116" s="17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C117" s="16" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C118" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C119" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C120" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C122" s="26" t="s">
+    <row r="122" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C122" s="25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C123" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="125" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="2:3" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="126" spans="2:3" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B126" s="9" t="s">
         <v>3</v>
       </c>
@@ -3732,19 +4807,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E385043E-C3E2-4C03-A268-335FAF038F1D}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:W168"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27"/>
+    <row r="1" spans="1:13" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26"/>
       <c r="C1" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="18" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" s="18" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="19">
         <f xml:space="preserve"> MAX(B$1:B1) + 1</f>
         <v>1</v>
@@ -3753,65 +4829,65 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C12" s="25" t="str" cm="1">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C12" s="24" t="str" cm="1">
         <f t="array" aca="1" ref="C12" ca="1" xml:space="preserve"> CELL("filename", $A$1)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\[RXL_WbInfo.xlsx]FilePath</v>
-      </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="32"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+        <v>D:\Work\_RXL\Development\LAMBDA\[RXL_WbInfo.xlsx]FilePath</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="31"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C13" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C12)</f>
         <v>= CELL("filename", $A$1)</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C16" s="37" t="str" cm="1">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="36" t="str" cm="1">
         <f t="array" aca="1" ref="C16" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm.cell_ref, $A$1,
   _xlpm._full, CELL("filename", _xlpm.cell_ref),
@@ -3819,20 +4895,20 @@
   _xlpm._rtn, IF( OR( ISERROR(_xlpm._filePath), _xlpm._filePath = "#"), "#[Error reading File Path]", _xlpm._filePath),
   _xlpm._rtn
 )</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\</v>
-      </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="32"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+        <v>D:\Work\_RXL\Development\LAMBDA\</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="31"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C17" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C16)</f>
         <v>= LET(
@@ -3844,13 +4920,13 @@
 )</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C20" s="37" t="str" cm="1">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C20" s="36" t="str" cm="1">
         <f t="array" aca="1" ref="C20" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm.cell_ref, $A$1,
   _xlpm._full, CELL("filename", _xlpm.cell_ref),
@@ -3863,20 +4939,20 @@
   ),
   _xlpm._rtn
 )</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
-      </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="32"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+        <v>D:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
+      </c>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="31"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C21" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C20)</f>
         <v>= LET(
@@ -3893,30 +4969,30 @@
 )</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>117</v>
       </c>
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>119</v>
       </c>
-      <c r="H24" s="34" t="s">
+      <c r="H24" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C25" s="37" t="str" cm="1">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C25" s="36" t="str" cm="1">
         <f t="array" aca="1" ref="C25" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm.cell_ref, $A$1,
   _xlpm.remove_last_char, I23,
@@ -3933,20 +5009,20 @@
   ),
   _xlpm._rtn
 )</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
-      </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="32"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+        <v>D:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
+      </c>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C26" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C25)</f>
         <v>= LET(
@@ -3967,13 +5043,13 @@
 )</v>
       </c>
     </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C30" s="25" t="str" cm="1">
+    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C30" s="24" t="str" cm="1">
         <f t="array" aca="1" ref="C30" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm.cell_ref, $A$1,
   _xlpm._full, CELL("filename", _xlpm.cell_ref),
@@ -3991,20 +5067,20 @@
   _xlpm._rtn, _xlpm._fPath &amp; _xlpm._wbName,
   IF( _xlpm._errChk &lt;&gt; "", _xlpm._errChk, _xlpm._rtn)
 )</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
-      </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="32"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+        <v>D:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
+      </c>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="31"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C31" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C30)</f>
         <v>= LET(
@@ -4026,27 +5102,27 @@
 )</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>121</v>
       </c>
-      <c r="H33" s="34" t="s">
+      <c r="H33" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="H34" s="34" t="s">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="H34" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C35" s="25" t="str" cm="1">
+    <row r="35" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C35" s="24" t="str" cm="1">
         <f t="array" aca="1" ref="C35" ca="1" xml:space="preserve"> _xlfn.LET(
   _xlpm.cell_ref, $A$1,
   _xlpm.remove_last_char, I33,
@@ -4067,20 +5143,20 @@
   _xlpm._rtn, IF(_xlpm.inc_file_name, _xlpm._fPath &amp; _xlpm._wbName, _xlpm._rPath),
   IF( _xlpm._errChk &lt;&gt; "", _xlpm._errChk, _xlpm._rtn)
 )</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
-      </c>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="32"/>
-    </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
+        <v>D:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
+      </c>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="31"/>
+    </row>
+    <row r="36" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C36" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C35)</f>
         <v>= LET(
@@ -4105,7 +5181,7 @@
 )</v>
       </c>
     </row>
-    <row r="39" spans="2:23" s="18" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:23" s="18" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="19">
         <f xml:space="preserve"> MAX(B$1:B38) + 1</f>
         <v>2</v>
@@ -4114,7 +5190,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B41" s="21" t="s">
         <v>42</v>
       </c>
@@ -4140,8 +5216,8 @@
       <c r="V41" s="20"/>
       <c r="W41" s="20"/>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C43" s="25" t="str" cm="1">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C43" s="24" t="str" cm="1">
         <f t="array" aca="1" ref="C43" ca="1" xml:space="preserve"> _xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_last_char,_xlop.inc_file_name,
   _xlfn.LET(
     _xlpm._chrChk, AND( NOT(_xlfn.ISOMITTED(_xlpm.remove_last_char)), NOT(ISLOGICAL(_xlpm.remove_last_char)), NOT(ISNUMBER(_xlpm.remove_last_char))),
@@ -4178,20 +5254,20 @@
     IF(_xlpm._errChk &lt;&gt; "", _xlpm._errChk, _xlpm._rtn)
   )
 )($A$1)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\</v>
-      </c>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="32"/>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+        <v>D:\Work\_RXL\Development\LAMBDA\</v>
+      </c>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="31"/>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C44" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C43)</f>
         <v>= LAMBDA(cell_ref,[remove_last_char],[inc_file_name],
@@ -4232,270 +5308,270 @@
 )($A$1)</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C45" s="7"/>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C46" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C47" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C48" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C49" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C50" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C51" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C52" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C53" s="16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C54" s="17" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C55" s="17" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C56" s="17" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C57" s="16" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C58" s="17" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C59" s="36" t="s">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C59" s="35" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C60" s="36" t="s">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C60" s="35" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C61" s="36" t="s">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C61" s="35" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C62" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C63" s="17" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C64" s="36" t="s">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C64" s="35" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C65" s="36" t="s">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="35" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C66" s="36" t="s">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C66" s="35" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C67" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C68" s="16" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C69" s="17" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C70" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C71" s="17" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C72" s="17" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C73" s="36" t="s">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C73" s="35" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C74" s="36" t="s">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C74" s="35" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C75" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C76" s="16" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C77" s="17" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C78" s="16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C79" s="16" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C80" s="17" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C81" s="36" t="s">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C81" s="35" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C82" s="36" t="s">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C82" s="35" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C83" s="36" t="s">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C83" s="35" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C84" s="36" t="s">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C84" s="35" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C85" s="36" t="s">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C85" s="35" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C86" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C87" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C88" s="17" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C89" s="36" t="s">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C89" s="35" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C90" s="36" t="s">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C90" s="35" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C91" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C92" s="16" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C93" s="17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C94" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C95" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C97" s="26" t="s">
+    <row r="97" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C97" s="25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="98" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C98" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="101" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B101" s="21" t="s">
         <v>34</v>
       </c>
@@ -4521,8 +5597,8 @@
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
     </row>
-    <row r="103" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C103" s="25" t="str" cm="1">
+    <row r="103" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C103" s="24" t="str" cm="1">
         <f t="array" aca="1" ref="C103" ca="1" xml:space="preserve"> _xlfn.LAMBDA(_xlpm.cell_ref,_xlop.remove_last_char,_xlop.inc_file_name,
   _xlfn.LET(
     _xlpm._chrChk, AND( NOT(_xlfn.ISOMITTED(_xlpm.remove_last_char)), NOT(ISLOGICAL(_xlpm.remove_last_char)), NOT(ISNUMBER(_xlpm.remove_last_char))),
@@ -4563,20 +5639,20 @@
     IF(_xlpm._errChk &lt;&gt; "", _xlpm._errChk, _xlpm._rtn)
   )
 )($A$1)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\</v>
-      </c>
-      <c r="D103" s="31"/>
-      <c r="E103" s="31"/>
-      <c r="F103" s="31"/>
-      <c r="G103" s="31"/>
-      <c r="H103" s="31"/>
-      <c r="I103" s="31"/>
-      <c r="J103" s="31"/>
-      <c r="K103" s="31"/>
-      <c r="L103" s="31"/>
-      <c r="M103" s="32"/>
-    </row>
-    <row r="104" spans="2:23" x14ac:dyDescent="0.2">
+        <v>D:\Work\_RXL\Development\LAMBDA\</v>
+      </c>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="30"/>
+      <c r="H103" s="30"/>
+      <c r="I103" s="30"/>
+      <c r="J103" s="30"/>
+      <c r="K103" s="30"/>
+      <c r="L103" s="30"/>
+      <c r="M103" s="31"/>
+    </row>
+    <row r="104" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C104" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(C103)</f>
         <v>= LAMBDA(cell_ref,[remove_last_char],[inc_file_name],
@@ -4621,325 +5697,325 @@
 )($A$1)</v>
       </c>
     </row>
-    <row r="105" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C105" s="7"/>
     </row>
-    <row r="106" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B106" s="7"/>
       <c r="C106" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B107" s="7"/>
       <c r="C107" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B108" s="7"/>
       <c r="C108" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B109" s="7"/>
       <c r="C109" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="110" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B110" s="7"/>
       <c r="C110" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="111" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B111" s="7"/>
       <c r="C111" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="112" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B112" s="7"/>
       <c r="C112" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B113" s="7"/>
       <c r="C113" s="16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" s="7"/>
       <c r="C114" s="17" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B115" s="7"/>
       <c r="C115" s="17" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B116" s="7"/>
       <c r="C116" s="17" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B117" s="7"/>
       <c r="C117" s="16" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B118" s="7"/>
       <c r="C118" s="17" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B119" s="7"/>
-      <c r="C119" s="36" t="s">
+      <c r="C119" s="35" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B120" s="7"/>
-      <c r="C120" s="36" t="s">
+      <c r="C120" s="35" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B121" s="7"/>
-      <c r="C121" s="36" t="s">
+      <c r="C121" s="35" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B122" s="7"/>
       <c r="C122" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B123" s="7"/>
       <c r="C123" s="17" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B124" s="7"/>
-      <c r="C124" s="36" t="s">
+      <c r="C124" s="35" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C125" s="36" t="s">
+    <row r="125" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C125" s="35" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C126" s="36" t="s">
+    <row r="126" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C126" s="35" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C127" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C128" s="16" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C129" s="17" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C130" s="16" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C131" s="16" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C132" s="16" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C133" s="17" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C134" s="17" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C135" s="17" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C136" s="17" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C137" s="16" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C138" s="17" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C139" s="17" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C140" s="36" t="s">
+    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C140" s="35" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C141" s="36" t="s">
+    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C141" s="35" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C142" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C143" s="16" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C144" s="17" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C145" s="16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="146" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C146" s="16" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="147" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C147" s="17" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C148" s="36" t="s">
+    <row r="148" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C148" s="35" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C149" s="36" t="s">
+    <row r="149" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C149" s="35" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C150" s="36" t="s">
+    <row r="150" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C150" s="35" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C151" s="36" t="s">
+    <row r="151" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C151" s="35" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C152" s="36" t="s">
+    <row r="152" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C152" s="35" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="153" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C153" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C154" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C155" s="17" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C156" s="36" t="s">
+    <row r="156" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C156" s="35" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C157" s="36" t="s">
+    <row r="157" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C157" s="35" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="158" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C158" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="159" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C159" s="16" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="160" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C160" s="17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C161" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C162" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C164" s="26" t="s">
+    <row r="164" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C164" s="25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C165" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="167" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="2:3" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="168" spans="2:3" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B168" s="9" t="s">
         <v>3</v>
       </c>
@@ -4958,18 +6034,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2279EF8F-92FC-40C6-ADC9-06F7A7DDD240}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B1:R69"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="4.28515625" customWidth="1"/>
+    <col min="1" max="3" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:18" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="2:18" s="18" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" s="18" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="19">
         <f xml:space="preserve"> MAX(B$1:B1) + 1</f>
         <v>1</v>
@@ -4978,422 +6055,422 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B4" s="33" t="s">
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B4" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D6" s="28" t="s">
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D6" s="27" t="s">
         <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D7" s="28" t="s">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D7" s="27" t="s">
         <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D8" s="28" t="s">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D8" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="37" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="C10" s="30" t="s">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C10" s="29" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D11" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D11" ca="1" xml:space="preserve"> RXL_SheetName($A$1)</f>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D11" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D11" ca="1" xml:space="preserve"> RXL_WbInfo.SheetName($A$1)</f>
         <v>Demo</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="32"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="31"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D12" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D11)</f>
-        <v>= RXL_SheetName($A$1)</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="C14" s="30" t="s">
+        <v>= RXL_WbInfo.SheetName($A$1)</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C14" s="29" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D15" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D15" ca="1" xml:space="preserve"> RXL_SheetName(Lookups!$A$1)</f>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D15" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D15" ca="1" xml:space="preserve"> RXL_WbInfo.SheetName(Lookups!$A$1)</f>
         <v>Lookups</v>
       </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="32"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="31"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D16" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D15)</f>
-        <v>= RXL_SheetName(Lookups!$A$1)</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B19" s="33" t="s">
+        <v>= RXL_WbInfo.SheetName(Lookups!$A$1)</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B19" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="29"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="29"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D21" s="28" t="s">
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D21" s="27" t="s">
         <v>49</v>
       </c>
       <c r="E21" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D22" s="28" t="s">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D22" s="27" t="s">
         <v>48</v>
       </c>
       <c r="E22" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D23" s="28" t="s">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D23" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="37" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="C25" s="30" t="s">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C25" s="29" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D26" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D26" ca="1" xml:space="preserve"> RXL_WorkbookName($A$1)</f>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D26" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D26" ca="1" xml:space="preserve"> RXL_WbInfo.WorkbookName($A$1)</f>
         <v>RXL_WbInfo.xlsx</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="32"/>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="31"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D27" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D26)</f>
-        <v>= RXL_WorkbookName($A$1)</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="C29" s="30" t="s">
+        <v>= RXL_WbInfo.WorkbookName($A$1)</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C29" s="29" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D30" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D30" ca="1" xml:space="preserve"> RXL_WorkbookName(Lookups!$A$1)</f>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D30" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D30" ca="1" xml:space="preserve"> RXL_WbInfo.WorkbookName(Lookups!$A$1)</f>
         <v>RXL_WbInfo.xlsx</v>
       </c>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="32"/>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="31"/>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D31" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D30)</f>
-        <v>= RXL_WorkbookName(Lookups!$A$1)</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="C33" s="30" t="s">
+        <v>= RXL_WbInfo.WorkbookName(Lookups!$A$1)</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C33" s="29" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D34" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D34" ca="1" xml:space="preserve"> RXL_WorkbookName($A$1, FALSE)</f>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D34" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D34" ca="1" xml:space="preserve"> RXL_WbInfo.WorkbookName($A$1, FALSE)</f>
         <v>RXL_WbInfo.xlsx</v>
       </c>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="32"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="31"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D35" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D34)</f>
-        <v>= RXL_WorkbookName($A$1, FALSE)</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="C37" s="30" t="s">
+        <v>= RXL_WbInfo.WorkbookName($A$1, FALSE)</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C37" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D38" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D38" ca="1" xml:space="preserve"> RXL_WorkbookName($A$1, TRUE)</f>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D38" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D38" ca="1" xml:space="preserve"> RXL_WbInfo.WorkbookName($A$1, TRUE)</f>
         <v>RXL_WbInfo</v>
       </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="32"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="31"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D39" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D38)</f>
-        <v>= RXL_WorkbookName($A$1, TRUE)</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B42" s="33" t="s">
+        <v>= RXL_WbInfo.WorkbookName($A$1, TRUE)</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B42" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D44" s="28" t="s">
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D44" s="27" t="s">
         <v>49</v>
       </c>
       <c r="E44" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D45" s="28" t="s">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D45" s="27" t="s">
         <v>48</v>
       </c>
       <c r="E45" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D46" s="28" t="s">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="D46" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="E46" s="38" t="s">
+      <c r="E46" s="37" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="C48" s="30" t="s">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C48" s="29" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="D49" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D49" ca="1" xml:space="preserve"> RXL_FilePath($A$1)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\</v>
-      </c>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="31"/>
-      <c r="N49" s="32"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D49" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D49" ca="1" xml:space="preserve"> RXL_WbInfo.FilePath($A$1)</f>
+        <v>D:\Work\_RXL\Development\LAMBDA\</v>
+      </c>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="31"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D50" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D49)</f>
-        <v>= RXL_FilePath($A$1)</v>
-      </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="C52" s="30" t="s">
+        <v>= RXL_WbInfo.FilePath($A$1)</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C52" s="29" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="D53" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D53" ca="1" xml:space="preserve"> RXL_FilePath(Lookups!$A$1)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\</v>
-      </c>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="32"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D53" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D53" ca="1" xml:space="preserve"> RXL_WbInfo.FilePath(Lookups!$A$1)</f>
+        <v>D:\Work\_RXL\Development\LAMBDA\</v>
+      </c>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="31"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D54" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D53)</f>
-        <v>= RXL_FilePath(Lookups!$A$1)</v>
-      </c>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="C56" s="30" t="s">
+        <v>= RXL_WbInfo.FilePath(Lookups!$A$1)</v>
+      </c>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C56" s="29" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="D57" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D57" ca="1" xml:space="preserve"> RXL_FilePath($A$1, FALSE)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\</v>
-      </c>
-      <c r="E57" s="31"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="31"/>
-      <c r="I57" s="31"/>
-      <c r="J57" s="31"/>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
-      <c r="N57" s="32"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D57" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D57" ca="1" xml:space="preserve"> RXL_WbInfo.FilePath($A$1, FALSE)</f>
+        <v>D:\Work\_RXL\Development\LAMBDA\</v>
+      </c>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="31"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D58" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D57)</f>
-        <v>= RXL_FilePath($A$1, FALSE)</v>
-      </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="C60" s="30" t="s">
+        <v>= RXL_WbInfo.FilePath($A$1, FALSE)</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C60" s="29" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="D61" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D61" ca="1" xml:space="preserve"> RXL_FilePath($A$1, TRUE)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA</v>
-      </c>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-      <c r="N61" s="32"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D61" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D61" ca="1" xml:space="preserve"> RXL_WbInfo.FilePath($A$1, TRUE)</f>
+        <v>D:\Work\_RXL\Development\LAMBDA</v>
+      </c>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="31"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D62" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D61)</f>
-        <v>= RXL_FilePath($A$1, TRUE)</v>
-      </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
-      <c r="C64" s="30" t="s">
+        <v>= RXL_WbInfo.FilePath($A$1, TRUE)</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C64" s="29" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="D65" s="25" t="str" cm="1">
-        <f t="array" aca="1" ref="D65" ca="1" xml:space="preserve"> RXL_FilePath($A$1, , TRUE)</f>
-        <v>E:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
-      </c>
-      <c r="E65" s="31"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="31"/>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
-      <c r="N65" s="32"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D65" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="D65" ca="1" xml:space="preserve"> RXL_WbInfo.FilePath($A$1, , TRUE)</f>
+        <v>D:\Work\_RXL\Development\LAMBDA\RXL_WbInfo.xlsx</v>
+      </c>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="30"/>
+      <c r="M65" s="30"/>
+      <c r="N65" s="31"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.3">
       <c r="D66" s="6" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D65)</f>
-        <v>= RXL_FilePath($A$1, , TRUE)</v>
-      </c>
-    </row>
-    <row r="68" spans="2:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:14" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>= RXL_WbInfo.FilePath($A$1, , TRUE)</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="69" spans="2:14" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B69" s="9" t="s">
         <v>3</v>
       </c>
@@ -5410,59 +6487,409 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C962E0C9-5BC4-4037-A0C4-2F6DC1820507}">
+  <sheetPr codeName="Sheet13"/>
+  <dimension ref="B1:C126"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" s="18" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="19">
+        <f xml:space="preserve"> MAX(B$1:B1) + 1</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B38" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="C63" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" s="18" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="19">
+        <f xml:space="preserve"> MAX(B$1:B70) + 1</f>
+        <v>2</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C73" s="40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C74" s="40"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C75" s="40" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C76" s="40" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C77" s="40" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C78" s="38" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C79" s="40" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C80" s="40" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C81" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C82" s="38" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C83" s="40" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C84" s="40" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C85" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C86" s="39" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C87" s="38" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C88" s="40" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C89" s="40" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C90" s="40" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C91" s="40" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C92" s="39" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C93" s="39" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C94" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C95" s="40" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C96" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="40" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="40" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C99" s="39" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C100" s="40" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C101" s="40" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="102" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C102" s="40" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="103" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C103" s="40" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="104" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C104" s="40" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="105" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C105" s="40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="106" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C106" s="40" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="107" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C107" s="40" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="108" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C108" s="40" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="109" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C109" s="39" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="110" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C110" s="40" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="111" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C111" s="39" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="112" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C112" s="39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C113" s="40" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C114" s="39" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C115" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C116" s="40" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C117" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C118" s="39" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C119" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C120" s="40" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C121" s="40" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C122" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C123" s="39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="126" spans="2:3" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B126" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F99A15E-3384-4194-A934-E1FDEF2D75BB}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="B1:D10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:4" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="23">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>0</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="23">
         <v>0</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>0</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="22">
         <v>0</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="2:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
         <v>3</v>
       </c>
@@ -5474,7 +6901,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBUAEUAUwBUACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAALQAtAC0AIABUAGUAcwB0ACAAbQBvAGQAdQBsAGUAIAAtAC0ALQBcAG4AIAAgACAAIABSAFMAIAAwADgALwAwADQALwAyADAAMgA0AFwAbgAgACAAIAAgAEEAIAB0AGUAcwB0ACAARQB4AGMAZQBsACAATABhAGIAcwAgAG0AbwBkAHUAbABlACAAXABuACAAIAAgACAAQwByAGUAYQB0AGUAZAAgAGEAcwAgAGEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAGkAbgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAgACAAIAAgACAAIAAgACAAbgBhAG0AZQAgAD0AIABkAGUAZgBpAG4AaQB0AGkAbwBuADsAXABuACoALwBcAG4AXABuAC8AKgAgACAATgBBAE0ARQA6ACAAIAAgACAAIAAgACAAIABBAGIAbwB1AHQAKAApAFwAbgAgACAAIAAgAEEAVQBUAEgATwBSADoAIAAgACAAIAAgACAAUgAuAFMAaQBsAGsAXABuACAAIAAgACAAVgBFAFIAUwBJAE8ATgA6ACAAIAAgACAAIAB2ADEALgAwADAAIAAgACgAMAA4AC8AMAA0AC8AMgAwADIANAApAFwAbgAgACAAIAAgAEQARQBTAEMAUgBJAFAAVABJAE8ATgA6ACAASABlAGwAcABlAHIAIABmAHUAbgBjAHQAaQBvAG4AIAB3AGgAaQBjAGgAIABwAHIAbwB2AGkAZABlAHMAIAB1AHMAZQByAHMAIAB3AGkAdABoACAAaQBuAGYAbwByAG0AYQB0AGkAbwBuACAAYQBiAG8AdQB0ACAAdABoAGUAIABmAHUAbgBjAHQAaQBvAG4AcwAgAGkAbgBjAGwAdQBkAGUAZABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgAgAHQAaABlACAAbQBvAGQAdQBsAGUALgAgAEMAYQBuACAAZQBpAHQAaABlAHIAIABwAHIAbwB2AGkAZABlACAAaABpAGcAaAAtAGwAZQB2AGUAbAAgAGkAbgBmAG8AcgBtAGEAdABpAG8AbgAgAG8AbgAgAHQAaABlACAAbQBvAGQAdQBsAGUAIABhAHMAIABhACAAdwBoAG8AbABlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAHIAIABtAG8AcgBlACAAZABlAHQAYQBpAGwAZQBkACAAbABlAHYAZQBsACAAYQBiAG8AdQB0ACAAYQAgAHMAcABlAGMAaQBmAGkAYwAgAGYAdQBuAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAbQBvAGQAdQBsAGUALgBcAG4AIAAgACAAIABQAEEAUgBBAE0ARQBUAEUAUgBTADoAIAAgAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuACAAIAAgACAAWwBvAHAAdABpAG8AbgBhAGwAXQAgACAAVABoAGUAIABpAG4AZABlAHgAIABuAHUAbQBiAGUAcgAgAG8AcgAgAHMAdAByAGkAbgBnACAAbgBhAG0AZQAgAG8AZgAgAGEAIABmAHUAbgBjAHQAaQBvAG4AIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbQBvAGQAdQBsAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBmACAAbwBtAGkAdAB0AGUAZAAgAHQAaABlACAAaABpAGcAaAAtAGwAZQB2AGUAbAAgAG0AbwBkAHUAbABlACAAaQBuAGYAbwByAG0AYQB0AGkAbwBuACAAaQBzACAAcgBlAHQAdQByAG4AZQBkAC4AXABuACAAIAAgACAARQBSAFIATwBSAEMASABFAEMASwBTADoAIAAoAG4AbwBuAGUAKQBcAG4AKgAvAFwAbgBBAGIAbwB1AHQAIAA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABbAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAXwBuAHUAbQAsACAASQBGACgAIABJAFMATwBNAEkAVABUAEUARAAoAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuACkALAAgADAALAAgAEkARgAoACAASQBTAE4AVQBNAEIARQBSACgAcwBlAGwAZQBjAHQAXwBmAHUAbgBjAHQAaQBvAG4AKQAsACAAcwBlAGwAZQBjAHQAXwBmAHUAbgBjAHQAaQBvAG4ALAAgAC0AMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AYQByAHIARABlAGYALAAgAEkARgAoAF8AbgB1AG0AIAA9ACAAMAAsACAAVABFAFgAVABTAFAATABJAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAYgBvAHUAdAA6AKwAVABlAHMAdAAgAG0AbwBkAHUAbABlACAAYwByAGUAYQB0AGUAZAAgAGkAbgAgAEUAeABjAGUAbAAgAEwAYQBiAHMALgB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAKwAUwB1AGcAZwBlAHMAdABlAGQAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAIAA9ACAAVABFAFMAVAB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAHMAaQBvAG4AOgCsAHYAMQAuADAAMAAgACAAKAAwADgALwAwADQALwAyADAAMgA0ACkAfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHcAbgBlAHIAOgCsAFIAUwBNACAAVQBLACAARgBpAG4AYQBuAGMAaQBhAGwAIABNAG8AZABlAGwAbABpAG4AZwAgAFQAZQBhAG0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAdABoAG8AcgA6AKwAUgAgAFMAaQBsAGsAfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgCsAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARgB1AG4AYwB0AGkAbwBuAKwARABlAHMAYwByAGkAcAB0AGkAbwBuAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMAAgAC0AIABBAGIAbwB1AHQArABQAHIAbwBkAHUAYwBlAHMAIAB0AGgAaQBzACAAdABhAGIAbABlACAAbwBmACAAbQBvAGQAdQBsAGUAIABpAG4AZgBvAHIAbQBhAHQAaQBvAG4AOwAgAHAAcgBvAHYAaQBkAGUAcwAgAGkAbgBmAG8AcgBtAGEAdABpAG8AbgAgAGYAbwByACAAZQBhAGMAaAAgAGYAdQBuAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAbQBvAGQAdQBsAGUALgB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAIAAtACAAQwBFAHIAcgCsAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAIAAtACAARgBsAGEAdAB0AGUAbgCsAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAIAAtACAARgBsAGEAdAB0AGUAbgBfAE0AdQBsAHQAaQBLAGUAeQCsAFsALgAuAC4AXQBcACIALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIArABcACIALAAgAFwAIgB8AFwAIgApACwAIABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AYQByAHIATgBhAG0AZQBzACwAIABUAEUAWABUAFMAUABMAEkAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBFAHIAcgCmAFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbABhAHQAdABlAG4ApgBcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAYQB0AHQAZQBuAF8ATQB1AGwAdABpAEsAZQB5AFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgCmAFwAIgApACwAIABcAG4AIAAgACAAIAAgACAAIAAgAF8AYQByAHIASABlAGwAcAAsACAAVABFAFgAVABTAFAATABJAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQQBNAEUAOgCsAEMARQByAHIAfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAEUAUwBDAFIASQBQAFQASQBPAE4AOgCsAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYARQBSAFMASQBPAE4AOgCsAHYAMQAuADAAMAAgACAAKAAwADgALwAwADQALwAyADAAMgA0ACkAfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEEAUgBBAE0ARQBUAEUAUgBTADoArAB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGUAcgByAG8AcgBfAG4AdQBtAGIAZQByAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAKYAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBBAE0ARQA6AKwARgBsAGEAdAB0AGUAbgB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQARQBTAEMAUgBJAFAAVABJAE8ATgA6AKwAWwAuAC4ALgBdAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBFAFIAUwBJAE8ATgA6AKwAdgAxAC4AMAA0ACAAIAAoADAAOAAvADAANAAvADIAMAAyADQAKQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAQQBSAEEATQBFAFQARQBSAFMAOgCsAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBvAHcAXwBoAGUAYQBkAGUAcgBzAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAcwCsACgAcgBlAHEAdQBpAHIAZQBkACkAIABbAC4ALgAuAF0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBkAGEAdABhAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwCsACgAbwBwAHQAaQBvAG4AYQBsACkAIABbAC4ALgAuAF0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzAKwAKABvAHAAdABpAG8AbgBhAGwAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAKYAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBBAE0ARQA6AKwARgBsAGEAdAB0AGUAbgBfAE0AdQBsAHQAaQBLAGUAeQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQARQBTAEMAUgBJAFAAVABJAE8ATgA6AKwAWwAuAC4ALgBdAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBFAFIAUwBJAE8ATgA6AKwAdgAxAC4AMAA1ACAAIAAoADAAOAAvADAANAAvADIAMAAyADQAKQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAQQBSAEEATQBFAFQARQBSAFMAOgCsAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBvAHcAXwBoAGUAYQBkAGUAcgBzAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAcwCsACgAcgBlAHEAdQBpAHIAZQBkACkAIABbAC4ALgAuAF0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBkAGEAdABhAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwCsACgAbwBwAHQAaQBvAG4AYQBsACkAIABbAC4ALgAuAF0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzAKwAKABvAHAAdABpAG8AbgBhAGwAKQAgAFsALgAuAC4AXQB8AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIApgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwBhAHIAcgBPAHUAdAAsACAASQBGACgAXwBuAHUAbQAgAD0AIAAtADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAF8AaQBkAHgALAAgAFMAVQBNACgAIABTAEUAUQBVAEUATgBDAEUAKAAxACwAIABDAE8AVQBOAFQAQQAoAF8AYQByAHIATgBhAG0AZQBzACkAKQAgACoAIAAoAF8AYQByAHIATgBhAG0AZQBzACAAPQAgAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuACkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAXwBpAGQAeAAgAD4AIAAwACwAIABUAEUAWABUAFMAUABMAEkAVAAoACAASQBOAEQARQBYACgAXwBhAHIAcgBIAGUAbABwACwAIABfAGkAZAB4ACkALAAgAFwAIgCsAFwAIgAsACAAXAAiAHwAXAAiACkALAAgAFwAIgAoAEYAdQBuAGMAdABpAG8AbgAgAG4AYQBtAGUAIABuAG8AdAAgAHIAZQBjAG8AZwBuAGkAcwBlAGQAKQBcACIAKQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAXwBuAHUAbQAgAD4AIAAwACwAIABJAEYARQBSAFIATwBSACgAIABUAEUAWABUAFMAUABMAEkAVAAoACAASQBOAEQARQBYACgAXwBhAHIAcgBIAGUAbABwACwAIABfAG4AdQBtACkALAAgAFwAIgCsAFwAIgAsACAAXAAiAHwAXAAiACkALAAgAFwAIgAoAEYAdQBuAGMAdABpAG8AbgAgAGkAbgBkAGUAeAAgAG4AbwB0ACAAcgBlAGMAbwBnAG4AaQBzAGUAZAApAFwAIgApACwAIABcACIAXAAiACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAXwBhAHIAcgBEAGUAZgAgAD0AIABcACIAXAAiACwAIABfAGEAcgByAE8AdQB0ACwAIABfAGEAcgByAEQAZQBmACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACAAIABOAEEATQBFADoAIAAgACAAIAAgACAAIAAgAEMARQByAHIAKAApAFwAbgAgACAAIAAgAEEAVQBUAEgATwBSADoAIAAgACAAIAAgACAAUgAuAFMAaQBsAGsAXABuACAAIAAgACAAVgBFAFIAUwBJAE8ATgA6ACAAIAAgACAAIAB2ADEALgAwADAAIAAgACgAMAA4AC8AMAA0AC8AMgAwADIANAApAFwAbgAgACAAIAAgAEQARQBTAEMAUgBJAFAAVABJAE8ATgA6ACAASABlAGwAcABlAHIAIABMAEEATQBCAEQAQQAgAGYAdQBuAGMAdABpAG8AbgAgAHcAaABpAGMAaAAgAGMAYQBuACAAYgBlACAAdQBzAGUAZAAgAHQAbwAgAHIAZQB0AHUAcgBuACAAYQAgAHMAcABlAGMAaQBmAGkAYwAvAGMAaABvAHMAZQBuACAARQB4AGMAZQBsACAAZQByAHIAbwByACAAYwBvAGQAZQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgB5ACAAcgBlAHQAdQByAG4AaQBuAGcAIABhAG4AIABFAHgAYwBlAGwAIABlAHIAcgBvAHIAIABjAG8AZABlACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAYQAgAGMAdQBzAHQAbwBtAGUAIABlAHIAcgBvAHIAIABjAG8AZABlACwAIAB0AGgAZQAgAGMAZQBsAGwAIABpAHMAIABtAGEAcgBrAGUAZAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBzACAAYQBuACAAZQByAHIAbwByACAAYgB5ACAARQB4AGMAZQBsACAAaQB0AHMAZQBsAGYALAAgAHcAaQBsAGwAIABiAGUAIABwAGkAYwBrAGUAZAAgAHUAcAAgAG8AdABoAGUAcgAgAGEAZABkAC0AaQBuAHMAIABhAG4AZAAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdwBoAGUAbgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQB1AGQAaQB0AGkAbgBnACAAZgBvAHIAIABlAHIAcgBvAHIAcwAsACAAZQB0AGMALgBcAG4AIAAgACAAIABQAEEAUgBBAE0ARQBUAEUAUgBTADoAIAAgAGUAcgByAG8AcgBfAG4AdQBtAGIAZQByACAAIAAgAFsAcgBlAHEAdQBpAHIAZQBkAF0AIAAgAFQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIAB0AGgAZQAgAEUAeABjAGUAbAAgAGYAbwByAG0AdQBsAGEAIABlAHIAcgBvAHIAIAB5AG8AdQAgAHcAaQBzAGgAIAB0AG8AIAByAGUAdAB1AHIAbgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQB1AHMAdAAgAGIAZQAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAIABpAG4AIAB0AGgAZQAgAHIAYQBuAGcAZQAgADAALQB0AG8ALQAxADQALgBcAG4AIAAgACAAIABFAFIAUgBPAFIAQwBIAEUAQwBLAFMAOgAgACgAbgBvAG4AZQApAFwAbgAqAC8AXABuAEMARQByAHIAIAA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAcgBhAG0AZQB0AGUAcgAgAGQAZQBjAGwAYQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgAGUAcgByAG8AcgBfAG4AdQBtAGIAZQByACwAXABuACAAIAAgACAALwAvACAATQBhAGkAbgAgAHAAcgBvAGMAZQBkAHUAcgBlAFwAbgAgACAAIAAgAEwARQBUACgAZQAsACAAZQByAHIAbwByAF8AbgB1AG0AYgBlAHIALAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBoAGUAYwBrACAAaQBuAHAAdQB0AHMAIAAtACAAaQBuAGkAdABpAGEAbABsAHkAIABjAGgAZQBjAGsAIABmAG8AcgAgAGEAIAB2AGEAbABpAGQAIABpAG4AcAB1AHQAIAB0AHkAcABlACAAPQA+ACAAbgB1AG0AZQByAGkAYwAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoACAATgBPAFQAKAAgAEkAUwBOAFUATQBCAEUAUgAoAGUAKQApACwAIABcACIASQBuAHYAYQBsAGkAZAAgAGUAcgByAG8AcgAgAG4AdQBtAGIAZQByACEAXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBoAGUAYwBrACAAaQBuAHAAdQB0AHMAIAAtACAAaQBmACAAbgB1AG0AZQByAGkAYwAgAGkAbgBwAHUAdAAsACAAYwBoAGUAYwBrACAAaQB0ACAAaQBzACAAdwBpAHQAaABpAG4AIABlAHgAcABlAGMAdABlAGQAIAByAGEAbgBnAGUAIABhAG4AZAAgAG8AZgAgAHIAZQBxAHUAaQByAGUAZAAgAHQAeQBwAGUAIAA9AD4AIABpAG4AdABlAGcAZQByAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAAgAE8AUgAoAGUAIAA8ACAAMAAsACAAZQAgAD4AIAAxADQALAAgAE0ATwBEACgAZQAsACAAMQApACAAPAA+ACAAMAApACwAIABcACIASQBuAHYAYQBsAGkAZAAgAGUAcgByAG8AcgAgAG4AdQBtAGIAZQByACEAXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAIABpAGYAIABzAHUAcABwAG8AcgB0AGUAZAAgAGUAcgByAG8AcgAgAG4AdQBtAGIAZQByAC8AdAB5AHAAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAAgAEkAUwBFAFIAUgBPAFIAKAAgAE0AQQBUAEMASAAoAGUALAAgAHsAMQAsADIALAAzACwANAAsADUALAA2ACwANwAsADgALAAxADMALAAxADQAfQAsADAAKQApACwAIABcACIATgBvAHQAIABzAHUAcABwAG8AcgB0AGUAZAAhAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAHIAZQBxAHUAaQByAGUAZAAgAEUAeABjAGUAbAAgAGUAcgByAG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHAAYQBzAHMAZQBkACAAZQByAHIAbwByACAAbgB1AG0AYgBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQAoAGUALAAgACMATgBVAEwATAAhACwAIAAjAEQASQBWAC8AMAAhACwAIAAjAFYAQQBMAFUARQAhACwAQwBhAHMAdABFAHIAcgBvAHIAIQAjAFIARQBGACEALAAgACMATgBBAE0ARQA/ACwAIAAjAE4AVQBNACEALAAgACMATgAvAEEALAAgACMARwBFAFQAVABJAE4ARwBfAEQAQQBUAEEALAAsACwALAAsACAASQBOAEQASQBSAEUAQwBUACgAXAAiAFwAIgApAC4AYQAsACAATABBAE0AQgBEAEEAKABcACIAXAAiACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAIAAgAE4AQQBNAEUAOgAgACAAIAAgACAAIAAgACAARgBsAGEAdAB0AGUAbgAoACkAXABuACAAIAAgACAAQQBVAFQASABPAFIAOgAgACAAIAAgACAAIABSAC4AUwBpAGwAawBcAG4AIAAgACAAIABWAEUAUgBTAEkATwBOADoAIAAgACAAIAAgAHYAMQAuADAANAAgACAAKAAwADgALwAwADQALwAyADAAMgA0ACkAXABuACAAIAAgACAARABFAFMAQwBSAEkAUABUAEkATwBOADoAIABGAHUAbABsAC0AZgB1AG4AYwB0AGkAbwBuAGEAbABpAHQAeQAgAHYAZQByAHMAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGYAbABhAHQALQBmAGkAbABlACAATABhAG0AYgBkAGEAIABmAHUAbgBjAHQAaQBvAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAZABlAGEAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgBhAGwAaQB0AHkAIABvAGYAIAB0AGgAZQAgAEcAbwBvAGcAbABlACAAUwBoAGUAZQB0AHMAIABGAEwAQQBUAFQARQBOACgAKQAgAGYAdQBuAGMAdABpAG8AbgAgAGEAbgBkACAAdABoAGUAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAbAB0AGUAcgB5AHgAIABUAHIAYQBuAHMAcABvAHMAZQAgAHQAbwBvAGwAIAAtACAAYwBvAG4AdgBlAHIAdAAgAGEAIAAyAEQAIAB0AGEAYgBsAGUAIABpAG4AdABvACAAdgBlAHIAdABpAGMAYQBsACAAZgBsAGEAdAAtAGYAaQBsAGUAIAB3AGkAdABoACAAYQAgAGsAZQB5ACAAYwBvAGwAdQBtAG4AIAAoAHIAbwB3ACAAdABpAHQAbABlAHMAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGEAbQBlAHMAIABjAG8AbAB1AG0AbgAgACgAcgBvAHcAIABoAGUAYQBkAGUAcgBzACkALAAgAGEAbgBkACAAdgBhAGwAdQBlAHMAIABjAG8AbAB1AG0AbgAgACgAbQBhAGkAbgAgAHQAYQBiAGwAZQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwApAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAEwAYQBtAGIAZABhACAAYwByAGUAYQB0AGUAcwAgAGEAIAB0AGgAZQAgAGwAaQBzAHQAIABvAGYAIAByAG8AdwAgAGEAbgBkACAAYwBvAGwAdQBtAG4AIABoAGUAYQBkAGUAcgBzACAAaQBuACAAdABoAGUAIABzAHQAeQBsAGUAIABvAGYAIABhACAAQwBhAHIAdABlAHMAaQBhAG4AIABqAG8AaQBuACAAYQBuAGQAIABkAGkAcwBwAGwAYQB5AHMAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAaABpAHMAIABhAHMAIAB0AHcAbwAgAG8AcgBkAGUAcgBlAGQAIABjAG8AbAB1AG0AbgBzAC8AZgBpAGUAbABkAHMALgAgAFQAaABlACAAdgBhAGwAdQBlAHMAIABjAG8AbAB1AG0AbgAgAGEAbABvAG4AZwAgAHMAaQBkAGUAIAB0AGgAZQBzAGUAIAB1AHMAZQAgAGEAbgAgAEkATgBEAEUAWAAtAFgATQBBAFQAQwBIACgAKQAgAGEAcABwAHIAbwBhAGMAaAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABvACAAcABpAGMAawBpAG4AZwAtAHUAcAAgAHQAaABlACAAZABhAHQAYQAgAHAAbwBpAG4AdAAgAHYAYQBsAHUAZQAgAHcAaABpAGMAaAAgAGMAbwByAHIAZQBzAHAAbwBuAGQAcwAgAHQAbwAgAHQAaABlACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuACAAbwBmACAAawBlAHkAIABhAG4AZAAgAG4AYQBtAGUAIABjAG8AbAB1AG0AbgBzAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQByAGUAIABhAHIAZQAgAHQAdwBvACAAbwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwAgAGEAbABsAG8AdwBpAG4AZwAgAGYAbwByACAAZQBpAHQAaABlAHIAIAB0AGgAZQAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAAgAG8AZgAgAGEAbgB5ACAAYgBsAGEAbgBrAC8AZQBtAHAAdAB5ACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAdAB1AHIAbgBlAGQAIAB3AGkAdABoACAAYQAgAHUAcwBlAHIAIABzAHAAZQBjAGkAZgBpAGUAZAAgAHYAYQBsAHUAZQAgACgAYwBhAG4AIABiAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAG4AdQBtAGUAcgBpAGMAKQAsACAAbwByACAAYQBsAGwAbwB3ACAAZgBvAHIAIABmAGwAaQB0AGUAcgBpAG4AZwAtAG8AdQB0ACAAbwBmACAAYQBuAHkAIAByAG8AdwBzACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAYQAgAGIAbABhAG4AawAvAGUAbQBwAHQAeQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAIAB2AGEAbAB1AGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAaABpAHMAIAB2AGUAcgBzAGkAbwBuACAAbwBmACAAdABoAGUAIABMAGEAbQBiAGQAYQAgAGEAbABzAG8AIABpAG4AYwBsAHUAZABlAHMAIABjAGgAZQBjAGsAaQBuAGcAIABvAGYAIAB0AGgAZQAgAHUAcwBlAHIAIABwAGEAcwBzAGUAZAAgAHAAYQByAGEAbQBlAHQAZQByACAAdgBhAGwAdQBlAHMAIABhAG4AZAAgAHcAaQBsAGwAIABlAGkAdABoAGUAcgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHQAdQByAG4AIABhACAAcABhAHIAdABpAGMAdQBsAGEAcgAgAEUAeABjAGUAbAAgAGUAcgByAG8AcgAgAHQAeQBwAGUAIABvAHIAIAB0AGgAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABvAHUAdABwAHUAdAAgAGEAcgByAGEAeQAgAGQAZQBwAGUAbgBkAGkAbgBnACAAdQBwAG8AbgAgAHQAaABlACAAcwB0AGEAdAB1AHMAIABvAGYAIAB0AGgAZQBzAGUAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBwAHUAdAAgAGMAaABlAGMAawBzAC4AXABuACAAIAAgACAAUABBAFIAQQBNAEUAVABFAFIAUwA6ACAAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMAIAAgACAAIABbAHIAZQBxAHUAaQByAGUAZABdACAAIABSAGEAbgBnAGUAIABvAGYAIABjAGUAbABsAHMAIABpAG4AIABhACAAcwBpAG4AZwBsAGUAIABjAG8AbAB1AG0AbgAgACgAMQArACAAcgBvAHcAcwAsACAAMQAgAGMAbwBsACkAIAB0AGgAYQB0ACAAcAByAG8AdgBpAGQAZQAgAHQAaABlACAAawBlAHkAIABmAGkAZQBsAGQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMAIABbAHIAZQBxAHUAaQByAGUAZABdACAAIABSAGEAbgBnAGUAIABvAGYAIABjAGUAbABsAHMAIABpAG4AIABhACAAcwBpAG4AZwBsAGUAIAByAG8AdwAgACgAMQAgAHIAbwB3ACwAIAAxACsAIABjAG8AbAApACAAdABoAGEAdAAgAHAAcgBvAHYAaQBkAGUAIAB0AGgAZQAgAG4AYQBtAGUAIABmAGkAZQBsAGQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGEAdABhACAAIAAgACAAIAAgACAAIAAgACAAIABbAHIAZQBxAHUAaQByAGUAZABdACAAIABSAGEAbgBnAGUAIABvAGYAIABjAGUAbABsAHMAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAcwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABhAGIAbABlACAAcgBlAHAAcgBlAHMAZQBuAHQAaQBuAGcAIAB0AGgAZQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwAgAHQAbwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBsAGEAdAAgAGYAaQBsAGUAOwAgAGUAeABwAGUAYwB0AGUAZAAgAHQAaABhAHQAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAHcAaQBsAGwAIABtAGEAdABjAGgAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGkAbgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABoAGUAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgAsACAAYQBuAGQAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAYwBvAGwAdQBtAG4AcwAgAHcAaQBsAGwAIABtAGEAdABjAGgAIAB0AGgAZQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACAAcABhAHIAYQBtAGUAdABlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAIABbAG8AcAB0AGkAbwBuAGEAbABdACAAIABTAGkAbgBnAGwAZQAgAHYAYQBsAHUAZQAgAGkAbgBwAHUAdAAgACgAYwBhAG4AIABiAGUAIABuAHUAbQBlAHIAaQBjACwAIABzAHQAcgBpAG4AZwAgAG8AcgAgAHIAZQBmAGUAcgBlAG4AYwBlACkAOwAgAHUAcwBlAGQAIAB0AG8AIAByAGUAcABsAGEAYwBlACAAYQBuAHkAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAbABhAG4AawAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwAgAHcAaQB0AGgAIAB0AGgAZQAgAHUAcwBlAHIAIABwAGEAcwBzAGUAZAAgAHAAYQByAGEAbQBlAHQAZQByAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AbwB0AGUAOgAgAHQAaABpAHMAIAB3AGkAbABsACAAcAByAGUAdgBlAG4AdAAgAHQAaABlACAAZgBpAGwAdABlAHIAXwBiAGwAYQBuAGsAcwAgAGYAdQBuAGMAdABpAG8AbgBhAGwAaQB0AHkAIABmAHIAbwBtACAAdwBvAHIAawBpAG4AZwAgAGEAcwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZQB4AHAAZQBjAHQAZQBkACAAYQBzACAAdQBzAGUAcwAgAGIAbABhAG4AawAgAHMAdAByAGkAbgBnACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAKABcACIAXAAiACkAIABpAG4AIAB0AGgAZQAgAHYAYQBsAHUAZQBzACAAZgBpAGUAbABkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAGwAdABlAHIAXwBiAGwAYQBuAGsAcwAgACAAWwBvAHAAdABpAG8AbgBhAGwAXQAgACAAVABSAFUARQAvAEYAQQBMAFMARQAgAGkAbgBwAHUAdAAgAHAAYQByAGEAbQBlAHQAZQByACAAYQBsAGwAbwB3AGkAbgBnACAAdABoAGUAIAB1AHMAZQByACAAdABvACAAZgBpAGwAdABlAHIAIABvAHUAdAAgAGIAbABhAG4AawAgAHIAbwB3AHMAIAAvACAAYgBsAGEAbgBrACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGEAdABhACAAcABvAGkAbgB0AHMAOwAgAHcAaQBsACAAZABlAGYAYQB1AGwAdAAgAHQAbwAgAEYAQQBMAFMARQAgAGkAZgAgAG4AbwB0ACAAcwBlAHQAIABiAHkAIAB1AHMAZQByAFwAbgAgACAAIAAgAEUAUgBSAE8AUgBDAEgARQBDAEsAUwA6ACAAIwBWAEEATABVAEUAIQAgACAAIAAgACAAIAAgACAATQBpAHMAcwBpAG4AZwAvAG8AbQBpAHQAdABlAGQAIABuAG8AbgAtAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIAAoAHIAbwB3AF8AaABlAGEAZABlAHIAcwAsACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACwAIABkAGEAdABhACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGQAbwBlAHMAIABuAG8AdAAgAGgAYQB2AGUAIABhAHQAIABsAGUAYQBzAHQAIAAxACAAcgBvAHcALAAgAG8AcgAgAGgAYQBzACAAbQBvAHIAZQAgAHQAaABhAG4AIAAxACAAYwBvAGwAdQBtAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGQAbwBlAHMAIABuAG8AdAAgAGgAYQB2AGUAIABhAHQAIABsAGUAYQBzAHQAIAAxACAAYwBvAGwAdQBtAG4ALAAgAG8AcgAgAGgAYQBzACAAbQBvAHIAZQAgAHQAaABhAG4AIAAxACAAcgBvAHcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIABkAGEAdABhACAAcABhAHIAYQBtAGUAdABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABoAGEAdgBlACAAYQB0ACAAbABlAGEAcwB0ACAAMQAgAHIAbwB3ACAAYQBuAGQAIABhAHQAIABsAGUAYQBzAHQAIAAxACAAYwBvAGwAdQBtAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAEMAQQBMAEMAIQAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGkAbgAgAHQAaABlACAAcABhAHMAcwBlAGQAIABkAGEAdABhACAAdABhAGIAbABlACAAKABkAGEAdABhACkAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGQAbwBlAHMAIABuAG8AdAAgAG0AYQB0AGMAaAAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAbwB3AHMAIABpAG4AIAB0AGgAZQAgAHIAbwB3AF8AaABlAGEAZABlAHIAcwAgAHAAYQByAGEAbQBlAHQAZQByADsAIABvAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAYwBvAGwAdQBtAG4AcwAgAGkAbgAgAHQAaABlACAAcABhAHMAcwBlAGQAIABkAGEAdABhACAAdABhAGIAbABlACAAKABkAGEAdABhACkAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGQAbwBlAHMAIABuAG8AdAAgAG0AYQB0AGMAaAAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABpAG4AIAB0AGgAZQAgAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAcwAgAHAAYQByAGEAbQBlAHQAZQByAFwAbgAqAC8AXABuAEYAbABhAHQAdABlAG4AIAA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAcgBhAG0AZQB0AGUAcgAgAGQAZQBjAGwAYQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgAHIAbwB3AF8AaABlAGEAZABlAHIAcwAsAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAcwAsAFwAbgAgACAAIAAgAGQAYQB0AGEALABcAG4AIAAgACAAIABbAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwBdACwAXABuACAAIAAgACAAWwBmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzAF0ALABcAG4AIAAgACAAIAAvAC8AIABNAGEAaQBuACAAcAByAG8AYwBlAGQAdQByAGUAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAF8AcgBoACwAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMALABcAG4AIAAgACAAIAAgACAAIAAgAF8AYwBoACwAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMALABcAG4AIAAgACAAIAAgACAAIAAgAF8AZABkACwAIABkAGEAdABhACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgACAALQAtAD4AIABpAHMAcwB1AGUAcwAgAGkAbgAgAHQAaABlACAAbQBhAGkAbgAgAHAAYQBzAHMAZQBkACAAcABhAHIAYQBtAGUAdABlAHIAcwAgAHcAaQBsAGwAIABnAGkAdgBlACAAYQAgACMAVgBBAEwAVQBFACEAIABlAHIAcgBvAHIAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAgAC0ALQA+ACAAbQBpAHMAbQBhAHQAYwBoACAAaQBuACAAYQByAHIAYQB5ACAAcwBpAHoAZQAgAG8AZgAgAGQAYQB0AGEAIAB0AGEAYgBsAGUAIABhAG4AZAAgAHIAbwB3AF8AaABlAGEAZABlAHIAIABhAG4AZAAgAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAIAByAGEAbgBnAGUAcwAgAHcAaQBsAGwAIABnAGkAdgBlACAAYQAgACMAQwBBAEwAQwAhACAAZQByAHIAbwByAFwAbgAgACAAIAAgACAAIAAgACAAXwBpAG4AcABDAGgAawAsACAASQBGAFMAKAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAIABPAFIAKAAgAFIATwBXAFMAKABfAHIAaAApACAAPAAgADEALAAgAEMATwBMAFUATQBOAFMAKABfAHIAaAApACAAPAA+ACAAMQAsACAAUgBPAFcAUwAoAF8AYwBoACkAIAA8AD4AIAAxACwAIABDAE8ATABVAE0ATgBTACgAXwBjAGgAKQAgADwAIAAxACwAIABSAE8AVwBTACgAXwBkAGQAKQAgADwAIAAxACwAIABDAE8ATABVAE0ATgBTACgAXwBkAGQAKQAgADwAIAAxACkALAAgADMAKQAsACAAMwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAIABPAFIAKAAgAFIATwBXAFMAKABfAGQAZAApACAAPAA+ACAAUgBPAFcAUwAoAF8AcgBoACkALAAgAEMATwBMAFUATQBOAFMAKABfAGQAZAApACAAPAA+ACAAQwBPAEwAVQBNAE4AUwAoAF8AYwBoACkAKQAsACAAMwApACwAIAAxADQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAFUARQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABEAGUAYQBsACAAdwBpAHQAaAAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIABhAG4AZAAgAHMAZQB0ACAAZABlAGYAYQB1AGwAdAAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAXwByAHAALAAgAEkARgAoACAASQBTAE8ATQBJAFQAVABFAEQAKAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAKQAsACAAXAAiAFwAIgAsACAAcgBlAHAAbABhAGMAZQBfAGIAbABhAG4AawBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AZgBsAHQAcgAsACAASQBGACgAIABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAHQAZQByAF8AYgBsAGEAbgBrAHMAKQAsACAARgBBAEwAUwBFACwAIABmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAdABoAGUAIABrAGUAeQAgAGYAaQBlAGwAZAAgAC0ALQAgAHIAZQBwAGUAYQB0AHMAIAB0AGgAZQAgAGMAbwBsAHUAbQBuACAAbwBmACAAcgBvAHcAIAB0AGkAdABsAGUAcwAgAHQAbwAgAG0AYQB0AGMAaAAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgAgAGgAZQBhAGQAZQByAHMAIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAcwAgAHQAbwAgAGEAIABzAGkAbgBnAGwAZQAgAGMAbwBsAHUAbQBuAFwAbgAgACAAIAAgACAAIAAgACAAXwBrAGUAeQAsACAAVABPAEMATwBMACgAIABJAEYAKAAgAFMARQBRAFUARQBOAEMARQAoADEALAAgAEMATwBMAFUATQBOAFMAKABfAGMAaAApACkALAAgAF8AcgBoACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwByAGUAYQB0AGUAIAB0AGgAZQAgAG4AYQBtAGUAcwAgAGYAaQBlAGwAZAAgAC0ALQAgAHIAZQBwAGUAYQB0AHMAIAB0AGgAZQAgAHIAbwB3ACAAbwBmACAAYwBvAGwAdQBtAG4AIABoAGUAYQBkAGUAcgBzACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3ACAAdABpAHQAbABlAHMAIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAcwAgAHQAbwAgAGEAIABzAGkAbgBnAGwAZQAgAGMAbwBsAHUAbQBuAFwAbgAgACAAIAAgACAAIAAgACAAXwBuAGEAbQBlAHMALAAgAFQATwBDAE8ATAAoACAASQBGACgAIABTAEUAUQBVAEUATgBDAEUAKAAgAFIATwBXAFMAKABfAHIAaAApACwAIAAxACkALAAgAF8AYwBoACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwByAGUAYQB0AGUAIAB0AGgAZQAgAHYAYQBsAHUAZQBzACAAZgBpAGUAbABkACAALQAtACAAdQBzAGUAcwAgAGEAbgAgAEkATgBEAEUAWAAtAFgATQBBAFQAQwBIACAAbQBlAHQAaABvAGQAbwBsAG8AZwB5ACAAdABvACAAZwBlAHQAIAB0AGgAZQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAGsAZQB5ACAAYQBuAGQAIABuAGEAbQBlAHMAIABmAGkAZQBsAGQAcwA7ACAAZQBtAHAAdAB5ACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAdwBpAGwAbAAgAHMAaABvAHcAIABhAHMAIAAwACAAKAB6AGUAcgBvACkAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAgAC0ALQA+ACAAdABlAHMAdABzACAAZgBvAHIAIABiAGwAYQBuAGsAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIABhAG4AZAAgAHIAZQBwAGwAYQBjAGUAcwAgAHcAaQB0AGgAIAB0AGgAZQAgAG8AcAB0AGkAbwBuAGEAbAAgAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwAgAHAAYQByAGEAbQBlAHQAZQByAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAIAAtAC0APgAgAGIAeQAgAGQAZQBmAGEAdQBsAHQAIABiAGwAYQBuAGsAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIABhAHIAZQAgAHAAcgBlAHMAZQByAHYAZQBkACAAdQBzAGkAbgBnACAAYQAgAE4AdQBsAGwAUwB0AHIAaQBuAGcAIAAoAFwAIgBcACIAKQAgAHQAbwAgAGEAbABsAG8AdwAgAGYAbwByACAAbwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAdABlAHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABfAHYAYQBsAHUAZQBzACwAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGQAcAAsACAASQBOAEQARQBYACgAXwBkAGQALAAgAFgATQBBAFQAQwBIACgAXwBrAGUAeQAsACAAXwByAGgALAAgADAAKQAsACAAWABNAEEAVABDAEgAKABfAG4AYQBtAGUAcwAsACAAXwBjAGgALAAgADAAKQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAIABJAFMAQgBMAEEATgBLACgAXwBkAHAAKQAsACAAXwByAHAALAAgAF8AZABwACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAG8AdQB0AHAAdQB0ACAALQAtACAAcwB0AGEAYwBrACAAawBlAHkALAAgAG4AYQBtAGUAIABhAG4AZAAgAHYAYQBsAHUAZQAgAGMAbwBsAHUAbQBuAHMAIAAoAF8AZAB0ACkALAAgAGEAbgBkACAAZgBpAGwAdABlAHIAIABiAGwAYQBuAGsAcwAgAHYAYQBsAHUAZQAgAHIAbwB3AHMAIABpAGYAIAByAGUAcQB1AGkAcgBlAGQAIAAoAF8AZgBsAHQAcgApAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAIAAtAC0APgAgACAAdABoAGUAIAByAG8AdwAgAGYAaQBsAHQAZQByAGkAbgBnACAAcgBlAGwAaQBlAHMAIABvAG4AIABiAGwAYQBuAGsAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIAB1AHMAaQBuAGcAIABOAHUAbABsAFMAdAByAGkAbgBnACAAKABcACIAXAAiACkAIAB0AG8AIAB3AG8AcgBrACAAYwBvAHIAcgBlAGMAdABsAHkALAAgAHMAbwAgAHcAaQBsAGwAIABuAG8AdAAgAGYAdQBuAGMAdABpAG8AbgAgAGkAZgAgAHQAaABlACAAcgBlAHAAbABhAGMAZQBfAGIAbABhAG4AawBzACAAZgB1AG4AYwB0AGkAbwBuACAAaQBzACAAdQBzAGUAZABcAG4AIAAgACAAIAAgACAAIAAgAF8AYwBhAGwAYwAsACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwBkAHQALAAgAEgAUwBUAEEAQwBLACgAXwBrAGUAeQAsACAAXwBuAGEAbQBlAHMALAAgAF8AdgBhAGwAdQBlAHMAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAF8AZgBsAHQAcgAsACAARgBJAEwAVABFAFIAKABfAGQAdAAsACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAF8AZAB0ACwAIAAtADEAKQAgADwAPgAgAFwAIgBcACIAKQAsACAAXwBkAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBlAHQAdQByAG4AIAB2AGEAbAB1AGUAIABkAGUAcABlAG4AZABpAG4AZwAgAG8AbgAgAGkAbgBwAHUAdAAgAGMAaABlAGMAawBzACAAcwB0AGEAdAB1AHMAIAAtAC0AIABmAG8AcgAgAGkAbgBwAHUAdAAgAGMAaABlAGMAawAgAGYAYQBpAGwAdQByAGUAIAByAGUAdAB1AHIAbgAgAGEAIAAjAFYAQQBMAFUARQAhACAAZQByAHIAbwByACwAIABvAHQAaABlAHIAdwBpAHMAZQAgAHIAZQB0AHUAcgBuACAAdABoAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAcgBlAHMAdQBsAHQAIAAoAF8AYwBhAGwAYwApAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAXwBpAG4AcABDAGgAawAgAD0AIAAwACwAIABfAGMAYQBsAGMALAAgAFIAUwBfAEMARQByAHIAKABfAGkAbgBwAEMAaABrACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAIAAgAE4AQQBNAEUAOgAgACAAIAAgACAAIAAgACAARgBsAGEAdAB0AGUAbgBfAE0AdQBsAHQAaQBLAGUAeQAoACkAXABuACAAIAAgACAAQQBVAFQASABPAFIAOgAgACAAIAAgACAAIABSAC4AUwBpAGwAawBcAG4AIAAgACAAIABWAEUAUgBTAEkATwBOADoAIAAgACAAIAAgAHYAMQAuADAANQAgACAAKAAwADgALwAwADQALwAyADAAMgA0ACkAXABuACAAIAAgACAARABFAFMAQwBSAEkAUABUAEkATwBOADoAIABBAG4AIABlAHgAdABlAG4AcwBpAG8AbgAgAG8AZgAgAHQAaABlACAAZgB1AGwAbAAtAGYAdQBuAGMAdABpAG8AbgBhAGwAaQB0AHkAIABSAFMAXwBGAGwAYQB0AHQAZQBuACgAKQAgAGYAdQBuAGMAdABpAG8AbgAuACAAVABoAGkAcwAgAEwAYQBtAGIAZABhACAAYQBsAGwAbwB3AHMAIABmAG8AcgAgAG0AdQBsAHQAaQBwAGwAZQAgAGsAZQB5ACAAYwBvAGwAdQBtAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAYQBzACAAbABvAG4AZwAgAGEAcwAgAHQAaABlAHkAIABhAHIAZQAgAGkAbgAgAGEAIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcgBhAG4AZwBlACkAIABpAG4AIABhACAAcwBpAG0AaQBsAGEAcgAgAG0AYQBuAG4AZQByACAAdABvACAAdABoAGUAIABBAGwAdABlAHIAeQB4ACAAVAByAGEAbgBzAHAAbwBzAGUAIAB0AG8AbwBsAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAGMAcgBlAGEAdABlAGQAIABrAGUAeQAgAGYAaQBlAGwAZAAgAGkAcwAgAGMAaABhAG4AZwBlAGQAIAB0AG8AIABfAGsAZQB5AHMAIABhAG4AZAAgAHUAcwBlAHMAIABhACAAZABpAGYAZgBlAHIAZQBuAHQAIABhAHAAcAByAG8AYQBjAGgAIAB0AG8AIABpAHQAcwAgAGMAbwBuAHMAdAB1AGMAdABpAG8AbgAgAHcAaQB0AGgAIAB0AGgAZQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAApACAAZgB1AG4AYwB0AGkAbwBuAC4AIABUAGgAZQAgAGUAYQByAGwAaQBlAHIAIAB2AGUAcgBzAGkAbwBuAHMAIABvAGYAIAB0AGgAZQAgAGYAbABhAHQALQBmAGkAbABlACAATABhAG0AYgBkAGEAIABjAHIAZQBhAHQAZQAgAHQAaABlACAAawBlAHkAIABmAGkAZQBsAGQAIABhAHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAbQBhAGQAZQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdQBwACAAbwBmACAAdABoAGUAIABzAGkAbgBnAGwAZQAgAGMAbwBsAHUAbQBuACAAbwBmACAAcgBvAHcAIAB0AGkAdABsAGUAcwAgAHIAZQBwAGUAYQB0AGUAZAAgAGEAYwByAG8AcwBzACAAdABoAGUAIABzAGEAbQBlACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAYQBzACAAdABoAGUAcgBlACAAYQByAGUAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGgAZQAgAHMAZQBsAGUAYwB0AGUAZAAgAGMAbwBsAHUAbQBuACAAaABlAGEAZABlAHIAcwAgAC0AIAB0AGgAaQBzACAAMgBEACAAYQByAHIAYQB5ACAAaQBzACAAdABoAGUAbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAYQAgAHMAaQBuAGcAbABlACAAYwBvAGwAdQBtAG4AIAB1AHMAaQBuAGcAIAB0AGgAZQAgAFQATwBDAE8ATAAoACkAIABmAHUAbgBjAHQAaQBvAG4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAYwBhAG4AbgBpAG4AZwAgAGEAYwByAG8AcwBzACAAcgBvAHcAcwAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABoAGUAIABlAHgAdABlAG4AZABlAGQAIABtAGUAdABoAG8AZABvAGwAbwBnAHkAIABjAG8AbgBzAHQAcgB1AGMAdABzACAAdABoAGUAIABrAGUAeQBzACAAZgBpAGUAbABkACAAdQBzAGkAbgBnACAAdABoAGUAIABNAEEASwBFAEEAUgBSAEEAWQAoACkAIABmAHUAbgBjAHQAaQBvAG4AIAB3AGgAZQByAGUAIABhACAAMgBEACAAYQByAHIAYQB5ACAAaQBzACAAYwByAGUAYQB0AGUAZAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdwBoAGkAYwBoACAAaQBzACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3ACAAdABpAHQAbABlACAAcgBvAHcAcwAgAG0AdQBsAHQAaQBwAGwAaQBlAGQAIABiAHkAIAB0AGgAeQBlACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgAgAGgAZQBhAGQAZQByACAAYwBvAGwAdQBtAG4AcwAgAHQAYQBsAGwAIABiAHkAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAdABoAGUAIABzAGUAbABlAGMAdABlAGQAIAByAG8AdwAgAHQAaQB0AGwAZQBzACAAcgBhAG4AZwBlAC4AIABUAGgAaQBzACAAMgBEACAAYQByAHIAYQB5ACAAaQBzACAAdABoAGUAbgAgAHAAbwBwAHUAbABhAHQAZQBkACAAYgB5ACAAdABoAGUAIABNAEEASwBFAEEAUgBSAEEAWQAoACkAIABMAGEAbQBiAGQAYQAgAHUAcwBpAG4AZwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBuACAASQBOAEQARQBYACgAKQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AbgAgAHQAaABlACAAbwByAGkAZwBpAG4AYQBsAGwAeQAgAHMAZQBsAGUAYwB0AGUAZAAgAHIAbwB3ACAAdABpAHQAbABlAHMAIAByAGEAbgBnAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMAdQByAHIAZQBuAHQAbAB5ACAAYQAgAHMAaQBtAHAAbABlACAAbQBlAHQAaABvAGQAbwBsAG8AZwB5ACAAKABUAE8AQwBPAEwAKAApACkAIABpAHMAIAB1AHMAZQBkACAAdABvACAAcABvAHAAdQBsAGEAdABlACAAdABoAGUAIAB2AGEAbAB1AGUAcwAgAGYAaQBlAGwAZAAsACAAdwBoAGkAYwBoACAAdwBvAHUAbABkACAAaQBkAGUAYQBsAGwAeQAgAGIAZQAgAHUAcABkAGEAdABlAGQAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAbwAgAGEAIABtAG8AcgBlACAAcgBvAGIAdQBzAHQAIABtAGUAdABoAG8AZABvAGwAbwBnAHkAIABzAHUAYwBoACAAYQBzACAAdABoAGUAIABJAE4ARABFAFgALQBYAE0AQQBUAEMASAAgAGEAcABwAHIAbwBhAGMAaAAuAFwAbgAgACAAIAAgAFAAQQBSAEEATQBFAFQARQBSAFMAOgAgACAAcgBvAHcAXwBoAGUAYQBkAGUAcgBzACAAIAAgACAAWwByAGUAcQB1AGkAcgBlAGQAXQAgACAAUgBhAG4AZwBlACAAbwBmACAAYwBlAGwAbABzACAAaQBuACAAYQAgAHMAaQBuAGcAbABlACAAYwBvAGwAdQBtAG4AIAAoADEAKwAgAHIAbwB3AHMALAAgADEAIABjAG8AbAApACAAdABoAGEAdAAgAHAAcgBvAHYAaQBkAGUAIAB0AGgAZQAgAGsAZQB5ACAAZgBpAGUAbABkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACAAWwByAGUAcQB1AGkAcgBlAGQAXQAgACAAUgBhAG4AZwBlACAAbwBmACAAYwBlAGwAbABzACAAaQBuACAAYQAgAHMAaQBuAGcAbABlACAAcgBvAHcAIAAoADEAIAByAG8AdwAsACAAMQArACAAYwBvAGwAKQAgAHQAaABhAHQAIABwAHIAbwB2AGkAZABlACAAdABoAGUAIABuAGEAbQBlACAAZgBpAGUAbABkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABhAHQAYQAgACAAIAAgACAAIAAgACAAIAAgACAAWwByAGUAcQB1AGkAcgBlAGQAXQAgACAAUgBhAG4AZwBlACAAbwBmACAAYwBlAGwAbABzACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAHMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAYQBiAGwAZQAgAHIAZQBwAHIAZQBzAGUAbgB0AGkAbgBnACAAdABoAGUAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIAB0AG8AIABmAGwAYQB0ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbABlADsAIABlAHgAcABlAGMAdABlAGQAIAB0AGgAYQB0ACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMAIAB3AGkAbABsACAAbQBhAHQAYwBoACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMAIABpAG4AIAB0AGgAZQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBvAHcAXwBoAGUAYQBkAGUAcgBzACAAcABhAHIAYQBtAGUAdABlAHIALAAgAGEAbgBkACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIAB3AGkAbABsACAAbQBhAHQAYwBoACAAdABoAGUAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwAgAFsAbwBwAHQAaQBvAG4AYQBsAF0AIAAgAFMAaQBuAGcAbABlACAAdgBhAGwAdQBlACAAaQBuAHAAdQB0ACAAKABjAGEAbgAgAGIAZQAgAG4AdQBtAGUAcgBpAGMALAAgAHMAdAByAGkAbgBnACAAbwByACAAcgBlAGYAZQByAGUAbgBjAGUAKQA7ACAAdQBzAGUAZAAgAHQAbwAgAHIAZQBwAGwAYQBjAGUAIABhAG4AeQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBsAGEAbgBrACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAdwBpAHQAaAAgAHQAaABlACAAdQBzAGUAcgAgAHAAYQBzAHMAZQBkACAAcABhAHIAYQBtAGUAdABlAHIALgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHQAZQA6ACAAdABoAGkAcwAgAHcAaQBsAGwAIABwAHIAZQB2AGUAbgB0ACAAdABoAGUAIABmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzACAAZgB1AG4AYwB0AGkAbwBuAGEAbABpAHQAeQAgAGYAcgBvAG0AIAB3AG8AcgBrAGkAbgBnACAAYQBzACAAZQB4AHAAZQBjAHQAZQBkACAAYQBzACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AHMAZQBzACAAYgBsAGEAbgBrACAAcwB0AHIAaQBuAGcAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIAAoAFwAIgBcACIAKQAgAGkAbgAgAHQAaABlACAAdgBhAGwAdQBlAHMAIABmAGkAZQBsAGQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzACAAIABbAG8AcAB0AGkAbwBuAGEAbABdACAAIABUAFIAVQBFAC8ARgBBAEwAUwBFACAAaQBuAHAAdQB0ACAAcABhAHIAYQBtAGUAdABlAHIAIABhAGwAbABvAHcAaQBuAGcAIAB0AGgAZQAgAHUAcwBlAHIAIAB0AG8AIABmAGkAbAB0AGUAcgAgAG8AdQB0ACAAYgBsAGEAbgBrACAAcgBvAHcAcwAgAC8AIABiAGwAYQBuAGsAIABkAGEAdABhACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AaQBuAHQAcwA7ACAAdwBpAGwAIABkAGUAZgBhAHUAbAB0ACAAdABvACAARgBBAEwAUwBFACAAaQBmACAAbgBvAHQAIABzAGUAdAAgAGIAeQAgAHUAcwBlAHIAXABuACAAIAAgACAARQBSAFIATwBSAEMASABFAEMASwBTADoAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIABNAGkAcwBzAGkAbgBnAC8AbwBtAGkAdAB0AGUAZAAgAG4AbwBuAC0AbwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwAgACgAcgBvAHcAXwBoAGUAYQBkAGUAcgBzACwAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMALAAgAGQAYQB0AGEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACMAVgBBAEwAVQBFACEAIAAgACAAIAAgACAAIAAgAHIAbwB3AF8AaABlAGEAZABlAHIAcwAgAHAAYQByAGEAbQBlAHQAZQByACAAZABvAGUAcwAgAG4AbwB0ACAAaABhAHYAZQAgAGEAdAAgAGwAZQBhAHMAdAAgADEAIAByAG8AdwAgAGEAbgBkACAAYQB0ACAAbABlAGEAcwB0ACAAMQAgAGMAbwBsAHUAbQBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIwBWAEEATABVAEUAIQAgACAAIAAgACAAIAAgACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACAAcABhAHIAYQBtAGUAdABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABoAGEAdgBlACAAYQB0ACAAbABlAGEAcwB0ACAAMQAgAGMAbwBsAHUAbQBuACwAIABvAHIAIABoAGEAcwAgAG0AbwByAGUAIAB0AGgAYQBuACAAMQAgAHIAbwB3AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIwBWAEEATABVAEUAIQAgACAAIAAgACAAIAAgACAAZABhAHQAYQAgAHAAYQByAGEAbQBlAHQAZQByACAAZABvAGUAcwAgAG4AbwB0ACAAaABhAHYAZQAgAGEAdAAgAGwAZQBhAHMAdAAgADEAIAByAG8AdwAgAGEAbgBkACAAYQB0ACAAbABlAGEAcwB0ACAAMQAgAGMAbwBsAHUAbQBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIwBDAEEATABDACEAIAAgACAAIAAgACAAIAAgACAAVABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMAIABpAG4AIAB0AGgAZQAgAHAAYQBzAHMAZQBkACAAZABhAHQAYQAgAHQAYQBiAGwAZQAgACgAZABhAHQAYQApACAAcABhAHIAYQBtAGUAdABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABtAGEAdABjAGgAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdwBzACAAaQBuACAAdABoAGUAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgA7ACAAbwByAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABpAG4AIAB0AGgAZQAgAHAAYQBzAHMAZQBkACAAZABhAHQAYQAgAHQAYQBiAGwAZQAgACgAZABhAHQAYQApACAAcABhAHIAYQBtAGUAdABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABtAGEAdABjAGgAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAdABoAGUAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgBcAG4AKgAvAFwAbgBGAGwAYQB0AHQAZQBuAF8ATQB1AGwAdABpAGsAZQB5ACAAPQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAALwAvACAAUABhAHIAYQBtAGUAdABlAHIAIABkAGUAYwBsAGEAcgBhAHQAaQBvAG4AcwBcAG4AIAAgACAAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMALABcAG4AIAAgACAAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMALABcAG4AIAAgACAAIABkAGEAdABhACwAXABuACAAIAAgACAAWwByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAXQAsAFwAbgAgACAAIAAgAFsAZgBpAGwAdABlAHIAXwBiAGwAYQBuAGsAcwBdACwAXABuACAAIAAgACAALwAvACAATQBhAGkAbgAgAHAAcgBvAGMAZQBkAHUAcgBlAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABfAHIAaAAsACAAcgBvAHcAXwBoAGUAYQBkAGUAcgBzACwAXABuACAAIAAgACAAIAAgACAAIABfAGMAaAAsACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACwAXABuACAAIAAgACAAIAAgACAAIABfAGQAZAAsACAAZABhAHQAYQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBoAGUAYwBrACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAgAC0ALQA+ACAAaQBzAHMAdQBlAHMAIABpAG4AIAB0AGgAZQAgAG0AYQBpAG4AIABwAGEAcwBzAGUAZAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIAB3AGkAbABsACAAZwBpAHYAZQAgAGEAIAAjAFYAQQBMAFUARQAhACAAZQByAHIAbwByAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAIAAtAC0APgAgAG0AaQBzAG0AYQB0AGMAaAAgAGkAbgAgAGEAcgByAGEAeQAgAHMAaQB6AGUAIABvAGYAIABkAGEAdABhACAAdABhAGIAbABlACAAYQBuAGQAIAByAG8AdwBfAGgAZQBhAGQAZQByACAAYQBuAGQAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByACAAcgBhAG4AZwBlAHMAIAB3AGkAbABsACAAZwBpAHYAZQAgAGEAIAAjAEMAQQBMAEMAIQAgAGUAcgByAG8AcgBcAG4AIAAgACAAIAAgACAAIAAgAF8AaQBuAHAAQwBoAGsALAAgAEkARgBTACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAgAE8AUgAoACAAUgBPAFcAUwAoAF8AcgBoACkAIAA8ACAAMQAsACAAQwBPAEwAVQBNAE4AUwAoAF8AcgBoACkAIAA8ACAAMQAsACAAUgBPAFcAUwAoAF8AYwBoACkAIAA8AD4AIAAxACwAIABDAE8ATABVAE0ATgBTACgAXwBjAGgAKQAgADwAIAAxACwAIABSAE8AVwBTACgAXwBkAGQAKQAgADwAIAAxACwAIABDAE8ATABVAE0ATgBTACgAXwBkAGQAKQAgADwAIAAxACkALAAgADMAKQAsACAAMwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAIABPAFIAKAAgAFIATwBXAFMAKABfAGQAZAApACAAPAA+ACAAUgBPAFcAUwAoAF8AcgBoACkALAAgAEMATwBMAFUATQBOAFMAKABfAGQAZAApACAAPAA+ACAAQwBPAEwAVQBNAE4AUwAoAF8AYwBoACkAKQAsACAAMwApACwAIAAxADQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAFUARQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABEAGUAYQBsACAAdwBpAHQAaAAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIABhAG4AZAAgAHMAZQB0ACAAZABlAGYAYQB1AGwAdAAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAXwByAHAALAAgAEkARgAoACAASQBTAE8ATQBJAFQAVABFAEQAKAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAKQAsACAAXAAiAFwAIgAsACAAcgBlAHAAbABhAGMAZQBfAGIAbABhAG4AawBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AZgBsAHQAcgAsACAASQBGACgAIABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAHQAZQByAF8AYgBsAGEAbgBrAHMAKQAsACAARgBBAEwAUwBFACwAIABmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAdABoAGUAIABrAGUAeQAgAGYAaQBlAGwAZABzACAALQAtACAAdQBzAGUAcwAgAHQAaABlACAATQBBAEsARQBBAFIAUgBBAFkAKAApACAAZgB1AG4AYwB0AGkAbwBuACAAdABvACAAYwByAGUAYQB0AGUAIAByAGUAcABlAGEAdAAgAGIAbABvAGMAawBzACAAbwBmACAAdABoAGUAIABzAGUAbABlAGMAdABlAGQAIAByAG8AdwBfAGgAZQBhAGQAZQByACAALwAgAGsAZQB5ACAAYwBvAGwAdQBtAG4AKABzACkAIABhAGwAbABvAHcAaQBuAGcAIABmAG8AcgAgADEAKwAgAGsAZQB5ACAAYwBvAGwAdQBtAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgAF8AawBlAHkAcwAsACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwByAHIALAAgAFIATwBXAFMAKABfAHIAaAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AcgBjACwAIABDAE8ATABVAE0ATgBTACgAXwByAGgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGMAYwAsACAAQwBPAEwAVQBNAE4AUwAoAF8AYwBoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKABfAHIAcgAgACoAIABfAGMAYwAsACAAXwByAGMALAAgAEwAQQBNAEIARABBACgAXwByAG8AdwAsAF8AYwBvAGwALAAgAEkATgBEAEUAWAAoAF8AcgBoACwAIABGAEwATwBPAFIALgBNAEEAVABIACgAKABfAHIAbwB3ACAALQAgADEAKQAgAC8AIABfAGMAYwApACAAKwAgADEAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAdABoAGUAIABuAGEAbQBlAHMAIABmAGkAZQBsAGQAIAAtAC0AIAByAGUAcABlAGEAdABzACAAdABoAGUAIAByAG8AdwAgAG8AZgAgAGMAbwBsAHUAbQBuACAAaABlAGEAZABlAHIAcwAgAHQAbwAgAG0AYQB0AGMAaAAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwAgAHQAaQB0AGwAZQBzACAAYQBuAGQAIABjAG8AbgB2AGUAcgB0AHMAIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABjAG8AbAB1AG0AbgBcAG4AIAAgACAAIAAgACAAIAAgAF8AbgBhAG0AZQBzACwAIABUAE8AQwBPAEwAKAAgAEkARgAoACAAUwBFAFEAVQBFAE4AQwBFACgAIABSAE8AVwBTACgAXwByAGgAKQAsACAAMQApACwAIABfAGMAaAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAdABoAGUAIAB2AGEAbAB1AGUAcwAgAGYAaQBlAGwAZAAgAC0ALQAgAHUAcwBlAHMAIABhAG4AIABJAE4ARABFAFgALQBYAE0AQQBUAEMASAAgAG0AZQB0AGgAbwBkAG8AbABvAGcAeQAgAHQAbwAgAGcAZQB0ACAAdABoAGUAIABkAGEAdABhACAAcABvAGkAbgB0ACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIABrAGUAeQAgAGEAbgBkACAAbgBhAG0AZQBzACAAZgBpAGUAbABkAHMAOwAgAGUAbQBwAHQAeQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwAgAHcAaQBsAGwAIABzAGgAbwB3ACAAYQBzACAAMAAgACgAegBlAHIAbwApAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAIAAtAC0APgAgAHQAZQBzAHQAcwAgAGYAbwByACAAYgBsAGEAbgBrACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAYQBuAGQAIAByAGUAcABsAGEAYwBlAHMAIAB3AGkAdABoACAAdABoAGUAIABvAHAAdABpAG8AbgBhAGwAIAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAIABwAGEAcgBhAG0AZQB0AGUAcgBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgACAALQAtAD4AIABiAHkAIABkAGUAZgBhAHUAbAB0ACAAYgBsAGEAbgBrACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAYQByAGUAIABwAHIAZQBzAGUAcgB2AGUAZAAgAHUAcwBpAG4AZwAgAGEAIABOAHUAbABsAFMAdAByAGkAbgBnACAAKABcACIAXAAiACkAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAG8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAHQAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAXwB2AGEAbAB1AGUAcwAsACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwBkAHAALAAgAFQATwBDAE8ATAAoAF8AZABkACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAIABJAFMAQgBMAEEATgBLACgAXwBkAHAAKQAsACAAXwByAHAALAAgAF8AZABwACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAbwB1AHQAcAB1AHQAIAAtAC0AIABzAHQAYQBjAGsAIABrAGUAeQAsACAAbgBhAG0AZQAgAGEAbgBkACAAdgBhAGwAdQBlACAAYwBvAGwAdQBtAG4AcwAgACgAXwBkAHQAKQAsACAAYQBuAGQAIABmAGkAbAB0AGUAcgAgAGIAbABhAG4AawBzACAAdgBhAGwAdQBlACAAcgBvAHcAcwAgAGkAZgAgAHIAZQBxAHUAaQByAGUAZAAgACgAXwBmAGwAdAByACkAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAgAC0ALQA+ACAAIAB0AGgAZQAgAHIAbwB3ACAAZgBpAGwAdABlAHIAaQBuAGcAIAByAGUAbABpAGUAcwAgAG8AbgAgAGIAbABhAG4AawAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwAgAHUAcwBpAG4AZwAgAE4AdQBsAGwAUwB0AHIAaQBuAGcAIAAoAFwAIgBcACIAKQAgAHQAbwAgAHcAbwByAGsAIABjAG8AcgByAGUAYwB0AGwAeQAsACAAcwBvACAAdwBpAGwAbAAgAG4AbwB0ACAAZgB1AG4AYwB0AGkAbwBuACAAaQBmACAAdABoAGUAIAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAIABmAHUAbgBjAHQAaQBvAG4AIABpAHMAIAB1AHMAZQBkAFwAbgAgACAAIAAgACAAIAAgACAAXwBjAGEAbABjACwAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGQAdAAsACAASABTAFQAQQBDAEsAKABfAGsAZQB5AHMALAAgAF8AbgBhAG0AZQBzACwAIABfAHYAYQBsAHUAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAXwBmAGwAdAByACwAIABGAEkATABUAEUAUgAoAF8AZAB0ACwAIABDAEgATwBPAFMARQBDAE8ATABTACgAXwBkAHQALAAgAC0AMQApACAAPAA+ACAAXAAiAFwAIgApACwAIABfAGQAdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAHIAZQB0AHUAcgBuACAAdgBhAGwAdQBlACAAZABlAHAAZQBuAGQAaQBuAGcAIABvAG4AIABpAG4AcAB1AHQAIABjAGgAZQBjAGsAcwAgAHMAdABhAHQAdQBzACAALQAtACAAZgBvAHIAIABpAG4AcAB1AHQAIABjAGgAZQBjAGsAIABmAGEAaQBsAHUAcgBlACAAcgBlAHQAdQByAG4AIABhAG4AIABFAHgAYwBlAGwAIABlAHIAcgBvAHIALAAgAG8AdABoAGUAcgB3AGkAcwBlACAAcgBlAHQAdQByAG4AIAB0AGgAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAByAGUAcwB1AGwAdAAgACgAXwBjAGEAbABjACkAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABfAGkAbgBwAEMAaABrACAAPQAgADAALAAgAF8AYwBhAGwAYwAsACAAUgBTAF8AQwBFAHIAcgAoAF8AaQBuAHAAQwBoAGsAKQApAFwAbgAgACAAIAAgACkAXABuACkAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAVABFAFMAVAAuAEEAYgBvAHUAdAAiACwAIgBUAEUAUwBUAC4AQwBFAHIAcgAiACwAIgBUAEUAUwBUAC4ARgBsAGEAdAB0AGUAbgAiACwAIgBUAEUAUwBUAC4ARgBsAGEAdAB0AGUAbgBfAE0AdQBsAHQAaQBrAGUAeQAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgCjACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAGcAYgAiAH0AfQA=</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuAC8AKgAgACAAUgBYAEwAXwBTAGgAZQBlAHQATgBhAG0AZQAgAEYAdQBuAGMAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgAHYAZQByAHMAaQBvAG4AIAAxAC4AMAA0ACAAIAAoADIAMwAtAE0AYQByAC0AMgAwADIANQApACAAXABuACAAIAAgACAAIAAgACAAIABSACAAUwBpAGwAawAsACAAUgBYAEwAIABEAGUAdgBlAGwAbwBwAG0AZQBuAHQAXABuACAAIAAgACAAIAAgACAAIABoAHQAdABwAHMAOgAvAC8AZwBpAHMAdAAuAGcAaQB0AGgAdQBiAC4AYwBvAG0ALwByAC0AcwBpAGwAawAvAGUAYwAwADUAMwBlADUAOQAwADUAOABlADMAOQA5AGYAMABmADkAYQBhADkAYQBjADcAMQA1ADMAMQBhADcAMQBcAG4AKgAvAFwAbgAvACoAXABuACAAIAAgACAATgBhAG0AZQA6ACAAIAAgACAAIAAgACAAIABTAGgAZQBlAHQATgBhAG0AZQAoACkAXABuACAAIAAgACAARABlAHMAYwByAGkAcAB0AGkAbwBuADoAIAAqAC8ALwAqACoAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAdwBvAHIAawBzAGgAZQBlAHQAIABuAGEAbQBlACAAKABhAHMAIABkAGkAcwBwAGwAYQB5AGUAZAAgAGkAbgAgAHQAaABlACAAdwBvAHIAawBzAGgAZQBlAHQAIAB0AGEAYgApACAAZgBvAHIAIAB0AGgAZQAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHAAcgBvAHYAaQBkAGUAZAA7ACAAVwBvAHIAawBiAG8AbwBrACAAbQB1AHMAdAAgAGIAZQAgAHMAYQB2AGUAZAAgAGYAaQByAHMAdAAqAC8ALwAqAFwAbgAgACAAIAAgAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgACsAIABjAGUAbABsAF8AcgBlAGYAIAAgACAAIAAgACAAPQAgACgAcgBlAHEAdQBpAHIAZQBkACkAIABBACAAdgBhAGwAaQBkACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlACwAIABlAC4AZwAuACAAQQAxACwAIABvAHIAIAAnAFMAaABlAGUAdAAxACcAIQBBADEAXABuACAAIAAgACAARQByAHIAbwByACAAYwBvAGQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQAgACAAIAA9ACAAdABoAGUAIABjAGUAbABsAF8AcgBlAGYAIABwAGEAcgBhAG0AZQB0AGUAcgAgAHIAZQBxAHUAaQByAGUAcwAgAGEAIAB2AGEAbABpAGQAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByADoAIABXAG8AcgBrAGIAbwBvAGsAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkAF0AIAAgACAAIAA9ACAAdABoAGUAIABXAG8AcgBrAGIAbwBvAGsAIABmAGkAbABlACAAbQB1AHMAdAAgAGIAZQAgAHMAYQB2AGUAZAAgAGYAaQByAHMAdAAgAGkAbgAgAG8AcgBkAGUAcgAgAGYAbwByACAAdABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIAB0AG8AIAB3AG8AcgBrACAAYwBvAHIAcgBlAGMAdABsAHkAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFMAaABlAGUAdAAgAG4AYQBtAGUAXQAgACAAIAAgACAAIAAgACAAIAA9ACAAYQBuACAAZQByAHIAbwByACAAbwBjAGMAdQByAHIAZQBkACAAZwBlAHQAdABpAG4AZwAgAHQAaABlACAAZgBpAGwAZQBuAGEAbQBlACAAcwB0AHIAaQBuAGcAIABvAHIAIABlAHgAdAByAGEAYwB0AGkAbgBnACAAdABoAGUAIAB3AG8AcgBrAHMAaABlAGUAdAAgAG4AYQBtAGUAIABmAHIAbwBtACAAdABoAGUAIABmAGkAbABlAG4AYQBtAGUAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIABOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABUAGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AdQB0AHAAdQB0AHMAIABjAHUAcwB0AG8AbQAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAcwAgAGEAcwAgAHMAdAByAGkAbgBnAHMAOwAgAHQAaABlAHMAZQAgAHcAaQBsAGwAIABuAG8AdAAgAGIAZQAgAGYAbABhAGcAZwBlAGQAIABiAHkAIABFAHgAYwBlAGwAIABvAHIAIABhAG4AeQAgAGEAZABkAC0AaQBuAHMAIABhAHMAIABlAHIAcgBvAHIAIABjAGUAbABsAHMALgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABBAGwAdABlAHIAbgBhAHQAaQB2AGUAbAB5ACwAIAB0AGgAZQAgAGMAdQBzAHQAbwBtACAAZQByAHIAbwByACAAbQBlAHMAcwBhAGcAZQBzACAAYwBhAG4AIABiAGUAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAbgBhAHQAaQB2AGUAIABFAHgAYwBlAGwAIABlAHIAcgBvAHIAIABjAG8AZABlAHMAIABzAG8AIAB0AGgAYQB0ACAAdABoAGUAIABlAHIAcgBvAHIAIABpAHMAIABmAGwAYQBnAGcAZQBkACAAaQBuACAAdABoAGUAIABuAG8AcgBtAGEAbAAgAHcAYQB5ADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAB0AG8AIABkAG8AIAB0AGgAaQBzADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQAgAHIAZQBwAGwAYQBjAGUAIAB0AGgAZQAgAFwAIgAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQBcACIAIABzAHQAcgBpAG4AZwAgAHcAaQB0AGgAIAB0AGgAZQAgACMAVgBBAEwAVQBFACEAIAAoAG8AcgAgACMAUgBFAEYAIQApACAAZQByAHIAbwByACAAYwBvAGQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAtACAAcgBlAHAAbABhAGMAZQAgAHQAaABlACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAFcAbwByAGsAYgBvAG8AawAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAXQBcACIAIABhAG4AZAAgAFwAIgAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFMAaABlAGUAdAAgAG4AYQBtAGUAXQBcACIAIABzAHQAcgBpAG4AZwBzACAAdwBpAHQAaAAgAEwAQQBNAEIARABBACgAMAApACAAaQBuACAAbwByAGQAZQByACAAdABvACAAYwByAGUAYQB0AGUAIABhACAAIwBDAEEATABDACEAIABlAHIAcgBvAHIAIABjAG8AZABlAFwAbgAqAC8AXABuAFIAWABMAF8AUwBoAGUAZQB0AE4AYQBtAGUAIAA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAcgBhAG0AZQB0AGUAcgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXABuACAAIAAgACAAYwBlAGwAbABfAHIAZQBmACwAXABuACAAIAAgACAALwAvACAATQBhAGkAbgAgAGYAdQBuAGMAdABpAG8AbgAgAGIAbwBkAHkALwBjAGEAbABjAHUAbABhAHQAaQBvAG4AcwBcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBoAGUAYwBrACAAdABoAGEAdAAgAGkAbgBwAHUAdAAgAHAAcgBvAHYAaQBkAGUAZAAgAGkAcwAgAGEAcwAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAsACAAbwB0AGgAZQByAHcAaQBzAGUAIABjAHIAZQBhAHQAZQAgAGEAIABjAHUAcwB0AG8AbQAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAXABuACAAIAAgACAAIAAgACAAIABfAGkAbgBwAEMAaABrACwAIABJAEYAKAAgAE4ATwBUACgASQBTAFIARQBGACgAYwBlAGwAbABfAHIAZQBmACkAKQAsACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHIAZQBxAHUAaQByAGUAZABdAFwAIgAsACAAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABHAGUAdAAgAHQAaABlACAAZgBpAGwAZQBuAGEAbQBlACAAcwB0AHIAaQBuAGcAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAG4AYQB0AGkAdgBlACAAQwBFAEwATAAoACkAIABmAHUAbgBjAHQAaQBvAG4AIABhAG4AZAAgAHQAaABlACAAYwBlAGwAbABfAHIAZQBmACAAYQByAGcAdQBtAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAXwBmAGkAbABlAE4AYQBtAGUALAAgAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAYwBlAGwAbABfAHIAZQBmACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFUAcwBlACAAdABoAGUAIABUAEUAWABUAEEARgBUAEUAUgAoACkAIABmAHUAbgBjAHQAaQBvAG4AIAB0AG8AIABsAG8AbwBrACAAZgBvAHIAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAFwAIgBdAFwAIgAgAGMAaABhAHIAYQBjAHQAZQByACAAaQBuACAAdABoAGUAIABmAGkAbABlAG4AYQBtAGUAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAZgAgAG4AbwAgAG0AYQB0AGMAaABpAG4AZwAgAFwAIgBdAFwAIgAgAGMAaABhAHIAYQBjAHQAZQByACAAaQBzACAAZgBvAHUAbgBkACAAdABoAGUAbgAgAHIAZQB0AHUAcgBuACAAYQBuACAAZQBtAHAAdAB5ACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABfAHcAcwBOAGEAbQBlACwAIABJAEYAKABfAGYAaQBsAGUATgBhAG0AZQAgADwAPgAgAFwAIgBcACIALAAgAFQARQBYAFQAQQBGAFQARQBSACgAIABfAGYAaQBsAGUATgBhAG0AZQAsACAAXAAiAF0AXAAiACwAIAAtADEALAAgACwAIAAsACAAXAAiACMAXAAiACkALAAgAFwAIgAjAFsARQByAHIAbwByADoAIABXAG8AcgBrAGIAbwBvAGsAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkAF0AXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAaABlAGMAawAgAGYAbwByACAAYQBuACAAZQByAHIAbwByACAAdgBhAGwAdQBlACAAbwByACAAZQBtAHAAdAB5ACAAcwB0AHIAaQBuAGcAIABhAG4AZAAgAGkAZgAgAGYAbwB1AG4AZAAgAHIAZQB0AHUAcgBuACAAYQAgAGMAdQBzAHQAbwBtACAAZQByAHIAbwByACAAbQBlAHMAcwBhAGcAZQAsACAAbwB0AGgAZQByAHcAaQBzAGUAIAByAGUAdAB1AHIAbgAgAHQAaABlACAAdwBvAHIAawBzAGgAZQBlAHQAIABuAGEAbQBlACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABfAHIAdABuACwAIABJAEYAKAAgAE8AUgAoACAASQBTAEUAUgBSAE8AUgAoAF8AdwBzAE4AYQBtAGUAKQAsACAAXwB3AHMATgBhAG0AZQAgAD0AIABcACIAIwBcACIAKQAsACAAXAAiACMAWwBFAHIAcgBvAHIAIAByAGUAYQBkAGkAbgBnACAAUwBoAGUAZQB0ACAAbgBhAG0AZQBdAFwAIgAsACAAXwB3AHMATgBhAG0AZQApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABGAGkAbgBhAGwAIABjAGgAZQBjAGsAIAB0AG8AIABzAGUAZQAgAGkAZgAgAHQAaABlAHIAZQAgAHcAYQBzACAAYQBuACAAaQBuAHAAdQB0ACAAZQByAHIAbwByACwAIABhAG4AZAAgAGkAZgAgAHMAbwAgAHIAZQB0AHUAcgBuACAAdABoAGUAIABjAHUAcwB0AG8AbQAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABfAGkAbgBwAEMAaABrACAAPAA+ACAAXAAiAFwAIgAsACAAXwBpAG4AcABDAGgAawAsACAAXwByAHQAbgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAgACAAUgBYAEwAXwBXAG8AcgBrAGIAbwBvAGsATgBhAG0AZQAgAEYAdQBuAGMAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgAHYAZQByAHMAaQBvAG4AIAAxAC4AMAA1ACAAIAAoADIAMwAtAE0AYQByAC0AMgAwADIANQApAFwAbgAgACAAIAAgACAAIAAgACAAUgAgAFMAaQBsAGsALAAgAFIAWABMACAARABlAHYAZQBsAG8AcABtAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAaAB0AHQAcABzADoALwAvAGcAaQBzAHQALgBnAGkAdABoAHUAYgAuAGMAbwBtAC8AcgAtAHMAaQBsAGsALwAzADMAMwAxAGEAOAA0ADMAYQAyADgANgA4ADMANQBjAGYANwAzAGEAMgA0ADgAYwA2ADgAZQBjADAAMABmADcAXABuACoALwBcAG4ALwAqAFwAbgAgACAAIAAgAE4AYQBtAGUAOgAgACAAIAAgACAAIAAgACAAVwBvAHIAawBiAG8AbwBrAE4AYQBtAGUAKAApAFwAbgAgACAAIAAgAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6ACAAKgAvAC8AKgAqAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAFcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUALAAgAHcAaQB0AGgAIABvAHIAIAB3AGkAdABoAG8AdQB0ACAAdABoAGUAIABmAGkAbABlACAAZQB4AHQAZQBuAHMAaQBvAG4ALAAgAGYAbwByACAAdABoAGUAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIABwAHIAbwB2AGkAZABlAGQAOwAgAFcAbwByAGsAYgBvAG8AawAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAIABmAGkAcgBzAHQAKgAvAC8AKgBcAG4AIAAgACAAIABQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAIAAgACAAIAArACAAYwBlAGwAbABfAHIAZQBmACAAIAAgACAAIAAgACAAIAAgACAAPQAgACgAcgBlAHEAdQBpAHIAZQBkACkAIABBACAAdgBhAGwAaQBkACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlACwAIABlAC4AZwAuACAAQQAxACwAIABvAHIAIAAnAFMAaABlAGUAdAAxACcAIQBBADEAXABuACAAIAAgACAAIAAgACAAIAArACAAcgBlAG0AbwB2AGUAXwBlAHgAdABlAG4AcwBpAG8AbgAgACAAPQAgACgAbwBwAHQAaQBvAG4AYQBsACkAIABBACAAVABSAFUARQAvAEYAQQBMAFMARQAgAG8AcgAgADEALwAwACAAdgBhAGwAdQBlACAAdABvACAAZABlAHQAZQByAG0AaQBuAGUAIAB3AGgAZQB0AGgAZQByACAAdABvACAAcgBlAG0AbwB2AGUAIAB0AGgAZQAgAGYAaQBsAGUAIABlAHgAdABlAG4AcwBpAG8AbgAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAbwByAGsAYgBvAG8AawAgAGYAaQBsAGUAbgBhAG0AZQBcAG4AIAAgACAAIABFAHIAcgBvAHIAIABjAG8AZABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgACMAWwBFAHIAcgBvAHIAOgAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHIAZQBxAHUAaQByAGUAZABdACAAIAAgAD0AIAB0AGgAZQAgAGMAZQBsAGwAXwByAGUAZgAgAHAAYQByAGEAbQBlAHQAZQByACAAcgBlAHEAdQBpAHIAZQBzACAAYQAgAHYAYQBsAGkAZAAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgACMAWwBFAHIAcgBvAHIAOgAgAFcAbwByAGsAYgBvAG8AawAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAXQAgACAAIAAgAD0AIAB0AGgAZQAgAFcAbwByAGsAYgBvAG8AawAgAGYAaQBsAGUAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkACAAZgBpAHIAcwB0ACAAaQBuACAAbwByAGQAZQByACAAZgBvAHIAIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAHQAbwAgAHcAbwByAGsAIABjAG8AcgByAGUAYwB0AGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACMAWwBFAHIAcgBvAHIAIAByAGUAYQBkAGkAbgBnACAAVwBvAHIAawBiAG8AbwBrACAAbgBhAG0AZQBdACAAIAAgACAAIAAgAD0AIABhAG4AIABlAHIAcgBvAHIAIABvAGMAYwB1AHIAcgBlAGQAIABnAGUAdAB0AGkAbgBnACAAdABoAGUAIABmAGkAbABlAG4AYQBtAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGUAeAB0AHIAYQBjAHQAaQBuAGcAIAB0AGgAZQAgAFcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUAIABmAHIAbwBtACAAdABoAGUAIABmAGkAbABlAG4AYQBtAGUAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIABOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABUAGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AdQB0AHAAdQB0AHMAIABjAHUAcwB0AG8AbQAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAcwAgAGEAcwAgAHMAdAByAGkAbgBnAHMAOwAgAHQAaABlAHMAZQAgAHcAaQBsAGwAIABuAG8AdAAgAGIAZQAgAGYAbABhAGcAZwBlAGQAIABiAHkAIABFAHgAYwBlAGwAIABvAHIAIABhAG4AeQAgAGEAZABkAC0AaQBuAHMAIABhAHMAIABlAHIAcgBvAHIAIABjAGUAbABsAHMALgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABBAGwAdABlAHIAbgBhAHQAaQB2AGUAbAB5ACwAIAB0AGgAZQAgAGMAdQBzAHQAbwBtACAAZQByAHIAbwByACAAbQBlAHMAcwBhAGcAZQBzACAAYwBhAG4AIABiAGUAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAbgBhAHQAaQB2AGUAIABFAHgAYwBlAGwAIABlAHIAcgBvAHIAIABjAG8AZABlAHMAIABzAG8AIAB0AGgAYQB0ACAAdABoAGUAIABlAHIAcgBvAHIAIABpAHMAIABmAGwAYQBnAGcAZQBkACAAaQBuACAAdABoAGUAIABuAG8AcgBtAGEAbAAgAHcAYQB5ADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAB0AG8AIABkAG8AIAB0AGgAaQBzADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQAgAHIAZQBwAGwAYQBjAGUAIAB0AGgAZQAgAFwAIgAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQBcACIAIABzAHQAcgBpAG4AZwAgAHcAaQB0AGgAIAB0AGgAZQAgACMAVgBBAEwAVQBFACEAIAAoAG8AcgAgACMAUgBFAEYAIQApACAAZQByAHIAbwByACAAYwBvAGQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAtACAAcgBlAHAAbABhAGMAZQAgAHQAaABlACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAFcAbwByAGsAYgBvAG8AawAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAXQBcACIAIABhAG4AZAAgAFwAIgAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUAXQBcACIAIABzAHQAcgBpAG4AZwBzACAAdwBpAHQAaAAgAEwAQQBNAEIARABBACgAMAApACAAaQBuACAAbwByAGQAZQByACAAdABvACAAYwByAGUAYQB0AGUAIABhACAAIwBDAEEATABDACEAIABlAHIAcgBvAHIAIABjAG8AZABlAFwAbgAqAC8AXABuAFIAWABMAF8AVwBvAHIAawBiAG8AbwBrAE4AYQBtAGUAIAA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAcgBhAG0AZQB0AGUAcgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcAG4AIAAgACAAIABjAGUAbABsAF8AcgBlAGYALABcAG4AIAAgACAAIABbAHIAZQBtAG8AdgBlAF8AZQB4AHQAZQBuAHMAaQBvAG4AXQAsAFwAbgAgACAAIAAgAC8ALwAgAE0AYQBpAG4AIABmAHUAbgBjAHQAaQBvAG4AIABiAG8AZAB5AC8AYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFUAcABkAGEAdABlACAAdABoAGUAIABvAHAAdABpAG8AbgBhAGwAIABpAG4AcAB1AHQAIAB0AG8AIABhACAAZABlAGYAYQB1AGwAdAAgAG8AZgAgAEYAYQBsAHMAZQAgAGkAZgAgAG8AbQBpAHQAdABlAGQAIABvAHIAIABhACAAbgBvAG4ALQBCAG8AbwBsAGUAYQBuAC8AbgBvAG4ALQBuAHUAbQBlAHIAaQBjACAAdgBhAGwAdQBlACAAaQBzACAAcwB1AHAAcABsAGkAZQBkAFwAbgAgACAAIAAgACAAIAAgACAAXwBlAHgAdABDAGgAawAsACAAQQBOAEQAKAAgAE4ATwBUACgASQBTAEwATwBHAEkAQwBBAEwAKAByAGUAbQBvAHYAZQBfAGUAeAB0AGUAbgBzAGkAbwBuACkAKQAsACAATgBPAFQAKABJAFMATgBVAE0AQgBFAFIAKAByAGUAbQBvAHYAZQBfAGUAeAB0AGUAbgBzAGkAbwBuACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIABfAGYAaQBsAGUARQB4AHQALAAgAEkARgAoACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoACAASQBTAE8ATQBJAFQAVABFAEQAKAByAGUAbQBvAHYAZQBfAGUAeAB0AGUAbgBzAGkAbwBuACkALAAgAF8AZQB4AHQAQwBoAGsAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAQQBMAFMARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBvAHYAZQBfAGUAeAB0AGUAbgBzAGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBoAGUAYwBrACAAdABoAGEAdAAgAHQAaABlACAAYwBlAGwAbABfAHIAZQBmACAAaQBuAHAAdQB0ACAAcwB1AHAAcABsAGkAZQBkACAAaQBzACAAYQAgAHYAYQBsAGkAZAAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgAF8AaQBuAHAAQwBoAGsALAAgAEkARgAoACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAFIARQBGACgAYwBlAGwAbABfAHIAZQBmACkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQBcACIALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARwBlAHQAIAB0AGgAZQAgAGYAaQBsAGUAbgBhAG0AZQAgAHMAdAByAGkAbgBnACAAdQBzAGkAbgBnACAAdABoAGUAIABuAGEAdABpAHYAZQAgAEMARQBMAEwAKAApACAAZgB1AG4AYwB0AGkAbwBuACAAYQBuAGQAIAB0AGgAZQAgAGMAZQBsAGwAXwByAGUAZgAgAGEAcgBnAHUAbQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgAF8AZgBpAGwAZQBOAGEAbQBlACwAIABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAGMAZQBsAGwAXwByAGUAZgApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABVAHMAZQAgAGEAIABjAG8AbQBiAGkAbgBhAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAFQARQBYAFQAQQBGAFQARQBSACgAKQAgAGEAbgBkACAAVABFAFgAVABCAEUARgBPAFIARQAoACkAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHQAbwAgAGcAZQB0ACAAdABoAGUAIAB3AG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlACAAZgByAG8AbQAgAHQAaABlACAAZgBpAGwAZQBuAGEAbQBlACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABfAHMAdAByAE4AYQBtAGUALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKAAgAFQARQBYAFQAQQBGAFQARQBSACgAXwBmAGkAbABlAE4AYQBtAGUALAAgAFwAIgBbAFwAIgAsACAALQAxACwAIAAsACAALAAgAFwAIgAjAFwAIgApACwAIABcACIAXQBcACIALAAgAC0AMQAsACAALAAgACwAIABcACIAIwBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAG0AbwB2AGUAIAB0AGgAZQAgAGYAaQBsAGUAIABlAHgAdABlAG4AcwBpAG8AbgAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUAIABzAHQAcgBpAG4AZwAgAGEAcwAgAHIAZQBxAHUAaQByAGUAZABcAG4AIAAgACAAIAAgACAAIAAgAF8AdwBiAE4AYQBtAGUALAAgAEkARgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGYAaQBsAGUARQB4AHQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUAEIARQBGAE8AUgBFACgAXwBzAHQAcgBOAGEAbQBlACwAIABcACIALgBcACIALAAgAC0AMQAsACAALAAgACwAIABfAHMAdAByAE4AYQBtAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AcwB0AHIATgBhAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEQAZQB0AGUAcgBtAGkAbgBlACAAdwBoAGUAdABoAGUAcgAgAHQAbwAgAHIAZQB0AHUAcgBuACAAYQBuACAAZQByAHIAbwByACAAbQBlAHMAcwBhAGcAZQAgAG8AcgAgAHQAaABlACAAdwBvAHIAawBiAG8AbwBrACAAbgBhAG0AZQAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAXwByAHQAbgAsACAASQBGAFMAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwBmAGkAbABlAE4AYQBtAGUAIAA9ACAAXAAiAFwAIgAsACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAFcAbwByAGsAYgBvAG8AawAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAXQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAIABJAFMARQBSAFIATwBSACgAXwB3AGIATgBhAG0AZQApACwAIABfAHcAYgBOAGEAbQBlACAAPQAgAFwAIgAjAFwAIgApACwAIABcACIAIwBbAEUAcgByAG8AcgAgAHIAZQBhAGQAaQBuAGcAIABXAG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlAF0AXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAFUARQAsACAAXwB3AGIATgBhAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbABsAHkAIABkAGUAdABlAHIAbQBpAG4AZQAgAHcAaABlAHQAaABlAHIAIAB0AG8AIAByAGUAdAB1AHIAbgAgAGEAbgAgAGkAbgBwAHUAdAAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAIABvAHIAIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABfAGkAbgBwAEMAaABrACAAPAA+ACAAXAAiAFwAIgAsACAAXwBpAG4AcABDAGgAawAsACAAXwByAHQAbgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAgACAAUgBYAEwAXwBGAGkAbABlAFAAYQB0AGgAIABGAHUAbgBjAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAB2AGUAcgBzAGkAbwBuACAAMQAuADAANAAgACAAKAAyADMALQBNAGEAcgAtADIAMAAyADUAKQBcAG4AIAAgACAAIAAgACAAIAAgAFIAIABTAGkAbABrACwAIABSAFgATAAgAEQAZQB2AGUAbABvAHAAbQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgAGgAdAB0AHAAcwA6AC8ALwBnAGkAcwB0AC4AZwBpAHQAaAB1AGIALgBjAG8AbQAvAHIALQBzAGkAbABrAC8AMgA2ADUAZAA5AGEAZAAxAGUAMwA2AGUANwAwAGYAMQAxADIAYQA3ADEAYgA3AGEAZAAwAGQAZQBmADQAOABmAFwAbgAqAC8AXABuAC8AKgBcAG4AIAAgACAAIABOAGEAbQBlADoAIAAgACAAIAAgACAAIAAgAEYAaQBsAGUAUABhAHQAaAAoACkAXABuACAAIAAgACAARABlAHMAYwByAGkAcAB0AGkAbwBuADoAIAAqAC8ALwAqACoAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAVwBvAHIAawBiAG8AbwBrACAAZgBpAGwAZQAgAHAAYQB0AGgALAAgAHcAaQB0AGgAIABvAHIAIAB3AGkAdABoAG8AdQB0ACAAdABoAGUAIABmAHUAbABsACAAZgBpAGwAZQAgAG4AYQBtAGUALAAgAGYAbwByACAAdABoAGUAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIABwAHIAbwB2AGkAZABlAGQAOwAgAFcAbwByAGsAYgBvAG8AawAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAIABmAGkAcgBzAHQAKgAvAC8AKgBcAG4AIAAgACAAIABQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAIAAgACAAIAArACAAYwBlAGwAbABfAHIAZQBmACAAIAAgACAAIAAgACAAIAAgACAAPQAgACgAcgBlAHEAdQBpAHIAZQBkACkAIABBACAAdgBhAGwAaQBkACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlACwAIABlAC4AZwAuACAAQQAxACwAIABvAHIAIAAnAFMAaABlAGUAdAAxACcAIQBBADEAXABuACAAIAAgACAAIAAgACAAIAArACAAcgBlAG0AbwB2AGUAXwBsAGEAcwB0AF8AYwBoAGEAcgAgACAAPQAgACgAbwBwAHQAaQBvAG4AYQBsACkAIABBACAAVABSAFUARQAvAEYAQQBMAFMARQAgAG8AcgAgADEALwAwACAAdgBhAGwAdQBlACAAdABvACAAZABlAHQAZQByAG0AaQBuAGUAIAB3AGgAZQB0AGgAZQByACAAdABvACAAcgBlAG0AbwB2AGUAIAB0AGgAZQAgAGwAYQBzAHQAIABjAGgAYQByAGEAYwB0AGUAcgAgAGkAbgAgAHQAaABlACAAZgBpAGwAZQAgAHAAYQB0AGgAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACsAIABpAG4AYwBfAGYAaQBsAGUAXwBuAGEAbQBlACAAIAAgACAAIAA9ACAAKABvAHAAdABpAG8AbgBhAGwAKQAgAEEAIABUAFIAVQBFAC8ARgBBAEwAUwBFACAAbwByACAAMQAvADAAIAB2AGEAbAB1AGUAIAB0AG8AIABkAGUAdABlAHIAbQBpAG4AZQAgAHcAaABlAHQAaABlAHIAIAB0AG8AIABpAG4AYwBsAHUAZABlACAAdABoAGUAIABmAHUAbABsACAAZgBpAGwAZQAgAG4AYQBtAGUAIAB3AGkAdABoACAAZgBpAGwAZQAgAGUAeAB0AGUAbgBzAGkAbwBuAFwAbgAgACAAIAAgAEUAcgByAG8AcgAgAGMAbwBkAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIwBbAEUAcgByAG8AcgA6ACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlACAAcgBlAHEAdQBpAHIAZQBkAF0AIAAgACAAPQAgAHQAaABlACAAYwBlAGwAbABfAHIAZQBmACAAcABhAHIAYQBtAGUAdABlAHIAIAByAGUAcQB1AGkAcgBlAHMAIABhACAAdgBhAGwAaQBkACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAIAAgACAAIAAgACAAIwBbAEUAcgByAG8AcgA6ACAAaQBuAHYAYQBsAGkAZAAgAG8AcAB0AGkAbwBuAGEAbAAgAGkAbgBwAHUAdABdACAAIAAgACAAPQAgAGUAaQB0AGgAZQByACAAdABoAGUAIAByAGUAbQBvAHYAZQBfAGwAYQBzAHQAXwBjAGgAYQByACAAbwB0ACAAaQBuAGMAXwBmAGkAbABlAF8AbgBhAG0AZQAgAGkAbgBwAHUAdABzACAAYQByAGUAIABuAG8AdAAgAGEAIABsAG8AZwBpAGMAYQBsACAAKABUAFIAVQBFAC8ARgBBAEwAUwBFACkAIABvAHIAIABuAHUAbQBlAHIAaQBjACAAdgBhAGwAdQBlAFwAbgAgACAAIAAgACAAIAAgACAAIwBbAEUAcgByAG8AcgA6ACAAVwBvAHIAawBiAG8AbwBrACAAbQB1AHMAdAAgAGIAZQAgAHMAYQB2AGUAZABdACAAIAAgACAAPQAgAHQAaABlACAAVwBvAHIAawBiAG8AbwBrACAAZgBpAGwAZQAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAIABmAGkAcgBzAHQAIABpAG4AIABvAHIAZABlAHIAIABmAG8AcgAgAHQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAdABvACAAdwBvAHIAawAgAGMAbwByAHIAZQBjAHQAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIwBbAEUAcgByAG8AcgAgAHIAZQBhAGQAaQBuAGcAIABGAGkAbABlACAAUABhAHQAaABdACAAIAAgACAAIAAgACAAIAAgACAAPQAgAGEAbgAgAGUAcgByAG8AcgAgAG8AYwBjAHUAcgByAGUAZAAgAGcAZQB0AHQAaQBuAGcAIAB0AGgAZQAgAGYAaQBsAGUAIABuAGEAbQBlACAAcwB0AHIAaQBuAGcAIABvAHIAIABlAHgAdAByAGEAYwB0AGkAbgBnACAAdABoAGUAIABmAGkAbABlACAAcABhAHQAaAAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAaQBsAGUAIABuAGEAbQBlACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUAXQAgACAAIAAgACAAIAA9ACAAYQBuACAAZQByAHIAbwByACAAbwBjAGMAdQByAHIAZQBkACAAZwBlAHQAdABpAG4AZwAgAHQAaABlACAAZgBpAGwAZQAgAG4AYQBtAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGUAeAB0AHIAYQBjAHQAaQBuAGcAIAB0AGgAZQAgAFcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUAIABmAHIAbwBtACAAdABoAGUAIABmAGkAbABlACAAbgBhAG0AZQAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAALQAgAFQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAbwB1AHQAcAB1AHQAcwAgAGMAdQBzAHQAbwBtACAAZQByAHIAbwByACAAbQBlAHMAcwBhAGcAZQBzACAAYQBzACAAcwB0AHIAaQBuAGcAcwA7ACAAdABoAGUAcwBlACAAdwBpAGwAbAAgAG4AbwB0ACAAYgBlACAAZgBsAGEAZwBnAGUAZAAgAGIAeQAgAEUAeABjAGUAbAAgAG8AcgAgAGEAbgB5ACAAYQBkAGQALQBpAG4AcwAgAGEAcwAgAGUAcgByAG8AcgAgAGMAZQBsAGwAcwAuAFwAbgAgACAAIAAgACAAIAAgACAALQAgAEEAbAB0AGUAcgBuAGEAdABpAHYAZQBsAHkALAAgAHQAaABlACAAYwB1AHMAdABvAG0AIABlAHIAcgBvAHIAIABtAGUAcwBzAGEAZwBlAHMAIABjAGEAbgAgAGIAZQAgAHIAZQBwAGwAYQBjAGUAZAAgAHcAaQB0AGgAIABuAGEAdABpAHYAZQAgAEUAeABjAGUAbAAgAGUAcgByAG8AcgAgAGMAbwBkAGUAcwAgAHMAbwAgAHQAaABhAHQAIAB0AGgAZQAgAGUAcgByAG8AcgAgAGkAcwAgAGYAbABhAGcAZwBlAGQAIABpAG4AIAB0AGgAZQAgAG4AbwByAG0AYQBsACAAdwBhAHkAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAHQAbwAgAGQAbwAgAHQAaABpAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAtACAAcgBlAHAAbABhAGMAZQAgAHQAaABlACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHIAZQBxAHUAaQByAGUAZABdAFwAIgAgAHMAdAByAGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAIwBWAEEATABVAEUAIQAgACgAbwByACAAIwBSAEUARgAhACkAIABlAHIAcgBvAHIAIABjAG8AZABlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AIAByAGUAcABsAGEAYwBlACAAdABoAGUAIABcACIAIwBbAEUAcgByAG8AcgA6ACAAaQBuAHYAYQBsAGkAZAAgAG8AcAB0AGkAbwBuAGEAbAAgAGkAbgBwAHUAdABdAFwAIgAgAHMAdAByAGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAIwBWAEEATABVAEUAIQAgAGUAcgByAG8AcgAgAGMAbwBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQAgAHIAZQBwAGwAYQBjAGUAIAB0AGgAZQAgAFwAIgAjAFsARQByAHIAbwByADoAIABXAG8AcgBrAGIAbwBvAGsAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkAF0AXAAiACwAIABcACIAIwBbAEUAcgByAG8AcgAgAHIAZQBhAGQAaQBuAGcAIABGAGkAbABlACAAUABhAHQAaABdAFwAIgAsACAAYQBuAGQAIABcACIAIwBbAEUAcgByAG8AcgAgAHIAZQBhAGQAaQBuAGcAIABTAGgAZQBlAHQAIABuAGEAbQBlAF0AXAAiACAAcwB0AHIAaQBuAGcAcwAgAHcAaQB0AGgAIABMAEEATQBCAEQAQQAoADAAKQAgAGkAbgAgAG8AcgBkAGUAcgAgAHQAbwAgAGMAcgBlAGEAdABlACAAYQAgACMAQwBBAEwAQwAhACAAZQByAHIAbwByACAAYwBvAGQAZQBcAG4AKgAvAFwAbgBSAFgATABfAEYAaQBsAGUAUABhAHQAaAAgAD0AIABMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAC8ALwAgAFAAYQByAGEAbQBlAHQAZQByACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAbgAgACAAIAAgAGMAZQBsAGwAXwByAGUAZgAsAFwAbgAgACAAIAAgAFsAcgBlAG0AbwB2AGUAXwBsAGEAcwB0AF8AYwBoAGEAcgBdACwAXABuACAAIAAgACAAWwBpAG4AYwBfAGYAaQBsAGUAXwBuAGEAbQBlAF0ALABcAG4AIAAgACAAIAAvAC8AIABNAGEAaQBuACAAZgB1AG4AYwB0AGkAbwBuACAAYgBvAGQAeQAvAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABJAG4AcAB1AHQAIABjAGgAZQBjAGsAcwBcAG4AIAAgACAAIAAgACAAIAAgAF8AYwBoAHIAQwBoAGsALAAgAEEATgBEACgAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAcgBlAG0AbwB2AGUAXwBsAGEAcwB0AF8AYwBoAGEAcgApACkALAAgAE4ATwBUACgASQBTAEwATwBHAEkAQwBBAEwAKAByAGUAbQBvAHYAZQBfAGwAYQBzAHQAXwBjAGgAYQByACkAKQAsACAATgBPAFQAKABJAFMATgBVAE0AQgBFAFIAKAByAGUAbQBvAHYAZQBfAGwAYQBzAHQAXwBjAGgAYQByACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIABfAGYAbgBtAEMAaABrACwAIABBAE4ARAAoACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGkAbgBjAF8AZgBpAGwAZQBfAG4AYQBtAGUAKQApACwAIABOAE8AVAAoAEkAUwBMAE8ARwBJAEMAQQBMACgAaQBuAGMAXwBmAGkAbABlAF8AbgBhAG0AZQApACkALAAgAE4ATwBUACgASQBTAE4AVQBNAEIARQBSACgAaQBuAGMAXwBmAGkAbABlAF8AbgBhAG0AZQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwByAGUAZgBDAGgAawAsACAATgBPAFQAKABJAFMAUgBFAEYAKABjAGUAbABsAF8AcgBlAGYAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABEAGUAYQBsAGkAbgBnACAAdwBpAHQAaAAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMALAAgAHMAZQB0AHQAaQBuAGcAIABkAGUAZgBhAHUAbAB0ACAAdgBhAGwAdQBlAHMAIABpAGYAIABvAG0AaQB0AHQAZQBkAFwAbgAgACAAIAAgACAAIAAgACAAXwBsAGEAcwB0AEMAaAByACwAIABJAEYAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAIABJAFMATwBNAEkAVABUAEUARAAoAHIAZQBtAG8AdgBlAF8AbABhAHMAdABfAGMAaABhAHIAKQAsACAAXwBjAGgAcgBDAGgAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAQQBMAFMARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBvAHYAZQBfAGwAYQBzAHQAXwBjAGgAYQByAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwBpAG4AYwBGAGkAbABlACwAIABJAEYAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAIABJAFMATwBNAEkAVABUAEUARAAoAGkAbgBjAF8AZgBpAGwAZQBfAG4AYQBtAGUAKQAsACAAXwBmAG4AbQBDAGgAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAQQBMAFMARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAG4AYwBfAGYAaQBsAGUAXwBuAGEAbQBlAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARwBlAHQAIAB0AGgAZQAgAGYAdQBsAGwAIABmAGkAbABlACAAcABhAHQAaAAgAGEAbgBkACAAbgBhAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgAF8AZgB1AGwAbAAsACAAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABjAGUAbABsAF8AcgBlAGYAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAHQAaABlACAAZgBpAGwAZQAgAHAAYQB0AGgAIABvAG4AbAB5AFwAbgAgACAAIAAgACAAIAAgACAAXwBwAGEAdABoACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgAXwBmAHUAbABsACwAIABcACIAWwBcACIALAAgAC0AMQAsACAALAAgACwAIABcACIAIwBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwBmAGkAbABlAFAAYQB0AGgALAAgAEkARgAoAF8AbABhAHMAdABDAGgAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUARgBUACgAXwBwAGEAdABoACwAIABMAEUATgAoAF8AcABhAHQAaAApACAALQAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAHAAYQB0AGgAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABXAG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlACAAZQBsAGUAbQBlAG4AdAAgAGkAbgBjAC4AIABmAGkAbABlACAAZQB4AHQAZQBuAHMAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIABfAHcAYgBOAGEAbQBlACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgAIABUAEUAWABUAEEARgBUAEUAUgAoAF8AZgB1AGwAbAAsACAAXAAiAFsAXAAiACwAIAAtADEALAAgACwAIAAsACAAXAAiACMAXAAiACkALAAgAFwAIgBdAFwAIgAsACAALQAxACwAIAAsACAALAAgAFwAIgAjAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAIABmAG8AcgAgAGkAbgBwAHUAdAAgAGUAcgByAG8AcgBzACAAYQBuAGQAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AIABlAHIAcgBvAHIAcwAsACAAYQBuAGQAIABzAGUAdAAgAHQAaABlACAAYQBwAHAAcgBvAHAAcgBpAGEAdABlACAAZQByAHIAbwByACAAbQBlAHMAcwBhAGcAZQBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE4AbwB0AGUAIAAtACAAZQByAHIAbwByAHMAIABwAGwAYQBjAGUAZAAgAGkAbgAgAG8AcgBkAGUAcgAgAG8AZgAgAGkAbQBwAG8AcgB0AGEAbgBjAGUALwByAGUAcABvAHIAdABpAG4AZwAgAGEAcwAgAG8AbgBsAHkAIABhACAAcwBpAG4AZwBsAGUAIABtAGUAcwBzAGEAZwBlACAAaQBzACAAcgBlAHQAdQByAG4AZQBkACAAZgBvAHIAIABtAHUAbAB0AGkAcABsAGUAIABlAHIAcgBvAHIAcwBcAG4AIAAgACAAIAAgACAAIAAgAF8AZQByAHIAQwBoAGsALAAgAEkARgBTACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AcgBlAGYAQwBoAGsALAAgAFwAIgAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwBmAHUAbABsACAAPQAgAFwAIgBcACIALAAgAFwAIgAjAFsARQByAHIAbwByADoAIABXAG8AcgBrAGIAbwBvAGsAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkAF0AXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAF8AYwBoAHIAQwBoAGsALAAgAF8AZgBuAG0AQwBoAGsAKQAsACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAGkAbgB2AGEAbABpAGQAIABvAHAAdABpAG8AbgBhAGwAIABpAG4AcAB1AHQAXQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAIABJAFMARQBSAFIATwBSACgAXwBmAGkAbABlAFAAYQB0AGgAKQAsACAAXwBmAGkAbABlAFAAYQB0AGgAIAA9ACAAXAAiACMAXAAiACkALAAgAFwAIgAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAEYAaQBsAGUAIABQAGEAdABoAF0AXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAIABPAFIAKAAgAEkAUwBFAFIAUgBPAFIAKABfAHcAYgBOAGEAbQBlACkALAAgAF8AdwBiAE4AYQBtAGUAIAA9ACAAXAAiACMAXAAiACkALAAgAF8AaQBuAGMARgBpAGwAZQApACwAIABcACIAIwBbAEUAcgByAG8AcgAgAHIAZQBhAGQAaQBuAGcAIABXAG8AcgBrAGIAbwBvAGsAIABOAGEAbQBlAF0AXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAUgBVAEUALAAgAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAG8AbgBzAHQAcgB1AGMAdAAgAHQAaABlACAAcgBlAHEAdQBpAHIAZQBkACAAbwB1AHQAcAB1AHQAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgAF8AcgB0AG4ALAAgAEkARgAoAF8AaQBuAGMARgBpAGwAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAHAAYQB0AGgAIAAmACAAXwB3AGIATgBhAG0AZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGYAaQBsAGUAUABhAHQAaABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAaQBuAGEAbAAgAGMAaABlAGMAawAgAC0AIABpAGYAIABhAG4AIABlAHIAcgBvAHIAIABtAGUAcwBzAGEAZwBlACAAaQBzACAAcAByAGUAcwBlAG4AdAAgAHIAZQB0AHUAcgBuACAAdABoAGEAdAAsACAAbwB0AGgAZQByAHcAaQBzAGUAIAByAGUAdAB1AHIAbgAgAHQAaABlACAAYwBvAG4AcwB0AHIAdQBjAHQAZQBkACAAbwB1AHQAcAB1AHQAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAF8AZQByAHIAQwBoAGsAIAA8AD4AIABcACIAXAAiACwAIABfAGUAcgByAEMAaABrACwAIABfAHIAdABuACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBYAEwAXwBXAGIASQBuAGYAbwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4AIAAgACAAIABNAE8ARABVAEwARQA6ACAAIAAgACAAIABSAFgATABfAFcAYgBJAG4AZgBvAFwAbgAgACAAIAAgAEEAVQBUAEgATwBSADoAIAAgACAAIAAgAFIAIABTAGkAbABrACwAIABSAFgATAAgAEQAZQB2AGUAbABvAHAAbQBlAG4AdABcAG4AIAAgACAAIABXAEUAQgBTAEkAVABFADoAIAAgACAAIABoAHQAdABwAHMAOgAvAC8AZQB4AGMAZQBsAC0AYgBpAHQAcwAuAG4AZQB0AFwAbgAgACAAIAAgAEcASQBTAFQAIABVAFIATAA6ACAAIAAgAGgAdAB0AHAAcwA6AC8ALwBnAGkAcwB0AC4AZwBpAHQAaAB1AGIALgBjAG8AbQAvAHIALQBzAGkAbABrAC8AOQBjADEAOAAwADkAMABmADYAMABmAGYAZQA0ADQAMgBiADcAZAAyADIAZQA2ADAANQA4AGUAOAAzAGUANABhAFwAbgAgACAAIAAgAFYARQBSAFMASQBPAE4AOgAgACAAIAAgADEALgAwADYAIAAoAEEAcAByAC0AMgAwADIANQApAFwAbgAqAC8AXABuAC8AKgBcAG4AIAAgACAAIABOAGEAbQBlADoAIAAgACAAIAAgACAAIAAgAEEAYgBvAHUAdAAoACkAXABuACAAIAAgACAAVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAxAC4AMQAwACAAKAAyADMALQBBAHAAcgAtADIAMAAyADUAKQAgAC0ALQAgAFIAIABTAGkAbABrACwAIABSAFgATAAgAEQAZQB2AGUAbABvAHAAbQBlAG4AdABcAG4AIAAgACAAIABEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgAgACoALwAvACoAKgBQAHIAbwB2AGkAZABlAHMAIABpAG4AZgBvAHIAbQBhAHQAaQBvAG4AIABhAGIAbwB1AHQAIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgBzACAAaQBuACAAdABoAGkAcwAgAG0AbwBkAHUAbABlACoALwAvACoAXABuACAAIAAgACAAUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAKwAgAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuACAAIAAgAD0AIAAoAG8AcAB0AGkAbwBuAGEAbAApACAAdABoAGUAIABuAGEAbQBlACAAbwByACAAaQBuAGQAZQB4ACAAbgB1AG0AYgBlAHIAIABvAGYAIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAHQAaABhAHQAIAB1AHMAZQByACAAdwBhAG4AdABzACAAaQBuAGYAbwByAG0AYQB0AGkAbwBuACAAYQBiAG8AdQB0AFwAbgAgACAAIAAgAEUAcgByAG8AcgAgAGMAbwBkAGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIwBbAEUAcgByAG8AcgA6ACAAbgBhAG0AZQAgAG4AbwB0ACAAcgBlAGMAbwBnAG4AaQBzAGUAZABdACAAIAAgAD0AIAB0AGgAZQAgAHAAcgBvAHYAaQBkAGUAZAAgAG4AYQBtAGUAIABzAHQAcgBpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG0AYQB0AGMAaAAgAHQAaABvAHMAZQAgAGkAbgAgAHQAaABlACAAbQBvAGQAdQBsAGUAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByADoAIABpAG4AZABlAHgAIABuAG8AdAAgAHIAZQBjAG8AZwBuAGkAcwBlAGQAXQAgACAAPQAgAHQAaABlACAAcAByAG8AdgBpAGQAZQBkACAAaQBuAGQAZQB4ACAAbgB1AG0AYgBlAHIAIABkAG8AZQBzACAAbgBvAHQAIABtAGEAdABjAGgAIAB0AGgAbwBzAGUAIABpAG4AIAB0AGgAZQAgAG0AbwBkAHUAbABlAFwAbgAgACAAIAAgAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAALQAgAGkAZgAgAHQAaABlACAAcwBlAGwAZQBjAHQAXwBmAHUAbgBjAHQAaQBvAG4AIABpAG4AcAB1AHQAIABpAHMAIABvAG0AaQB0AHQAZQBkACAAbwByACAAYQBuACAAaQBuAGQAZQB4ACAAbwBmACAAMAAgAGkAcwAgAHAAcgBvAHYAaQBkAGUAZAAgAHQAaABlAG4AIABhACAAdABhAGIAbABlACAAbwBmACAAaQBuAGYAbwByAG0AYQB0AGkAbwBuACAAYQBiAG8AdQB0ACAAdABoAGUAIABtAG8AZAB1AGwAZQAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZABcAG4AIAAgACAAIAAgACAAIAAgAC0AIAB0AGgAZQAgAHUAcwBlAHIAIABjAGEAbgAgAGUAaQB0AGgAZQByACAAcAByAG8AdgBpAGQAZQAgAHQAaABlACAAaQBuAGQAZQB4ACAAbwBmACAAdABoAGUAIABjAGgAbwBzAGUAbgAgAGYAdQBuAGMAdABpAG8AbgAgAGEAcwAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAIAAoADEAKwApACwAIABvAHIAIAB0AGgAZQAgAG4AYQBtAGUAIABvAGYAIAB0AGgAZQAgAGMAaABvAHMAZQBuACAAZgB1AG4AYwB0AGkAbwBuACAAYQBzACAAYQAgAHMAdAByAGkAbgBnAFwAbgBcAG4AKgAvAFwAbgBBAGIAbwB1AHQAIAA9ACAATABBAE0AQgBEAEEAKABbAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAXwBuAHUAbQAsACAASQBGACgAIABJAFMATwBNAEkAVABUAEUARAAoAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuACkALAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAIABJAFMATgBVAE0AQgBFAFIAKABzAGUAbABlAGMAdABfAGYAdQBuAGMAdABpAG8AbgApACwAIABJAE4AVAAoAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAjAFwAIgApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwBhAHIAcgBEAGUAZgAsACAASQBGACgAXwBuAHUAbQAgAD0AIAAwACwAIABUAEUAWABUAFMAUABMAEkAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBiAG8AdQB0ADoArABSAFgATAAgAFcAbwByAGsAYgBvAG8AawAgAEkAbgBmAG8AIABmAHUAbgBjAHQAaQBvAG4AcwAuAHwAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAKwAUwB1AGcAZwBlAHMAdABlAGQAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAIAA9ACAAUgBYAEwAXwBXAGIASQBuAGYAbwB8AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBzAGkAbwBuADoArAB2ADEALgAwADYAIAAgACgAQQBwAHIAaQBsACAAMgAwADIANQApAHwAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQB0AGgAbwByADoArABSACAAUwBpAGwAawAsACAAUgBYAEwAIABEAGUAdgBlAGwAbwBwAG0AZQBuAHQAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBSAEwAOgCsAGgAdAB0AHAAcwA6AC8ALwBnAGkAcwB0AC4AZwBpAHQAaAB1AGIALgBjAG8AbQAvAHIALQBzAGkAbABrAC8AOAAxADYAMAA4ADYANgBjADEANQBkADYAMQA4ADQAZAA0ADkANQA4ADUANwA5ADkAMgA4ADYANAA3ADMANwAxAHwAXAAiACYAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgCsAHwAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBuAGMAdABpAG8AbgCsAEQAZQBzAGMAcgBpAHAAdABpAG8AbgB8AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAwACAALQAgAEEAYgBvAHUAdACsAFAAcgBvAHYAaQBkAGUAcwAgAGkAbgBmAG8AcgBtAGEAdABpAG8AbgAgAGEAYgBvAHUAdAAgAHQAaABlACAAZgB1AG4AYwB0AGkAbwBuAHMAIABpAG4AIAB0AGgAaQBzACAAbQBvAGQAdQBsAGUAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAgAC0AIABTAGgAZQBlAHQATgBhAG0AZQCsAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABXAG8AcgBrAHMAaABlAGUAdAAgAG4AYQBtAGUAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMgAgAC0AIABXAG8AcgBrAGIAbwBvAGsATgBhAG0AZQCsAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABXAG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlAHwAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAIAAtACAARgBpAGwAZQBQAGEAdABoAKwAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAcgBlAGYAZQByAGUAbgBjAGUAZAAgAFcAbwByAGsAYgBvAG8AawAgAGYAaQBsAGUAIABwAGEAdABoAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIArABcACIALAAgAFwAIgB8AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABfAGEAcgByAE4AYQBtAGUAcwAsACAAVABFAFgAVABTAFAATABJAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAdABOAGEAbQBlAKYAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAbwByAGsAYgBvAG8AawBOAGEAbQBlAKYAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQBsAGUAUABhAHQAaABcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAKYAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwBhAHIAcgBIAGUAbABwACwAIABUAEUAWABUAFMAUABMAEkAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBBAE0ARQA6AKwAUwBoAGUAZQB0AE4AYQBtAGUAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARABFAFMAQwBSAEkAUABUAEkATwBOADoArABSAGUAdAB1AHIAbgBzACAAdABoAGUAIAByAGUAZgBlAHIAZQBuAGMAZQBkACAAdwBvAHIAawBzAGgAZQBlAHQAIABuAGEAbQBlAHwAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYARQBSAFMASQBPAE4AOgCsAHYAMQAuADAANAAgACAAKAAyADMALQBNAGEAcgAtADIAMAAyADUAKQB8AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEEAUgBBAE0ARQBUAEUAUgBTADoArAB8AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGUAbABsAF8AcgBlAGYArAAoAHIAZQBxAHUAaQByAGUAZAApACAAYQAgAHYAYQBsAGkAZAAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAsACAAZQAuAGcALgAgACcAUwBoAGUAZQB0ADEAJwAhAEEAMQBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIApgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBBAE0ARQA6AKwAVwBvAHIAawBiAG8AbwBrAE4AYQBtAGUAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARABFAFMAQwBSAEkAUABUAEkATwBOADoArABSAGUAdAB1AHIAbgBzACAAdABoAGUAIAByAGUAZgBlAHIAZQBuAGMAZQBkACAAVwBvAHIAawBiAG8AbwBrACAAbgBhAG0AZQB8AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEUAUgBTAEkATwBOADoArAB2ADEALgAwADUAIAAgACgAMgAzAC0ATQBhAHIALQAyADAAMgA1ACkAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUABBAFIAQQBNAEUAVABFAFIAUwA6AKwAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBlAGwAbABfAHIAZQBmAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAGEAIAB2AGEAbABpAGQAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUALAAgAGUALgBnAC4AIAAnAFMAaABlAGUAdAAxACcAIQBBADEAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBlAG0AbwB2AGUAXwBlAHgAdABlAG4AcwBpAG8AbgCsACgAbwBwAHQAaQBvAG4AYQBsACkAIABDAGgAbwBvAHMAZQAgAHcAaABlAHQAaABlAHIAIAB0AG8AIAByAGUAbQBvAHYAZQAgAHQAaABlACAAZgBpAGwAZQAgAGUAeAB0AGUAbgBzAGkAbwBuACAAKABUAHIAdQBlAC8ARgBhAGwAcwBlACkAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAKYAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQQBNAEUAOgCsAEYAaQBsAGUAUABhAHQAaAB8AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAEUAUwBDAFIASQBQAFQASQBPAE4AOgCsAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABXAG8AcgBrAGIAbwBvAGsAIABmAGkAbABlACAAcABhAHQAaAB8AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEUAUgBTAEkATwBOADoArAB2ADEALgAwADQAIAAgACgAMgAzAC0ATQBhAHIALQAyADAAMgA1ACkAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUABBAFIAQQBNAEUAVABFAFIAUwA6AKwAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBlAGwAbABfAHIAZQBmAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAGEAIAB2AGEAbABpAGQAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUALAAgAGUALgBnAC4AIAAnAFMAaABlAGUAdAAxACcAIQBBADEAfABcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBlAG0AbwB2AGUAXwBsAGEAcwB0AF8AYwBoAGEAcgCsACgAbwBwAHQAaQBvAG4AYQBsACkAIABDAGgAbwBvAHMAZQAgAHcAaABlAHQAaABlAHIAIAB0AG8AIAByAGUAbQBvAHYAZQAgAHQAaABlACAAbABhAHMAdAAgAGMAaABhAHIAYQBjAHQAZQByACAAbwBmACAAdABoAGUAIABmAGkAbABlACAAcABhAHQAaAAgACgAVAByAHUAZQAvAEYAYQBsAHMAZQApAHwAXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAbgBjAF8AZgBpAGwAZQBfAG4AYQBtAGUArAAoAG8AcAB0AGkAbwBuAGEAbAApACAAQwBoAG8AbwBzAGUAIAB3AGgAZQB0AGgAZQByACAAdABvACAAYQBkAGQAIAB0AGgAZQAgAGYAaQBsAGUAIABuAGEAbQBlACAAdABvACAAdABoAGUAIABmAGkAbABlACAAcABhAHQAaAAgACgAVAByAHUAZQAvAEYAYQBsAHMAZQApAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIApgBcACIAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABfAGEAcgByAE8AdQB0ACwAIABJAEYAKABfAG4AdQBtACAAPQAgAFwAIgAjAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwBpAGQAeAAsACAAUwBVAE0AKAAgAFMARQBRAFUARQBOAEMARQAoADEALAAgAEMATwBVAE4AVABBACgAXwBhAHIAcgBOAGEAbQBlAHMAKQApACAAKgAgACgAXwBhAHIAcgBOAGEAbQBlAHMAIAA9ACAAcwBlAGwAZQBjAHQAXwBmAHUAbgBjAHQAaQBvAG4AKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABfAGkAZAB4ACAAPgAgADAALAAgAFQARQBYAFQAUwBQAEwASQBUACgAIABJAE4ARABFAFgAKABfAGEAcgByAEgAZQBsAHAALAAgAF8AaQBkAHgAKQAsACAAXAAiAKwAXAAiACwAIABcACIAfABcACIAKQAsACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAG4AYQBtAGUAIABuAG8AdAAgAHIAZQBjAG8AZwBuAGkAcwBlAGQAXQBcACIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABfAG4AdQBtACAAPAA+ACAAMAAsACAASQBGAEUAUgBSAE8AUgAoACAAVABFAFgAVABTAFAATABJAFQAKAAgAEkATgBEAEUAWAAoAF8AYQByAHIASABlAGwAcAAsACAAXwBuAHUAbQApACwAIABcACIArABcACIALAAgAFwAIgB8AFwAIgApACwAIABcACIAIwBbAEUAcgByAG8AcgA6ACAAaQBuAGQAZQB4ACAAbgBvAHQAIAByAGUAYwBvAGcAbgBpAHMAZQBkAF0AXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAXwBhAHIAcgBEAGUAZgAgAD0AIABcACIAXAAiACwAIABfAGEAcgByAE8AdQB0ACwAIABfAGEAcgByAEQAZQBmACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqAFwAbgAgACAAIAAgAE4AYQBtAGUAOgAgACAAIAAgACAAIAAgACAAUwBoAGUAZQB0AE4AYQBtAGUAKAApAFwAbgAgACAAIAAgAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAMQAuADAANAAgACgAMgAzAC0ATQBhAHIALQAyADAAMgA1ACkAIAAtAC0AIABSACAAUwBpAGwAawAsACAAUgBYAEwAIABEAGUAdgBlAGwAbwBwAG0AZQBuAHQAXABuACAAIAAgACAARABlAHMAYwByAGkAcAB0AGkAbwBuADoAIAAqAC8ALwAqACoAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAdwBvAHIAawBzAGgAZQBlAHQAIABuAGEAbQBlACAAKABhAHMAIABkAGkAcwBwAGwAYQB5AGUAZAAgAGkAbgAgAHQAaABlACAAdwBvAHIAawBzAGgAZQBlAHQAIAB0AGEAYgApACAAZgBvAHIAIAB0AGgAZQAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHAAcgBvAHYAaQBkAGUAZAA7ACAAVwBvAHIAawBiAG8AbwBrACAAbQB1AHMAdAAgAGIAZQAgAHMAYQB2AGUAZAAgAGYAaQByAHMAdAAqAC8ALwAqAFwAbgAgACAAIAAgAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgACsAIABjAGUAbABsAF8AcgBlAGYAIAAgACAAIAAgACAAPQAgACgAcgBlAHEAdQBpAHIAZQBkACkAIABBACAAdgBhAGwAaQBkACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlACwAIABlAC4AZwAuACAAQQAxACwAIABvAHIAIAAnAFMAaABlAGUAdAAxACcAIQBBADEAXABuACAAIAAgACAARQByAHIAbwByACAAYwBvAGQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQAgACAAIAA9ACAAdABoAGUAIABjAGUAbABsAF8AcgBlAGYAIABwAGEAcgBhAG0AZQB0AGUAcgAgAHIAZQBxAHUAaQByAGUAcwAgAGEAIAB2AGEAbABpAGQAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByADoAIABXAG8AcgBrAGIAbwBvAGsAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkAF0AIAAgACAAIAA9ACAAdABoAGUAIABXAG8AcgBrAGIAbwBvAGsAIABmAGkAbABlACAAbQB1AHMAdAAgAGIAZQAgAHMAYQB2AGUAZAAgAGYAaQByAHMAdAAgAGkAbgAgAG8AcgBkAGUAcgAgAGYAbwByACAAdABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIAB0AG8AIAB3AG8AcgBrACAAYwBvAHIAcgBlAGMAdABsAHkAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFMAaABlAGUAdAAgAG4AYQBtAGUAXQAgACAAIAAgACAAIAAgACAAIAA9ACAAYQBuACAAZQByAHIAbwByACAAbwBjAGMAdQByAHIAZQBkACAAZwBlAHQAdABpAG4AZwAgAHQAaABlACAAZgBpAGwAZQBuAGEAbQBlACAAcwB0AHIAaQBuAGcAIABvAHIAIABlAHgAdAByAGEAYwB0AGkAbgBnACAAdABoAGUAIAB3AG8AcgBrAHMAaABlAGUAdAAgAG4AYQBtAGUAIABmAHIAbwBtACAAdABoAGUAIABmAGkAbABlAG4AYQBtAGUAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIABOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABUAGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AdQB0AHAAdQB0AHMAIABjAHUAcwB0AG8AbQAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAcwAgAGEAcwAgAHMAdAByAGkAbgBnAHMAOwAgAHQAaABlAHMAZQAgAHcAaQBsAGwAIABuAG8AdAAgAGIAZQAgAGYAbABhAGcAZwBlAGQAIABiAHkAIABFAHgAYwBlAGwAIABvAHIAIABhAG4AeQAgAGEAZABkAC0AaQBuAHMAIABhAHMAIABlAHIAcgBvAHIAIABjAGUAbABsAHMALgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABBAGwAdABlAHIAbgBhAHQAaQB2AGUAbAB5ACwAIAB0AGgAZQAgAGMAdQBzAHQAbwBtACAAZQByAHIAbwByACAAbQBlAHMAcwBhAGcAZQBzACAAYwBhAG4AIABiAGUAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAbgBhAHQAaQB2AGUAIABFAHgAYwBlAGwAIABlAHIAcgBvAHIAIABjAG8AZABlAHMAIABzAG8AIAB0AGgAYQB0ACAAdABoAGUAIABlAHIAcgBvAHIAIABpAHMAIABmAGwAYQBnAGcAZQBkACAAaQBuACAAdABoAGUAIABuAG8AcgBtAGEAbAAgAHcAYQB5ADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAB0AG8AIABkAG8AIAB0AGgAaQBzADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQAgAHIAZQBwAGwAYQBjAGUAIAB0AGgAZQAgAFwAIgAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQBcACIAIABzAHQAcgBpAG4AZwAgAHcAaQB0AGgAIAB0AGgAZQAgACMAVgBBAEwAVQBFACEAIAAoAG8AcgAgACMAUgBFAEYAIQApACAAZQByAHIAbwByACAAYwBvAGQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAtACAAcgBlAHAAbABhAGMAZQAgAHQAaABlACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAFcAbwByAGsAYgBvAG8AawAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAXQBcACIAIABhAG4AZAAgAFwAIgAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFMAaABlAGUAdAAgAG4AYQBtAGUAXQBcACIAIABzAHQAcgBpAG4AZwBzACAAdwBpAHQAaAAgAEwAQQBNAEIARABBACgAMAApACAAaQBuACAAbwByAGQAZQByACAAdABvACAAYwByAGUAYQB0AGUAIABhACAAIwBDAEEATABDACEAIABlAHIAcgBvAHIAIABjAG8AZABlAFwAbgAqAC8AXABuAFMAaABlAGUAdABOAGEAbQBlACAAPQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAALwAvACAAUABhAHIAYQBtAGUAdABlAHIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAbgAgACAAIAAgAGMAZQBsAGwAXwByAGUAZgAsAFwAbgAgACAAIAAgAC8ALwAgAE0AYQBpAG4AIABmAHUAbgBjAHQAaQBvAG4AIABiAG8AZAB5AC8AYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAaABlAGMAawAgAHQAaABhAHQAIABpAG4AcAB1AHQAIABwAHIAbwB2AGkAZABlAGQAIABpAHMAIABhAHMAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUALAAgAG8AdABoAGUAcgB3AGkAcwBlACAAYwByAGUAYQB0AGUAIABhACAAYwB1AHMAdABvAG0AIABlAHIAcgBvAHIAIABtAGUAcwBzAGEAZwBlAFwAbgAgACAAIAAgACAAIAAgACAAXwBpAG4AcABDAGgAawAsACAASQBGACgAIABOAE8AVAAoAEkAUwBSAEUARgAoAGMAZQBsAGwAXwByAGUAZgApACkALAAgAFwAIgAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQBcACIALAAgAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARwBlAHQAIAB0AGgAZQAgAGYAaQBsAGUAbgBhAG0AZQAgAHMAdAByAGkAbgBnACAAdQBzAGkAbgBnACAAdABoAGUAIABuAGEAdABpAHYAZQAgAEMARQBMAEwAKAApACAAZgB1AG4AYwB0AGkAbwBuACAAYQBuAGQAIAB0AGgAZQAgAGMAZQBsAGwAXwByAGUAZgAgAGEAcgBnAHUAbQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgAF8AZgBpAGwAZQBOAGEAbQBlACwAIABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAGMAZQBsAGwAXwByAGUAZgApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABVAHMAZQAgAHQAaABlACAAVABFAFgAVABBAEYAVABFAFIAKAApACAAZgB1AG4AYwB0AGkAbwBuACAAdABvACAAbABvAG8AawAgAGYAbwByACAAdABoAGUAIABmAGkAbgBhAGwAIABcACIAXQBcACIAIABjAGgAYQByAGEAYwB0AGUAcgAgAGkAbgAgAHQAaABlACAAZgBpAGwAZQBuAGEAbQBlACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABJAGYAIABuAG8AIABtAGEAdABjAGgAaQBuAGcAIABcACIAXQBcACIAIABjAGgAYQByAGEAYwB0AGUAcgAgAGkAcwAgAGYAbwB1AG4AZAAgAHQAaABlAG4AIAByAGUAdAB1AHIAbgAgAGEAbgAgAGUAbQBwAHQAeQAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAXwB3AHMATgBhAG0AZQAsACAASQBGACgAXwBmAGkAbABlAE4AYQBtAGUAIAA8AD4AIABcACIAXAAiACwAIABUAEUAWABUAEEARgBUAEUAUgAoACAAXwBmAGkAbABlAE4AYQBtAGUALAAgAFwAIgBdAFwAIgAsACAALQAxACwAIAAsACAALAAgAFwAIgAjAFwAIgApACwAIABcACIAIwBbAEUAcgByAG8AcgA6ACAAVwBvAHIAawBiAG8AbwBrACAAbQB1AHMAdAAgAGIAZQAgAHMAYQB2AGUAZABdAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAIABmAG8AcgAgAGEAbgAgAGUAcgByAG8AcgAgAHYAYQBsAHUAZQAgAG8AcgAgAGUAbQBwAHQAeQAgAHMAdAByAGkAbgBnACAAYQBuAGQAIABpAGYAIABmAG8AdQBuAGQAIAByAGUAdAB1AHIAbgAgAGEAIABjAHUAcwB0AG8AbQAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUALAAgAG8AdABoAGUAcgB3AGkAcwBlACAAcgBlAHQAdQByAG4AIAB0AGgAZQAgAHcAbwByAGsAcwBoAGUAZQB0ACAAbgBhAG0AZQAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAXwByAHQAbgAsACAASQBGACgAIABPAFIAKAAgAEkAUwBFAFIAUgBPAFIAKABfAHcAcwBOAGEAbQBlACkALAAgAF8AdwBzAE4AYQBtAGUAIAA9ACAAXAAiACMAXAAiACkALAAgAFwAIgAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFMAaABlAGUAdAAgAG4AYQBtAGUAXQBcACIALAAgAF8AdwBzAE4AYQBtAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARgBpAG4AYQBsACAAYwBoAGUAYwBrACAAdABvACAAcwBlAGUAIABpAGYAIAB0AGgAZQByAGUAIAB3AGEAcwAgAGEAbgAgAGkAbgBwAHUAdAAgAGUAcgByAG8AcgAsACAAYQBuAGQAIABpAGYAIABzAG8AIAByAGUAdAB1AHIAbgAgAHQAaABlACAAYwB1AHMAdABvAG0AIABlAHIAcgBvAHIAIABtAGUAcwBzAGEAZwBlAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAXwBpAG4AcABDAGgAawAgADwAPgAgAFwAIgBcACIALAAgAF8AaQBuAHAAQwBoAGsALAAgAF8AcgB0AG4AKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAXABuACAAIAAgACAATgBhAG0AZQA6ACAAIAAgACAAIAAgACAAIABXAG8AcgBrAGIAbwBvAGsATgBhAG0AZQAoACkAXABuACAAIAAgACAAVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAxAC4AMAA1ACAAKAAyADMALQBNAGEAcgAtADIAMAAyADUAKQAgAC0ALQAgAFIAIABTAGkAbABrACwAIABSAFgATAAgAEQAZQB2AGUAbABvAHAAbQBlAG4AdABcAG4AIAAgACAAIABEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgAgACoALwAvACoAKgBSAGUAdAB1AHIAbgBzACAAdABoAGUAIABXAG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlACwAIAB3AGkAdABoACAAbwByACAAdwBpAHQAaABvAHUAdAAgAHQAaABlACAAZgBpAGwAZQAgAGUAeAB0AGUAbgBzAGkAbwBuACwAIABmAG8AcgAgAHQAaABlACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlACAAcAByAG8AdgBpAGQAZQBkADsAIABXAG8AcgBrAGIAbwBvAGsAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkACAAZgBpAHIAcwB0ACoALwAvACoAXABuACAAIAAgACAAUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAKwAgAGMAZQBsAGwAXwByAGUAZgAgACAAIAAgACAAIAAgACAAIAAgAD0AIAAoAHIAZQBxAHUAaQByAGUAZAApACAAQQAgAHYAYQBsAGkAZAAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAsACAAZQAuAGcALgAgAEEAMQAsACAAbwByACAAJwBTAGgAZQBlAHQAMQAnACEAQQAxAFwAbgAgACAAIAAgACAAIAAgACAAKwAgAHIAZQBtAG8AdgBlAF8AZQB4AHQAZQBuAHMAaQBvAG4AIAAgAD0AIAAoAG8AcAB0AGkAbwBuAGEAbAApACAAQQAgAFQAUgBVAEUALwBGAEEATABTAEUAIABvAHIAIAAxAC8AMAAgAHYAYQBsAHUAZQAgAHQAbwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdwBoAGUAdABoAGUAcgAgAHQAbwAgAHIAZQBtAG8AdgBlACAAdABoAGUAIABmAGkAbABlACAAZQB4AHQAZQBuAHMAaQBvAG4AIABmAHIAbwBtACAAdABoAGUAIAB3AG8AcgBrAGIAbwBvAGsAIABmAGkAbABlAG4AYQBtAGUAXABuACAAIAAgACAARQByAHIAbwByACAAYwBvAGQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQAgACAAIAA9ACAAdABoAGUAIABjAGUAbABsAF8AcgBlAGYAIABwAGEAcgBhAG0AZQB0AGUAcgAgAHIAZQBxAHUAaQByAGUAcwAgAGEAIAB2AGEAbABpAGQAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByADoAIABXAG8AcgBrAGIAbwBvAGsAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkAF0AIAAgACAAIAA9ACAAdABoAGUAIABXAG8AcgBrAGIAbwBvAGsAIABmAGkAbABlACAAbQB1AHMAdAAgAGIAZQAgAHMAYQB2AGUAZAAgAGYAaQByAHMAdAAgAGkAbgAgAG8AcgBkAGUAcgAgAGYAbwByACAAdABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIAB0AG8AIAB3AG8AcgBrACAAYwBvAHIAcgBlAGMAdABsAHkAXABuACAAIAAgACAAIAAgACAAIAAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUAXQAgACAAIAAgACAAIAA9ACAAYQBuACAAZQByAHIAbwByACAAbwBjAGMAdQByAHIAZQBkACAAZwBlAHQAdABpAG4AZwAgAHQAaABlACAAZgBpAGwAZQBuAGEAbQBlACAAcwB0AHIAaQBuAGcAIABvAHIAIABlAHgAdAByAGEAYwB0AGkAbgBnACAAdABoAGUAIABXAG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlACAAZgByAG8AbQAgAHQAaABlACAAZgBpAGwAZQBuAGEAbQBlACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAATgBvAHQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAtACAAVABoAGUAIABmAHUAbgBjAHQAaQBvAG4AIABvAHUAdABwAHUAdABzACAAYwB1AHMAdABvAG0AIABlAHIAcgBvAHIAIABtAGUAcwBzAGEAZwBlAHMAIABhAHMAIABzAHQAcgBpAG4AZwBzADsAIAB0AGgAZQBzAGUAIAB3AGkAbABsACAAbgBvAHQAIABiAGUAIABmAGwAYQBnAGcAZQBkACAAYgB5ACAARQB4AGMAZQBsACAAbwByACAAYQBuAHkAIABhAGQAZAAtAGkAbgBzACAAYQBzACAAZQByAHIAbwByACAAYwBlAGwAbABzAC4AXABuACAAIAAgACAAIAAgACAAIAAtACAAQQBsAHQAZQByAG4AYQB0AGkAdgBlAGwAeQAsACAAdABoAGUAIABjAHUAcwB0AG8AbQAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAcwAgAGMAYQBuACAAYgBlACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAG4AYQB0AGkAdgBlACAARQB4AGMAZQBsACAAZQByAHIAbwByACAAYwBvAGQAZQBzACAAcwBvACAAdABoAGEAdAAgAHQAaABlACAAZQByAHIAbwByACAAaQBzACAAZgBsAGEAZwBnAGUAZAAgAGkAbgAgAHQAaABlACAAbgBvAHIAbQBhAGwAIAB3AGEAeQA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAdABvACAAZABvACAAdABoAGkAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AIAByAGUAcABsAGEAYwBlACAAdABoAGUAIABcACIAIwBbAEUAcgByAG8AcgA6ACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlACAAcgBlAHEAdQBpAHIAZQBkAF0AXAAiACAAcwB0AHIAaQBuAGcAIAB3AGkAdABoACAAdABoAGUAIAAjAFYAQQBMAFUARQAhACAAKABvAHIAIAAjAFIARQBGACEAKQAgAGUAcgByAG8AcgAgAGMAbwBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQAgAHIAZQBwAGwAYQBjAGUAIAB0AGgAZQAgAFwAIgAjAFsARQByAHIAbwByADoAIABXAG8AcgBrAGIAbwBvAGsAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkAF0AXAAiACAAYQBuAGQAIABcACIAIwBbAEUAcgByAG8AcgAgAHIAZQBhAGQAaQBuAGcAIABXAG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlAF0AXAAiACAAcwB0AHIAaQBuAGcAcwAgAHcAaQB0AGgAIABMAEEATQBCAEQAQQAoADAAKQAgAGkAbgAgAG8AcgBkAGUAcgAgAHQAbwAgAGMAcgBlAGEAdABlACAAYQAgACMAQwBBAEwAQwAhACAAZQByAHIAbwByACAAYwBvAGQAZQBcAG4AKgAvAFwAbgBXAG8AcgBrAGIAbwBvAGsATgBhAG0AZQAgAD0AIABMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAC8ALwAgAFAAYQByAGEAbQBlAHQAZQByACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAbgAgACAAIAAgAGMAZQBsAGwAXwByAGUAZgAsAFwAbgAgACAAIAAgAFsAcgBlAG0AbwB2AGUAXwBlAHgAdABlAG4AcwBpAG8AbgBdACwAXABuACAAIAAgACAALwAvACAATQBhAGkAbgAgAGYAdQBuAGMAdABpAG8AbgAgAGIAbwBkAHkALwBjAGEAbABjAHUAbABhAHQAaQBvAG4AcwBcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAVQBwAGQAYQB0AGUAIAB0AGgAZQAgAG8AcAB0AGkAbwBuAGEAbAAgAGkAbgBwAHUAdAAgAHQAbwAgAGEAIABkAGUAZgBhAHUAbAB0ACAAbwBmACAARgBhAGwAcwBlACAAaQBmACAAbwBtAGkAdAB0AGUAZAAgAG8AcgAgAGEAIABuAG8AbgAtAEIAbwBvAGwAZQBhAG4ALwBuAG8AbgAtAG4AdQBtAGUAcgBpAGMAIAB2AGEAbAB1AGUAIABpAHMAIABzAHUAcABwAGwAaQBlAGQAXABuACAAIAAgACAAIAAgACAAIABfAGUAeAB0AEMAaABrACwAIABBAE4ARAAoACAATgBPAFQAKABJAFMATABPAEcASQBDAEEATAAoAHIAZQBtAG8AdgBlAF8AZQB4AHQAZQBuAHMAaQBvAG4AKQApACwAIABOAE8AVAAoAEkAUwBOAFUATQBCAEUAUgAoAHIAZQBtAG8AdgBlAF8AZQB4AHQAZQBuAHMAaQBvAG4AKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AZgBpAGwAZQBFAHgAdAAsACAASQBGACgAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAIABJAFMATwBNAEkAVABUAEUARAAoAHIAZQBtAG8AdgBlAF8AZQB4AHQAZQBuAHMAaQBvAG4AKQAsACAAXwBlAHgAdABDAGgAawApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBBAEwAUwBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAG8AdgBlAF8AZQB4AHQAZQBuAHMAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAIAB0AGgAYQB0ACAAdABoAGUAIABjAGUAbABsAF8AcgBlAGYAIABpAG4AcAB1AHQAIABzAHUAcABwAGwAaQBlAGQAIABpAHMAIABhACAAdgBhAGwAaQBkACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAIAAgACAAIAAgACAAXwBpAG4AcABDAGgAawAsACAASQBGACgAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMAUgBFAEYAKABjAGUAbABsAF8AcgBlAGYAKQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHIAZQBxAHUAaQByAGUAZABdAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABHAGUAdAAgAHQAaABlACAAZgBpAGwAZQBuAGEAbQBlACAAcwB0AHIAaQBuAGcAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAG4AYQB0AGkAdgBlACAAQwBFAEwATAAoACkAIABmAHUAbgBjAHQAaQBvAG4AIABhAG4AZAAgAHQAaABlACAAYwBlAGwAbABfAHIAZQBmACAAYQByAGcAdQBtAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAXwBmAGkAbABlAE4AYQBtAGUALAAgAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAYwBlAGwAbABfAHIAZQBmACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFUAcwBlACAAYQAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAVABFAFgAVABBAEYAVABFAFIAKAApACAAYQBuAGQAIABUAEUAWABUAEIARQBGAE8AUgBFACgAKQAgAGYAdQBuAGMAdABpAG8AbgBzACAAdABvACAAZwBlAHQAIAB0AGgAZQAgAHcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUAIABmAHIAbwBtACAAdABoAGUAIABmAGkAbABlAG4AYQBtAGUAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgAF8AcwB0AHIATgBhAG0AZQAsACAAVABFAFgAVABCAEUARgBPAFIARQAoACAAVABFAFgAVABBAEYAVABFAFIAKABfAGYAaQBsAGUATgBhAG0AZQAsACAAXAAiAFsAXAAiACwAIAAtADEALAAgACwAIAAsACAAXAAiACMAXAAiACkALAAgAFwAIgBdAFwAIgAsACAALQAxACwAIAAsACAALAAgAFwAIgAjAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAbQBvAHYAZQAgAHQAaABlACAAZgBpAGwAZQAgAGUAeAB0AGUAbgBzAGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAdwBvAHIAawBiAG8AbwBrACAAbgBhAG0AZQAgAHMAdAByAGkAbgBnACAAYQBzACAAcgBlAHEAdQBpAHIAZQBkAFwAbgAgACAAIAAgACAAIAAgACAAXwB3AGIATgBhAG0AZQAsACAASQBGACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AZgBpAGwAZQBFAHgAdAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABfAHMAdAByAE4AYQBtAGUALAAgAFwAIgAuAFwAIgAsACAALQAxACwAIAAsACAALAAgAF8AcwB0AHIATgBhAG0AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwBzAHQAcgBOAGEAbQBlAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARABlAHQAZQByAG0AaQBuAGUAIAB3AGgAZQB0AGgAZQByACAAdABvACAAcgBlAHQAdQByAG4AIABhAG4AIABlAHIAcgBvAHIAIABtAGUAcwBzAGEAZwBlACAAbwByACAAdABoAGUAIAB3AG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABfAHIAdABuACwAIABJAEYAUwAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGYAaQBsAGUATgBhAG0AZQAgAD0AIABcACIAXAAiACwAIABcACIAIwBbAEUAcgByAG8AcgA6ACAAVwBvAHIAawBiAG8AbwBrACAAbQB1AHMAdAAgAGIAZQAgAHMAYQB2AGUAZABdAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKAAgAEkAUwBFAFIAUgBPAFIAKABfAHcAYgBOAGEAbQBlACkALAAgAF8AdwBiAE4AYQBtAGUAIAA9ACAAXAAiACMAXAAiACkALAAgAFwAIgAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUAXQBcACIALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAFIAVQBFACwAIABfAHcAYgBOAGEAbQBlAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARgBpAG4AYQBsAGwAeQAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdwBoAGUAdABoAGUAcgAgAHQAbwAgAHIAZQB0AHUAcgBuACAAYQBuACAAaQBuAHAAdQB0ACAAZQByAHIAbwByACAAbQBlAHMAcwBhAGcAZQAgAG8AcgAgAHQAaABlACAAcgBlAHQAdQByAG4AIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAF8AaQBuAHAAQwBoAGsAIAA8AD4AIABcACIAXAAiACwAIABfAGkAbgBwAEMAaABrACwAIABfAHIAdABuACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqAFwAbgAgACAAIAAgAE4AYQBtAGUAOgAgACAAIAAgACAAIAAgACAARgBpAGwAZQBQAGEAdABoACgAKQBcAG4AIAAgACAAIABWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgADEALgAwADQAIAAoADIAMwAtAE0AYQByAC0AMgAwADIANQApACAALQAtACAAUgAgAFMAaQBsAGsALAAgAFIAWABMACAARABlAHYAZQBsAG8AcABtAGUAbgB0AFwAbgAgACAAIAAgAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6ACAAKgAvAC8AKgAqAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAFcAbwByAGsAYgBvAG8AawAgAGYAaQBsAGUAIABwAGEAdABoACwAIAB3AGkAdABoACAAbwByACAAdwBpAHQAaABvAHUAdAAgAHQAaABlACAAZgB1AGwAbAAgAGYAaQBsAGUAIABuAGEAbQBlACwAIABmAG8AcgAgAHQAaABlACAAYwBlAGwAbAAgAHIAZQBmAGUAcgBlAG4AYwBlACAAcAByAG8AdgBpAGQAZQBkADsAIABXAG8AcgBrAGIAbwBvAGsAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkACAAZgBpAHIAcwB0ACoALwAvACoAXABuACAAIAAgACAAUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgACAAIAAgACAAKwAgAGMAZQBsAGwAXwByAGUAZgAgACAAIAAgACAAIAAgACAAIAAgAD0AIAAoAHIAZQBxAHUAaQByAGUAZAApACAAQQAgAHYAYQBsAGkAZAAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAsACAAZQAuAGcALgAgAEEAMQAsACAAbwByACAAJwBTAGgAZQBlAHQAMQAnACEAQQAxAFwAbgAgACAAIAAgACAAIAAgACAAKwAgAHIAZQBtAG8AdgBlAF8AbABhAHMAdABfAGMAaABhAHIAIAAgAD0AIAAoAG8AcAB0AGkAbwBuAGEAbAApACAAQQAgAFQAUgBVAEUALwBGAEEATABTAEUAIABvAHIAIAAxAC8AMAAgAHYAYQBsAHUAZQAgAHQAbwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdwBoAGUAdABoAGUAcgAgAHQAbwAgAHIAZQBtAG8AdgBlACAAdABoAGUAIABsAGEAcwB0ACAAYwBoAGEAcgBhAGMAdABlAHIAIABpAG4AIAB0AGgAZQAgAGYAaQBsAGUAIABwAGEAdABoACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAArACAAaQBuAGMAXwBmAGkAbABlAF8AbgBhAG0AZQAgACAAIAAgACAAPQAgACgAbwBwAHQAaQBvAG4AYQBsACkAIABBACAAVABSAFUARQAvAEYAQQBMAFMARQAgAG8AcgAgADEALwAwACAAdgBhAGwAdQBlACAAdABvACAAZABlAHQAZQByAG0AaQBuAGUAIAB3AGgAZQB0AGgAZQByACAAdABvACAAaQBuAGMAbAB1AGQAZQAgAHQAaABlACAAZgB1AGwAbAAgAGYAaQBsAGUAIABuAGEAbQBlACAAdwBpAHQAaAAgAGYAaQBsAGUAIABlAHgAdABlAG4AcwBpAG8AbgBcAG4AIAAgACAAIABFAHIAcgBvAHIAIABjAG8AZABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgACMAWwBFAHIAcgBvAHIAOgAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHIAZQBxAHUAaQByAGUAZABdACAAIAAgAD0AIAB0AGgAZQAgAGMAZQBsAGwAXwByAGUAZgAgAHAAYQByAGEAbQBlAHQAZQByACAAcgBlAHEAdQBpAHIAZQBzACAAYQAgAHYAYQBsAGkAZAAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgACMAWwBFAHIAcgBvAHIAOgAgAGkAbgB2AGEAbABpAGQAIABvAHAAdABpAG8AbgBhAGwAIABpAG4AcAB1AHQAXQAgACAAIAAgAD0AIABlAGkAdABoAGUAcgAgAHQAaABlACAAcgBlAG0AbwB2AGUAXwBsAGEAcwB0AF8AYwBoAGEAcgAgAG8AdAAgAGkAbgBjAF8AZgBpAGwAZQBfAG4AYQBtAGUAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAbgBvAHQAIABhACAAbABvAGcAaQBjAGEAbAAgACgAVABSAFUARQAvAEYAQQBMAFMARQApACAAbwByACAAbgB1AG0AZQByAGkAYwAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAIAAgACMAWwBFAHIAcgBvAHIAOgAgAFcAbwByAGsAYgBvAG8AawAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAXQAgACAAIAAgAD0AIAB0AGgAZQAgAFcAbwByAGsAYgBvAG8AawAgAGYAaQBsAGUAIABtAHUAcwB0ACAAYgBlACAAcwBhAHYAZQBkACAAZgBpAHIAcwB0ACAAaQBuACAAbwByAGQAZQByACAAZgBvAHIAIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAHQAbwAgAHcAbwByAGsAIABjAG8AcgByAGUAYwB0AGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACMAWwBFAHIAcgBvAHIAIAByAGUAYQBkAGkAbgBnACAARgBpAGwAZQAgAFAAYQB0AGgAXQAgACAAIAAgACAAIAAgACAAIAAgAD0AIABhAG4AIABlAHIAcgBvAHIAIABvAGMAYwB1AHIAcgBlAGQAIABnAGUAdAB0AGkAbgBnACAAdABoAGUAIABmAGkAbABlACAAbgBhAG0AZQAgAHMAdAByAGkAbgBnACAAbwByACAAZQB4AHQAcgBhAGMAdABpAG4AZwAgAHQAaABlACAAZgBpAGwAZQAgAHAAYQB0AGgAIABmAHIAbwBtACAAdABoAGUAIABmAGkAbABlACAAbgBhAG0AZQAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIwBbAEUAcgByAG8AcgAgAHIAZQBhAGQAaQBuAGcAIABXAG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlAF0AIAAgACAAIAAgACAAPQAgAGEAbgAgAGUAcgByAG8AcgAgAG8AYwBjAHUAcgByAGUAZAAgAGcAZQB0AHQAaQBuAGcAIAB0AGgAZQAgAGYAaQBsAGUAIABuAGEAbQBlACAAcwB0AHIAaQBuAGcAIABvAHIAIABlAHgAdAByAGEAYwB0AGkAbgBnACAAdABoAGUAIABXAG8AcgBrAGIAbwBvAGsAIABuAGEAbQBlACAAZgByAG8AbQAgAHQAaABlACAAZgBpAGwAZQAgAG4AYQBtAGUAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIABOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABUAGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AdQB0AHAAdQB0AHMAIABjAHUAcwB0AG8AbQAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAcwAgAGEAcwAgAHMAdAByAGkAbgBnAHMAOwAgAHQAaABlAHMAZQAgAHcAaQBsAGwAIABuAG8AdAAgAGIAZQAgAGYAbABhAGcAZwBlAGQAIABiAHkAIABFAHgAYwBlAGwAIABvAHIAIABhAG4AeQAgAGEAZABkAC0AaQBuAHMAIABhAHMAIABlAHIAcgBvAHIAIABjAGUAbABsAHMALgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABBAGwAdABlAHIAbgBhAHQAaQB2AGUAbAB5ACwAIAB0AGgAZQAgAGMAdQBzAHQAbwBtACAAZQByAHIAbwByACAAbQBlAHMAcwBhAGcAZQBzACAAYwBhAG4AIABiAGUAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAbgBhAHQAaQB2AGUAIABFAHgAYwBlAGwAIABlAHIAcgBvAHIAIABjAG8AZABlAHMAIABzAG8AIAB0AGgAYQB0ACAAdABoAGUAIABlAHIAcgBvAHIAIABpAHMAIABmAGwAYQBnAGcAZQBkACAAaQBuACAAdABoAGUAIABuAG8AcgBtAGEAbAAgAHcAYQB5ADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAB0AG8AIABkAG8AIAB0AGgAaQBzADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQAgAHIAZQBwAGwAYQBjAGUAIAB0AGgAZQAgAFwAIgAjAFsARQByAHIAbwByADoAIABjAGUAbABsACAAcgBlAGYAZQByAGUAbgBjAGUAIAByAGUAcQB1AGkAcgBlAGQAXQBcACIAIABzAHQAcgBpAG4AZwAgAHcAaQB0AGgAIAB0AGgAZQAgACMAVgBBAEwAVQBFACEAIAAoAG8AcgAgACMAUgBFAEYAIQApACAAZQByAHIAbwByACAAYwBvAGQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAtACAAcgBlAHAAbABhAGMAZQAgAHQAaABlACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAGkAbgB2AGEAbABpAGQAIABvAHAAdABpAG8AbgBhAGwAIABpAG4AcAB1AHQAXQBcACIAIABzAHQAcgBpAG4AZwAgAHcAaQB0AGgAIAB0AGgAZQAgACMAVgBBAEwAVQBFACEAIABlAHIAcgBvAHIAIABjAG8AZABlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AIAByAGUAcABsAGEAYwBlACAAdABoAGUAIABcACIAIwBbAEUAcgByAG8AcgA6ACAAVwBvAHIAawBiAG8AbwBrACAAbQB1AHMAdAAgAGIAZQAgAHMAYQB2AGUAZABdAFwAIgAsACAAXAAiACMAWwBFAHIAcgBvAHIAIAByAGUAYQBkAGkAbgBnACAARgBpAGwAZQAgAFAAYQB0AGgAXQBcACIALAAgAGEAbgBkACAAXAAiACMAWwBFAHIAcgBvAHIAIAByAGUAYQBkAGkAbgBnACAAUwBoAGUAZQB0ACAAbgBhAG0AZQBdAFwAIgAgAHMAdAByAGkAbgBnAHMAIAB3AGkAdABoACAATABBAE0AQgBEAEEAKAAwACkAIABpAG4AIABvAHIAZABlAHIAIAB0AG8AIABjAHIAZQBhAHQAZQAgAGEAIAAjAEMAQQBMAEMAIQAgAGUAcgByAG8AcgAgAGMAbwBkAGUAXABuACoALwBcAG4ARgBpAGwAZQBQAGEAdABoACAAPQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAALwAvACAAUABhAHIAYQBtAGUAdABlAHIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXABuACAAIAAgACAAYwBlAGwAbABfAHIAZQBmACwAXABuACAAIAAgACAAWwByAGUAbQBvAHYAZQBfAGwAYQBzAHQAXwBjAGgAYQByAF0ALABcAG4AIAAgACAAIABbAGkAbgBjAF8AZgBpAGwAZQBfAG4AYQBtAGUAXQAsAFwAbgAgACAAIAAgAC8ALwAgAE0AYQBpAG4AIABmAHUAbgBjAHQAaQBvAG4AIABiAG8AZAB5AC8AYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAbgBwAHUAdAAgAGMAaABlAGMAawBzAFwAbgAgACAAIAAgACAAIAAgACAAXwBjAGgAcgBDAGgAawAsACAAQQBOAEQAKAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAByAGUAbQBvAHYAZQBfAGwAYQBzAHQAXwBjAGgAYQByACkAKQAsACAATgBPAFQAKABJAFMATABPAEcASQBDAEEATAAoAHIAZQBtAG8AdgBlAF8AbABhAHMAdABfAGMAaABhAHIAKQApACwAIABOAE8AVAAoAEkAUwBOAFUATQBCAEUAUgAoAHIAZQBtAG8AdgBlAF8AbABhAHMAdABfAGMAaABhAHIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AZgBuAG0AQwBoAGsALAAgAEEATgBEACgAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAaQBuAGMAXwBmAGkAbABlAF8AbgBhAG0AZQApACkALAAgAE4ATwBUACgASQBTAEwATwBHAEkAQwBBAEwAKABpAG4AYwBfAGYAaQBsAGUAXwBuAGEAbQBlACkAKQAsACAATgBPAFQAKABJAFMATgBVAE0AQgBFAFIAKABpAG4AYwBfAGYAaQBsAGUAXwBuAGEAbQBlACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIABfAHIAZQBmAEMAaABrACwAIABOAE8AVAAoAEkAUwBSAEUARgAoAGMAZQBsAGwAXwByAGUAZgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEQAZQBhAGwAaQBuAGcAIAB3AGkAdABoACAAbwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwAsACAAcwBlAHQAdABpAG4AZwAgAGQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwAgAGkAZgAgAG8AbQBpAHQAdABlAGQAXABuACAAIAAgACAAIAAgACAAIABfAGwAYQBzAHQAQwBoAHIALAAgAEkARgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKAAgAEkAUwBPAE0ASQBUAFQARQBEACgAcgBlAG0AbwB2AGUAXwBsAGEAcwB0AF8AYwBoAGEAcgApACwAIABfAGMAaAByAEMAaABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBBAEwAUwBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAG8AdgBlAF8AbABhAHMAdABfAGMAaABhAHIAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABfAGkAbgBjAEYAaQBsAGUALAAgAEkARgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKAAgAEkAUwBPAE0ASQBUAFQARQBEACgAaQBuAGMAXwBmAGkAbABlAF8AbgBhAG0AZQApACwAIABfAGYAbgBtAEMAaABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBBAEwAUwBFACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBjAF8AZgBpAGwAZQBfAG4AYQBtAGUAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABHAGUAdAAgAHQAaABlACAAZgB1AGwAbAAgAGYAaQBsAGUAIABwAGEAdABoACAAYQBuAGQAIABuAGEAbQBlAFwAbgAgACAAIAAgACAAIAAgACAAXwBmAHUAbABsACwAIABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAGMAZQBsAGwAXwByAGUAZgApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABmAGkAbABlACAAcABhAHQAaAAgAG8AbgBsAHkAXABuACAAIAAgACAAIAAgACAAIABfAHAAYQB0AGgALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABfAGYAdQBsAGwALAAgAFwAIgBbAFwAIgAsACAALQAxACwAIAAsACAALAAgAFwAIgAjAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABfAGYAaQBsAGUAUABhAHQAaAAsACAASQBGACgAXwBsAGEAcwB0AEMAaAByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBGAFQAKABfAHAAYQB0AGgALAAgAEwARQBOACgAXwBwAGEAdABoACkAIAAtACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AcABhAHQAaABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIAB0AGgAZQAgAFcAbwByAGsAYgBvAG8AawAgAG4AYQBtAGUAIABlAGwAZQBtAGUAbgB0ACAAaQBuAGMALgAgAGYAaQBsAGUAIABlAHgAdABlAG4AcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgAF8AdwBiAE4AYQBtAGUALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKAAgAFQARQBYAFQAQQBGAFQARQBSACgAXwBmAHUAbABsACwAIABcACIAWwBcACIALAAgAC0AMQAsACAALAAgACwAIABcACIAIwBcACIAKQAsACAAXAAiAF0AXAAiACwAIAAtADEALAAgACwAIAAsACAAXAAiACMAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAaABlAGMAawAgAGYAbwByACAAaQBuAHAAdQB0ACAAZQByAHIAbwByAHMAIABhAG4AZAAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAgAGUAcgByAG8AcgBzACwAIABhAG4AZAAgAHMAZQB0ACAAdABoAGUAIABhAHAAcAByAG8AcAByAGkAYQB0AGUAIABlAHIAcgBvAHIAIABtAGUAcwBzAGEAZwBlAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATgBvAHQAZQAgAC0AIABlAHIAcgBvAHIAcwAgAHAAbABhAGMAZQBkACAAaQBuACAAbwByAGQAZQByACAAbwBmACAAaQBtAHAAbwByAHQAYQBuAGMAZQAvAHIAZQBwAG8AcgB0AGkAbgBnACAAYQBzACAAbwBuAGwAeQAgAGEAIABzAGkAbgBnAGwAZQAgAG0AZQBzAHMAYQBnAGUAIABpAHMAIAByAGUAdAB1AHIAbgBlAGQAIABmAG8AcgAgAG0AdQBsAHQAaQBwAGwAZQAgAGUAcgByAG8AcgBzAFwAbgAgACAAIAAgACAAIAAgACAAXwBlAHIAcgBDAGgAawAsACAASQBGAFMAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwByAGUAZgBDAGgAawAsACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAGMAZQBsAGwAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHIAZQBxAHUAaQByAGUAZABdAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGYAdQBsAGwAIAA9ACAAXAAiAFwAIgAsACAAXAAiACMAWwBFAHIAcgBvAHIAOgAgAFcAbwByAGsAYgBvAG8AawAgAG0AdQBzAHQAIABiAGUAIABzAGEAdgBlAGQAXQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAXwBjAGgAcgBDAGgAawAsACAAXwBmAG4AbQBDAGgAawApACwAIABcACIAIwBbAEUAcgByAG8AcgA6ACAAaQBuAHYAYQBsAGkAZAAgAG8AcAB0AGkAbwBuAGEAbAAgAGkAbgBwAHUAdABdAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABPAFIAKAAgAEkAUwBFAFIAUgBPAFIAKABfAGYAaQBsAGUAUABhAHQAaAApACwAIABfAGYAaQBsAGUAUABhAHQAaAAgAD0AIABcACIAIwBcACIAKQAsACAAXAAiACMAWwBFAHIAcgBvAHIAIAByAGUAYQBkAGkAbgBnACAARgBpAGwAZQAgAFAAYQB0AGgAXQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKAAgAE8AUgAoACAASQBTAEUAUgBSAE8AUgAoAF8AdwBiAE4AYQBtAGUAKQAsACAAXwB3AGIATgBhAG0AZQAgAD0AIABcACIAIwBcACIAKQAsACAAXwBpAG4AYwBGAGkAbABlACkALAAgAFwAIgAjAFsARQByAHIAbwByACAAcgBlAGEAZABpAG4AZwAgAFcAbwByAGsAYgBvAG8AawAgAE4AYQBtAGUAXQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAFUARQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAbwBuAHMAdAByAHUAYwB0ACAAdABoAGUAIAByAGUAcQB1AGkAcgBlAGQAIABvAHUAdABwAHUAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAXwByAHQAbgAsACAASQBGACgAXwBpAG4AYwBGAGkAbABlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AcABhAHQAaAAgACYAIABfAHcAYgBOAGEAbQBlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AZgBpAGwAZQBQAGEAdABoAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARgBpAG4AYQBsACAAYwBoAGUAYwBrACAALQAgAGkAZgAgAGEAbgAgAGUAcgByAG8AcgAgAG0AZQBzAHMAYQBnAGUAIABpAHMAIABwAHIAZQBzAGUAbgB0ACAAcgBlAHQAdQByAG4AIAB0AGgAYQB0ACwAIABvAHQAaABlAHIAdwBpAHMAZQAgAHIAZQB0AHUAcgBuACAAdABoAGUAIABjAG8AbgBzAHQAcgB1AGMAdABlAGQAIABvAHUAdABwAHUAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAXwBlAHIAcgBDAGgAawAgADwAPgAgAFwAIgBcACIALAAgAF8AZQByAHIAQwBoAGsALAAgAF8AcgB0AG4AKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAUgBYAEwAXwBTAGgAZQBlAHQATgBhAG0AZQAiACwAIgBSAFgATABfAFcAbwByAGsAYgBvAG8AawBOAGEAbQBlACIALAAiAFIAWABMAF8ARgBpAGwAZQBQAGEAdABoACIALAAiAFIAWABMAF8AVwBiAEkAbgBmAG8ALgBBAGIAbwB1AHQAIgAsACIAUgBYAEwAXwBXAGIASQBuAGYAbwAuAFMAaABlAGUAdABOAGEAbQBlACIALAAiAFIAWABMAF8AVwBiAEkAbgBmAG8ALgBXAG8AcgBrAGIAbwBvAGsATgBhAG0AZQAiACwAIgBSAFgATABfAFcAYgBJAG4AZgBvAC4ARgBpAGwAZQBQAGEAdABoACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiAKMAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
